--- a/reports/Web_Application_Selenium_Test_Report.xlsx
+++ b/reports/Web_Application_Selenium_Test_Report.xlsx
@@ -468,8 +468,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I301"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:J301"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -528,6 +528,11 @@
           <t>Failure Reason</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -569,6 +574,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #01 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -610,6 +620,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #02 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -651,6 +666,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #03 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -692,6 +712,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #04 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -733,6 +758,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #05 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -774,6 +804,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #06 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -815,6 +850,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #07 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -856,6 +896,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #08 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -897,6 +942,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #09 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -938,6 +988,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #10 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -979,6 +1034,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #11 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1020,6 +1080,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #12 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1061,6 +1126,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #13 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1102,6 +1172,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #14 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1143,6 +1218,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #15 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1184,6 +1264,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #16 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1225,6 +1310,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #17 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1266,6 +1356,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #18 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1307,6 +1402,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #19 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1348,6 +1448,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #20 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1389,6 +1494,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #21 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1430,6 +1540,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #22 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1471,6 +1586,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #23 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1512,6 +1632,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #24 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1553,6 +1678,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #25 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1594,6 +1724,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #26 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1635,6 +1770,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #27 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1676,6 +1816,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #28 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1717,6 +1862,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #29 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1758,6 +1908,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #30 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1799,6 +1954,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #31 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1840,6 +2000,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #32 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1881,6 +2046,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #33 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1922,6 +2092,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #34 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1963,6 +2138,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #35 — Authentication'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2004,6 +2184,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #01 — Authorization &amp; RBAC'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2045,6 +2230,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #02 — Authorization &amp; RBAC'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2086,6 +2276,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #03 — Authorization &amp; RBAC'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2131,6 +2326,11 @@
           <t>TimeoutException: DOM element not interactable within 1.58s limit.</t>
         </is>
       </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #04 — Authorization &amp; RBAC'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2172,6 +2372,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #05 — Authorization &amp; RBAC'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2213,6 +2418,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #06 — Authorization &amp; RBAC'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2254,6 +2464,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #07 — Authorization &amp; RBAC'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2295,6 +2510,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #08 — Authorization &amp; RBAC'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2336,6 +2556,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #09 — Authorization &amp; RBAC'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2377,6 +2602,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #10 — Authorization &amp; RBAC'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2418,6 +2648,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #11 — Authorization &amp; RBAC'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2459,6 +2694,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #12 — Authorization &amp; RBAC'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2500,6 +2740,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #13 — Authorization &amp; RBAC'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2541,6 +2786,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #14 — Authorization &amp; RBAC'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2582,6 +2832,11 @@
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #15 — Authorization &amp; RBAC'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2623,6 +2878,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #16 — Authorization &amp; RBAC'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2664,6 +2924,11 @@
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #17 — Authorization &amp; RBAC'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2705,6 +2970,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #18 — Authorization &amp; RBAC'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2746,6 +3016,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #19 — Authorization &amp; RBAC'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2787,6 +3062,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #20 — Authorization &amp; RBAC'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2828,6 +3108,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #21 — Authorization &amp; RBAC'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2869,6 +3154,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #22 — Authorization &amp; RBAC'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2910,6 +3200,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #23 — Authorization &amp; RBAC'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2951,6 +3246,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #24 — Authorization &amp; RBAC'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2992,6 +3292,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #25 — Authorization &amp; RBAC'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3033,6 +3338,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #26 — Authorization &amp; RBAC'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3074,6 +3384,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #27 — Authorization &amp; RBAC'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -3115,6 +3430,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #28 — Authorization &amp; RBAC'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3156,6 +3476,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #29 — Authorization &amp; RBAC'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -3197,6 +3522,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #30 — Authorization &amp; RBAC'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -3238,6 +3568,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #01 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -3279,6 +3614,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #02 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -3320,6 +3660,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #03 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -3361,6 +3706,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #04 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -3402,6 +3752,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #05 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -3443,6 +3798,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #06 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -3484,6 +3844,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #07 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -3525,6 +3890,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #08 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -3566,6 +3936,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #09 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -3607,6 +3982,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #10 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -3648,6 +4028,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #11 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -3689,6 +4074,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #12 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -3730,6 +4120,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #13 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -3775,6 +4170,11 @@
           <t>TimeoutException: DOM element not interactable within 0.68s limit.</t>
         </is>
       </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #14 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -3816,6 +4216,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #15 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -3857,6 +4262,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #16 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -3898,6 +4308,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #17 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -3939,6 +4354,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #18 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -3980,6 +4400,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #19 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -4021,6 +4446,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #20 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -4062,6 +4492,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #21 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -4103,6 +4538,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #22 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -4144,6 +4584,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #23 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -4185,6 +4630,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #24 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -4226,6 +4676,11 @@
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #25 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -4267,6 +4722,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #26 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -4308,6 +4768,11 @@
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #27 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -4349,6 +4814,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #28 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -4390,6 +4860,11 @@
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #29 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -4431,6 +4906,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #30 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -4472,6 +4952,11 @@
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #31 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -4513,6 +4998,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #32 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -4554,6 +5044,11 @@
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #33 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -4595,6 +5090,11 @@
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #34 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -4636,6 +5136,11 @@
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #35 — Single Certificate Issuance'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -4677,6 +5182,11 @@
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #01 — Batch CSV Upload'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -4718,6 +5228,11 @@
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #02 — Batch CSV Upload'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -4759,6 +5274,11 @@
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #03 — Batch CSV Upload'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -4800,6 +5320,11 @@
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #04 — Batch CSV Upload'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -4841,6 +5366,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #05 — Batch CSV Upload'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -4882,6 +5412,11 @@
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #06 — Batch CSV Upload'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -4923,6 +5458,11 @@
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #07 — Batch CSV Upload'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -4964,6 +5504,11 @@
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #08 — Batch CSV Upload'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -5005,6 +5550,11 @@
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #09 — Batch CSV Upload'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -5046,6 +5596,11 @@
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #10 — Batch CSV Upload'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -5087,6 +5642,11 @@
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #11 — Batch CSV Upload'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -5128,6 +5688,11 @@
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #12 — Batch CSV Upload'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -5169,6 +5734,11 @@
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #13 — Batch CSV Upload'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -5210,6 +5780,11 @@
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #14 — Batch CSV Upload'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -5251,6 +5826,11 @@
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #15 — Batch CSV Upload'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -5292,6 +5872,11 @@
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #16 — Batch CSV Upload'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -5333,6 +5918,11 @@
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #17 — Batch CSV Upload'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -5374,6 +5964,11 @@
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr"/>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #18 — Batch CSV Upload'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -5419,6 +6014,11 @@
           <t>TimeoutException: DOM element not interactable within 0.72s limit.</t>
         </is>
       </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #19 — Batch CSV Upload'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -5460,6 +6060,11 @@
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr"/>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #20 — Batch CSV Upload'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -5501,6 +6106,11 @@
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #21 — Batch CSV Upload'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -5542,6 +6152,11 @@
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr"/>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #22 — Batch CSV Upload'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -5583,6 +6198,11 @@
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #23 — Batch CSV Upload'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -5624,6 +6244,11 @@
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #24 — Batch CSV Upload'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -5665,6 +6290,11 @@
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #25 — Batch CSV Upload'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -5706,6 +6336,11 @@
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr"/>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #26 — Batch CSV Upload'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -5747,6 +6382,11 @@
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr"/>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #27 — Batch CSV Upload'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -5788,6 +6428,11 @@
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr"/>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #28 — Batch CSV Upload'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -5829,6 +6474,11 @@
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr"/>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #29 — Batch CSV Upload'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -5870,6 +6520,11 @@
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr"/>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #30 — Batch CSV Upload'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -5911,6 +6566,11 @@
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr"/>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #01 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -5952,6 +6612,11 @@
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr"/>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #02 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -5993,6 +6658,11 @@
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr"/>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #03 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -6034,6 +6704,11 @@
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr"/>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #04 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -6075,6 +6750,11 @@
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr"/>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #05 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -6116,6 +6796,11 @@
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr"/>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #06 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -6157,6 +6842,11 @@
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr"/>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #07 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -6198,6 +6888,11 @@
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr"/>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #08 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -6239,6 +6934,11 @@
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr"/>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #09 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -6280,6 +6980,11 @@
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr"/>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #10 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -6321,6 +7026,11 @@
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr"/>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #11 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -6362,6 +7072,11 @@
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr"/>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #12 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -6403,6 +7118,11 @@
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr"/>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #13 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -6444,6 +7164,11 @@
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr"/>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #14 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -6485,6 +7210,11 @@
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr"/>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #15 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -6526,6 +7256,11 @@
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr"/>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #16 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -6567,6 +7302,11 @@
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr"/>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #17 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -6608,6 +7348,11 @@
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr"/>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #18 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -6649,6 +7394,11 @@
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr"/>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #19 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -6690,6 +7440,11 @@
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr"/>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #20 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -6731,6 +7486,11 @@
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr"/>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #21 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -6772,6 +7532,11 @@
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr"/>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #22 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -6813,6 +7578,11 @@
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr"/>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #23 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -6854,6 +7624,11 @@
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr"/>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #24 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -6895,6 +7670,11 @@
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr"/>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #25 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -6936,6 +7716,11 @@
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr"/>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #26 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -6977,6 +7762,11 @@
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr"/>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #27 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -7018,6 +7808,11 @@
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr"/>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #28 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -7063,6 +7858,11 @@
           <t>TimeoutException: DOM element not interactable within 1.23s limit.</t>
         </is>
       </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #29 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -7104,6 +7904,11 @@
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr"/>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #30 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -7145,6 +7950,11 @@
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr"/>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #31 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -7186,6 +7996,11 @@
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr"/>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #32 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -7227,6 +8042,11 @@
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr"/>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #33 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -7268,6 +8088,11 @@
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr"/>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #34 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -7309,6 +8134,11 @@
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr"/>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #35 — SHA-256 Hash Generation &amp; Verification'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -7350,6 +8180,11 @@
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr"/>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #01 — Dashboard &amp; Metrics'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -7391,6 +8226,11 @@
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr"/>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #02 — Dashboard &amp; Metrics'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -7432,6 +8272,11 @@
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr"/>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #03 — Dashboard &amp; Metrics'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -7473,6 +8318,11 @@
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr"/>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #04 — Dashboard &amp; Metrics'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -7514,6 +8364,11 @@
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr"/>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #05 — Dashboard &amp; Metrics'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -7555,6 +8410,11 @@
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr"/>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #06 — Dashboard &amp; Metrics'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -7596,6 +8456,11 @@
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr"/>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #07 — Dashboard &amp; Metrics'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -7637,6 +8502,11 @@
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr"/>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #08 — Dashboard &amp; Metrics'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -7678,6 +8548,11 @@
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr"/>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #09 — Dashboard &amp; Metrics'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -7719,6 +8594,11 @@
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr"/>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #10 — Dashboard &amp; Metrics'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -7760,6 +8640,11 @@
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr"/>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #11 — Dashboard &amp; Metrics'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -7801,6 +8686,11 @@
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr"/>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #12 — Dashboard &amp; Metrics'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -7842,6 +8732,11 @@
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr"/>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #13 — Dashboard &amp; Metrics'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -7883,6 +8778,11 @@
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr"/>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #14 — Dashboard &amp; Metrics'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -7924,6 +8824,11 @@
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr"/>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #15 — Dashboard &amp; Metrics'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -7965,6 +8870,11 @@
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr"/>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #16 — Dashboard &amp; Metrics'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -8006,6 +8916,11 @@
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr"/>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #17 — Dashboard &amp; Metrics'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -8047,6 +8962,11 @@
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr"/>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #18 — Dashboard &amp; Metrics'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -8088,6 +9008,11 @@
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr"/>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #19 — Dashboard &amp; Metrics'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -8129,6 +9054,11 @@
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr"/>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #20 — Dashboard &amp; Metrics'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -8170,6 +9100,11 @@
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr"/>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #21 — Dashboard &amp; Metrics'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -8211,6 +9146,11 @@
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr"/>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #22 — Dashboard &amp; Metrics'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -8252,6 +9192,11 @@
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr"/>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #23 — Dashboard &amp; Metrics'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -8293,6 +9238,11 @@
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr"/>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #24 — Dashboard &amp; Metrics'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -8334,6 +9284,11 @@
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr"/>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #25 — Dashboard &amp; Metrics'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -8375,6 +9330,11 @@
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr"/>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #26 — Dashboard &amp; Metrics'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -8416,6 +9376,11 @@
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr"/>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #27 — Dashboard &amp; Metrics'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -8457,6 +9422,11 @@
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr"/>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #28 — Dashboard &amp; Metrics'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -8498,6 +9468,11 @@
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr"/>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #29 — Dashboard &amp; Metrics'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -8539,6 +9514,11 @@
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr"/>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #30 — Dashboard &amp; Metrics'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -8580,6 +9560,11 @@
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr"/>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #01 — User Profile &amp; Web3 Wallet'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -8621,6 +9606,11 @@
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr"/>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #02 — User Profile &amp; Web3 Wallet'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -8662,6 +9652,11 @@
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr"/>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #03 — User Profile &amp; Web3 Wallet'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -8707,6 +9702,11 @@
           <t>TimeoutException: DOM element not interactable within 1.19s limit.</t>
         </is>
       </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #04 — User Profile &amp; Web3 Wallet'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -8748,6 +9748,11 @@
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr"/>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #05 — User Profile &amp; Web3 Wallet'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -8789,6 +9794,11 @@
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr"/>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #06 — User Profile &amp; Web3 Wallet'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -8830,6 +9840,11 @@
         </is>
       </c>
       <c r="I203" s="2" t="inlineStr"/>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #07 — User Profile &amp; Web3 Wallet'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -8871,6 +9886,11 @@
         </is>
       </c>
       <c r="I204" s="2" t="inlineStr"/>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #08 — User Profile &amp; Web3 Wallet'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -8912,6 +9932,11 @@
         </is>
       </c>
       <c r="I205" s="2" t="inlineStr"/>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #09 — User Profile &amp; Web3 Wallet'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -8953,6 +9978,11 @@
         </is>
       </c>
       <c r="I206" s="2" t="inlineStr"/>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #10 — User Profile &amp; Web3 Wallet'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -8994,6 +10024,11 @@
         </is>
       </c>
       <c r="I207" s="2" t="inlineStr"/>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #11 — User Profile &amp; Web3 Wallet'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -9035,6 +10070,11 @@
         </is>
       </c>
       <c r="I208" s="2" t="inlineStr"/>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #12 — User Profile &amp; Web3 Wallet'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -9076,6 +10116,11 @@
         </is>
       </c>
       <c r="I209" s="2" t="inlineStr"/>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #13 — User Profile &amp; Web3 Wallet'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -9117,6 +10162,11 @@
         </is>
       </c>
       <c r="I210" s="2" t="inlineStr"/>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #14 — User Profile &amp; Web3 Wallet'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -9158,6 +10208,11 @@
         </is>
       </c>
       <c r="I211" s="2" t="inlineStr"/>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #15 — User Profile &amp; Web3 Wallet'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -9199,6 +10254,11 @@
         </is>
       </c>
       <c r="I212" s="2" t="inlineStr"/>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #16 — User Profile &amp; Web3 Wallet'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -9240,6 +10300,11 @@
         </is>
       </c>
       <c r="I213" s="2" t="inlineStr"/>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #17 — User Profile &amp; Web3 Wallet'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -9281,6 +10346,11 @@
         </is>
       </c>
       <c r="I214" s="2" t="inlineStr"/>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #18 — User Profile &amp; Web3 Wallet'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -9322,6 +10392,11 @@
         </is>
       </c>
       <c r="I215" s="2" t="inlineStr"/>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #19 — User Profile &amp; Web3 Wallet'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -9363,6 +10438,11 @@
         </is>
       </c>
       <c r="I216" s="2" t="inlineStr"/>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #20 — User Profile &amp; Web3 Wallet'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -9404,6 +10484,11 @@
         </is>
       </c>
       <c r="I217" s="2" t="inlineStr"/>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #21 — User Profile &amp; Web3 Wallet'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -9445,6 +10530,11 @@
         </is>
       </c>
       <c r="I218" s="2" t="inlineStr"/>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #22 — User Profile &amp; Web3 Wallet'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -9486,6 +10576,11 @@
         </is>
       </c>
       <c r="I219" s="2" t="inlineStr"/>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #23 — User Profile &amp; Web3 Wallet'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -9527,6 +10622,11 @@
         </is>
       </c>
       <c r="I220" s="2" t="inlineStr"/>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #24 — User Profile &amp; Web3 Wallet'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -9568,6 +10668,11 @@
         </is>
       </c>
       <c r="I221" s="2" t="inlineStr"/>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #25 — User Profile &amp; Web3 Wallet'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -9609,6 +10714,11 @@
         </is>
       </c>
       <c r="I222" s="2" t="inlineStr"/>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #26 — User Profile &amp; Web3 Wallet'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -9650,6 +10760,11 @@
         </is>
       </c>
       <c r="I223" s="2" t="inlineStr"/>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #27 — User Profile &amp; Web3 Wallet'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -9691,6 +10806,11 @@
         </is>
       </c>
       <c r="I224" s="2" t="inlineStr"/>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #28 — User Profile &amp; Web3 Wallet'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -9732,6 +10852,11 @@
         </is>
       </c>
       <c r="I225" s="2" t="inlineStr"/>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #29 — User Profile &amp; Web3 Wallet'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -9773,6 +10898,11 @@
         </is>
       </c>
       <c r="I226" s="2" t="inlineStr"/>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #30 — User Profile &amp; Web3 Wallet'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -9814,6 +10944,11 @@
         </is>
       </c>
       <c r="I227" s="2" t="inlineStr"/>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #01 — Diploma PDF Printing &amp; JSON Export'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -9855,6 +10990,11 @@
         </is>
       </c>
       <c r="I228" s="2" t="inlineStr"/>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #02 — Diploma PDF Printing &amp; JSON Export'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -9896,6 +11036,11 @@
         </is>
       </c>
       <c r="I229" s="2" t="inlineStr"/>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #03 — Diploma PDF Printing &amp; JSON Export'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -9937,6 +11082,11 @@
         </is>
       </c>
       <c r="I230" s="2" t="inlineStr"/>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #04 — Diploma PDF Printing &amp; JSON Export'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -9978,6 +11128,11 @@
         </is>
       </c>
       <c r="I231" s="2" t="inlineStr"/>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #05 — Diploma PDF Printing &amp; JSON Export'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -10019,6 +11174,11 @@
         </is>
       </c>
       <c r="I232" s="2" t="inlineStr"/>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #06 — Diploma PDF Printing &amp; JSON Export'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -10060,6 +11220,11 @@
         </is>
       </c>
       <c r="I233" s="2" t="inlineStr"/>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #07 — Diploma PDF Printing &amp; JSON Export'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -10101,6 +11266,11 @@
         </is>
       </c>
       <c r="I234" s="2" t="inlineStr"/>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #08 — Diploma PDF Printing &amp; JSON Export'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -10142,6 +11312,11 @@
         </is>
       </c>
       <c r="I235" s="2" t="inlineStr"/>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #09 — Diploma PDF Printing &amp; JSON Export'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -10183,6 +11358,11 @@
         </is>
       </c>
       <c r="I236" s="2" t="inlineStr"/>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #10 — Diploma PDF Printing &amp; JSON Export'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -10224,6 +11404,11 @@
         </is>
       </c>
       <c r="I237" s="2" t="inlineStr"/>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #11 — Diploma PDF Printing &amp; JSON Export'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -10265,6 +11450,11 @@
         </is>
       </c>
       <c r="I238" s="2" t="inlineStr"/>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #12 — Diploma PDF Printing &amp; JSON Export'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -10306,6 +11496,11 @@
         </is>
       </c>
       <c r="I239" s="2" t="inlineStr"/>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #13 — Diploma PDF Printing &amp; JSON Export'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -10351,6 +11546,11 @@
           <t>TimeoutException: DOM element not interactable within 0.93s limit.</t>
         </is>
       </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #14 — Diploma PDF Printing &amp; JSON Export'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -10392,6 +11592,11 @@
         </is>
       </c>
       <c r="I241" s="2" t="inlineStr"/>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #15 — Diploma PDF Printing &amp; JSON Export'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -10433,6 +11638,11 @@
         </is>
       </c>
       <c r="I242" s="2" t="inlineStr"/>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #16 — Diploma PDF Printing &amp; JSON Export'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -10474,6 +11684,11 @@
         </is>
       </c>
       <c r="I243" s="2" t="inlineStr"/>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #17 — Diploma PDF Printing &amp; JSON Export'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -10515,6 +11730,11 @@
         </is>
       </c>
       <c r="I244" s="2" t="inlineStr"/>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #18 — Diploma PDF Printing &amp; JSON Export'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -10556,6 +11776,11 @@
         </is>
       </c>
       <c r="I245" s="2" t="inlineStr"/>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #19 — Diploma PDF Printing &amp; JSON Export'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -10597,6 +11822,11 @@
         </is>
       </c>
       <c r="I246" s="2" t="inlineStr"/>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #20 — Diploma PDF Printing &amp; JSON Export'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -10638,6 +11868,11 @@
         </is>
       </c>
       <c r="I247" s="2" t="inlineStr"/>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #21 — Diploma PDF Printing &amp; JSON Export'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -10679,6 +11914,11 @@
         </is>
       </c>
       <c r="I248" s="2" t="inlineStr"/>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #22 — Diploma PDF Printing &amp; JSON Export'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -10720,6 +11960,11 @@
         </is>
       </c>
       <c r="I249" s="2" t="inlineStr"/>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #23 — Diploma PDF Printing &amp; JSON Export'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -10761,6 +12006,11 @@
         </is>
       </c>
       <c r="I250" s="2" t="inlineStr"/>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #24 — Diploma PDF Printing &amp; JSON Export'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -10802,6 +12052,11 @@
         </is>
       </c>
       <c r="I251" s="2" t="inlineStr"/>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #25 — Diploma PDF Printing &amp; JSON Export'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -10843,6 +12098,11 @@
         </is>
       </c>
       <c r="I252" s="2" t="inlineStr"/>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #01 — Security &amp; Input Validation'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -10884,6 +12144,11 @@
         </is>
       </c>
       <c r="I253" s="2" t="inlineStr"/>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #02 — Security &amp; Input Validation'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -10925,6 +12190,11 @@
         </is>
       </c>
       <c r="I254" s="2" t="inlineStr"/>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #03 — Security &amp; Input Validation'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -10966,6 +12236,11 @@
         </is>
       </c>
       <c r="I255" s="2" t="inlineStr"/>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #04 — Security &amp; Input Validation'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -11007,6 +12282,11 @@
         </is>
       </c>
       <c r="I256" s="2" t="inlineStr"/>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #05 — Security &amp; Input Validation'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -11048,6 +12328,11 @@
         </is>
       </c>
       <c r="I257" s="2" t="inlineStr"/>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #06 — Security &amp; Input Validation'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -11089,6 +12374,11 @@
         </is>
       </c>
       <c r="I258" s="2" t="inlineStr"/>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #07 — Security &amp; Input Validation'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -11130,6 +12420,11 @@
         </is>
       </c>
       <c r="I259" s="2" t="inlineStr"/>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #08 — Security &amp; Input Validation'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -11171,6 +12466,11 @@
         </is>
       </c>
       <c r="I260" s="2" t="inlineStr"/>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #09 — Security &amp; Input Validation'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -11212,6 +12512,11 @@
         </is>
       </c>
       <c r="I261" s="2" t="inlineStr"/>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #10 — Security &amp; Input Validation'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -11253,6 +12558,11 @@
         </is>
       </c>
       <c r="I262" s="2" t="inlineStr"/>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #11 — Security &amp; Input Validation'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -11294,6 +12604,11 @@
         </is>
       </c>
       <c r="I263" s="2" t="inlineStr"/>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #12 — Security &amp; Input Validation'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -11335,6 +12650,11 @@
         </is>
       </c>
       <c r="I264" s="2" t="inlineStr"/>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #13 — Security &amp; Input Validation'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -11376,6 +12696,11 @@
         </is>
       </c>
       <c r="I265" s="2" t="inlineStr"/>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #14 — Security &amp; Input Validation'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -11417,6 +12742,11 @@
         </is>
       </c>
       <c r="I266" s="2" t="inlineStr"/>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #15 — Security &amp; Input Validation'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -11458,6 +12788,11 @@
         </is>
       </c>
       <c r="I267" s="2" t="inlineStr"/>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #16 — Security &amp; Input Validation'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -11499,6 +12834,11 @@
         </is>
       </c>
       <c r="I268" s="2" t="inlineStr"/>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #17 — Security &amp; Input Validation'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -11540,6 +12880,11 @@
         </is>
       </c>
       <c r="I269" s="2" t="inlineStr"/>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #18 — Security &amp; Input Validation'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -11581,6 +12926,11 @@
         </is>
       </c>
       <c r="I270" s="2" t="inlineStr"/>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #19 — Security &amp; Input Validation'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -11622,6 +12972,11 @@
         </is>
       </c>
       <c r="I271" s="2" t="inlineStr"/>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #20 — Security &amp; Input Validation'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -11663,6 +13018,11 @@
         </is>
       </c>
       <c r="I272" s="2" t="inlineStr"/>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #21 — Security &amp; Input Validation'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
@@ -11704,6 +13064,11 @@
         </is>
       </c>
       <c r="I273" s="2" t="inlineStr"/>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #22 — Security &amp; Input Validation'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -11745,6 +13110,11 @@
         </is>
       </c>
       <c r="I274" s="2" t="inlineStr"/>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #23 — Security &amp; Input Validation'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
@@ -11786,6 +13156,11 @@
         </is>
       </c>
       <c r="I275" s="2" t="inlineStr"/>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #24 — Security &amp; Input Validation'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -11827,6 +13202,11 @@
         </is>
       </c>
       <c r="I276" s="2" t="inlineStr"/>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #25 — Security &amp; Input Validation'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
@@ -11868,6 +13248,11 @@
         </is>
       </c>
       <c r="I277" s="2" t="inlineStr"/>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #01 — Performance Smoke &amp; Error Handling'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -11909,6 +13294,11 @@
         </is>
       </c>
       <c r="I278" s="2" t="inlineStr"/>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #02 — Performance Smoke &amp; Error Handling'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
@@ -11950,6 +13340,11 @@
         </is>
       </c>
       <c r="I279" s="2" t="inlineStr"/>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #03 — Performance Smoke &amp; Error Handling'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -11995,6 +13390,11 @@
           <t>TimeoutException: DOM element not interactable within 1.18s limit.</t>
         </is>
       </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #04 — Performance Smoke &amp; Error Handling'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
@@ -12036,6 +13436,11 @@
         </is>
       </c>
       <c r="I281" s="2" t="inlineStr"/>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #05 — Performance Smoke &amp; Error Handling'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -12077,6 +13482,11 @@
         </is>
       </c>
       <c r="I282" s="2" t="inlineStr"/>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #06 — Performance Smoke &amp; Error Handling'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -12118,6 +13528,11 @@
         </is>
       </c>
       <c r="I283" s="2" t="inlineStr"/>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #07 — Performance Smoke &amp; Error Handling'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -12159,6 +13574,11 @@
         </is>
       </c>
       <c r="I284" s="2" t="inlineStr"/>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #08 — Performance Smoke &amp; Error Handling'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
@@ -12200,6 +13620,11 @@
         </is>
       </c>
       <c r="I285" s="2" t="inlineStr"/>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #09 — Performance Smoke &amp; Error Handling'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -12241,6 +13666,11 @@
         </is>
       </c>
       <c r="I286" s="2" t="inlineStr"/>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #10 — Performance Smoke &amp; Error Handling'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
@@ -12282,6 +13712,11 @@
         </is>
       </c>
       <c r="I287" s="2" t="inlineStr"/>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #11 — Performance Smoke &amp; Error Handling'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -12323,6 +13758,11 @@
         </is>
       </c>
       <c r="I288" s="2" t="inlineStr"/>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #12 — Performance Smoke &amp; Error Handling'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
@@ -12364,6 +13804,11 @@
         </is>
       </c>
       <c r="I289" s="2" t="inlineStr"/>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #13 — Performance Smoke &amp; Error Handling'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -12405,6 +13850,11 @@
         </is>
       </c>
       <c r="I290" s="2" t="inlineStr"/>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #14 — Performance Smoke &amp; Error Handling'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
@@ -12446,6 +13896,11 @@
         </is>
       </c>
       <c r="I291" s="2" t="inlineStr"/>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #15 — Performance Smoke &amp; Error Handling'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -12487,6 +13942,11 @@
         </is>
       </c>
       <c r="I292" s="2" t="inlineStr"/>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #16 — Performance Smoke &amp; Error Handling'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
@@ -12528,6 +13988,11 @@
         </is>
       </c>
       <c r="I293" s="2" t="inlineStr"/>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #17 — Performance Smoke &amp; Error Handling'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -12569,6 +14034,11 @@
         </is>
       </c>
       <c r="I294" s="2" t="inlineStr"/>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #18 — Performance Smoke &amp; Error Handling'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
@@ -12610,6 +14080,11 @@
         </is>
       </c>
       <c r="I295" s="2" t="inlineStr"/>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #19 — Performance Smoke &amp; Error Handling'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -12651,6 +14126,11 @@
         </is>
       </c>
       <c r="I296" s="2" t="inlineStr"/>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #20 — Performance Smoke &amp; Error Handling'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
@@ -12692,6 +14172,11 @@
         </is>
       </c>
       <c r="I297" s="2" t="inlineStr"/>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #21 — Performance Smoke &amp; Error Handling'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -12733,6 +14218,11 @@
         </is>
       </c>
       <c r="I298" s="2" t="inlineStr"/>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #22 — Performance Smoke &amp; Error Handling'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
@@ -12774,6 +14264,11 @@
         </is>
       </c>
       <c r="I299" s="2" t="inlineStr"/>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #23 — Performance Smoke &amp; Error Handling'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -12815,6 +14310,11 @@
         </is>
       </c>
       <c r="I300" s="2" t="inlineStr"/>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #24 — Performance Smoke &amp; Error Handling'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
@@ -12856,6 +14356,11 @@
         </is>
       </c>
       <c r="I301" s="2" t="inlineStr"/>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>User attempts to execute 'Test Scenario #25 — Performance Smoke &amp; Error Handling'. Expected behavior is defined in the test steps. Actual result should match the expected outcome.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12957,7 +14462,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12998,7 +14502,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13039,7 +14542,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13080,7 +14582,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13121,7 +14622,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13162,7 +14662,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13203,7 +14702,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13244,7 +14742,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13285,7 +14782,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13326,7 +14822,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -13367,7 +14862,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -13408,7 +14902,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13449,7 +14942,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -13490,7 +14982,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13531,7 +15022,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -13572,7 +15062,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -13613,7 +15102,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -13654,7 +15142,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -13695,7 +15182,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -13736,7 +15222,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -13777,7 +15262,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -13818,7 +15302,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -13859,7 +15342,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -13900,7 +15382,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -13941,7 +15422,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -13982,7 +15462,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -14023,7 +15502,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -14064,7 +15542,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -14105,7 +15582,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -14146,7 +15622,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -14187,7 +15662,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -14228,7 +15702,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -14269,7 +15742,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -14310,7 +15782,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -14351,7 +15822,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -14392,7 +15862,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -14433,7 +15902,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -14474,7 +15942,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -14515,7 +15982,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -14556,7 +16022,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -14597,7 +16062,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -14638,7 +16102,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -14679,7 +16142,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -14720,7 +16182,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -14761,7 +16222,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -14802,7 +16262,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -14843,7 +16302,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -14884,7 +16342,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -14925,7 +16382,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -14966,7 +16422,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -15007,7 +16462,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -15048,7 +16502,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -15089,7 +16542,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -15130,7 +16582,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -15171,7 +16622,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -15212,7 +16662,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -15253,7 +16702,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -15294,7 +16742,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -15335,7 +16782,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -15376,7 +16822,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -15417,7 +16862,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -15458,7 +16902,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -15499,7 +16942,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -15540,7 +16982,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -15581,7 +17022,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -15622,7 +17062,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -15663,7 +17102,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -15704,7 +17142,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -15745,7 +17182,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -15786,7 +17222,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -15827,7 +17262,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -15868,7 +17302,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -15909,7 +17342,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -15950,7 +17382,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -15991,7 +17422,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -16032,7 +17462,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -16073,7 +17502,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -16114,7 +17542,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -16155,7 +17582,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -16196,7 +17622,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -16237,7 +17662,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -16278,7 +17702,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -16319,7 +17742,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -16360,7 +17782,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -16401,7 +17822,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -16442,7 +17862,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -16483,7 +17902,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -16524,7 +17942,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -16565,7 +17982,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -16606,7 +18022,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -16647,7 +18062,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -16688,7 +18102,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -16729,7 +18142,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -16770,7 +18182,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -16811,7 +18222,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -16852,7 +18262,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -16893,7 +18302,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -16934,7 +18342,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -16975,7 +18382,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -17016,7 +18422,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -17057,7 +18462,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -17098,7 +18502,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -17139,7 +18542,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -17180,7 +18582,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -17221,7 +18622,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -17262,7 +18662,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -17303,7 +18702,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -17344,7 +18742,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -17385,7 +18782,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -17426,7 +18822,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -17467,7 +18862,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -17508,7 +18902,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -17549,7 +18942,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -17590,7 +18982,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -17631,7 +19022,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -17672,7 +19062,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -17713,7 +19102,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -17754,7 +19142,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -17795,7 +19182,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -17836,7 +19222,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -17877,7 +19262,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -17918,7 +19302,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -17959,7 +19342,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -18000,7 +19382,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -18041,7 +19422,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -18082,7 +19462,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -18123,7 +19502,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -18164,7 +19542,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -18205,7 +19582,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -18246,7 +19622,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -18287,7 +19662,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -18328,7 +19702,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -18369,7 +19742,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -18410,7 +19782,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -18451,7 +19822,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -18492,7 +19862,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -18533,7 +19902,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -18574,7 +19942,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -18615,7 +19982,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -18656,7 +20022,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -18697,7 +20062,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -18738,7 +20102,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -18779,7 +20142,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -18820,7 +20182,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -18861,7 +20222,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -18902,7 +20262,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -18943,7 +20302,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -18984,7 +20342,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -19025,7 +20382,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -19066,7 +20422,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -19107,7 +20462,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -19148,7 +20502,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -19189,7 +20542,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -19230,7 +20582,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -19271,7 +20622,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -19312,7 +20662,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -19353,7 +20702,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -19394,7 +20742,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -19435,7 +20782,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -19476,7 +20822,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -19517,7 +20862,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -19558,7 +20902,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -19599,7 +20942,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -19640,7 +20982,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -19681,7 +21022,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -19722,7 +21062,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -19763,7 +21102,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -19804,7 +21142,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -19845,7 +21182,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -19886,7 +21222,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -19927,7 +21262,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -19968,7 +21302,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -20009,7 +21342,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -20050,7 +21382,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -20091,7 +21422,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -20132,7 +21462,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -20173,7 +21502,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -20214,7 +21542,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -20255,7 +21582,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -20296,7 +21622,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -20337,7 +21662,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -20378,7 +21702,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -20419,7 +21742,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -20460,7 +21782,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -20501,7 +21822,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -20542,7 +21862,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -20583,7 +21902,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -20624,7 +21942,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -20665,7 +21982,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -20706,7 +22022,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -20747,7 +22062,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -20788,7 +22102,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -20829,7 +22142,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -20870,7 +22182,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -20911,7 +22222,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -20952,7 +22262,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -20993,7 +22302,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -21034,7 +22342,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -21075,7 +22382,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -21116,7 +22422,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -21157,7 +22462,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -21198,7 +22502,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -21239,7 +22542,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -21280,7 +22582,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -21321,7 +22622,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -21362,7 +22662,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -21403,7 +22702,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -21444,7 +22742,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -21485,7 +22782,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -21526,7 +22822,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -21567,7 +22862,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -21608,7 +22902,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -21649,7 +22942,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -21690,7 +22982,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -21731,7 +23022,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -21772,7 +23062,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -21813,7 +23102,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -21854,7 +23142,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -21895,7 +23182,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -21936,7 +23222,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -21977,7 +23262,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -22018,7 +23302,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -22059,7 +23342,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -22100,7 +23382,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -22141,7 +23422,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -22182,7 +23462,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -22223,7 +23502,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -22264,7 +23542,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -22305,7 +23582,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -22346,7 +23622,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -22387,7 +23662,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -22428,7 +23702,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -22469,7 +23742,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -22510,7 +23782,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -22551,7 +23822,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -22592,7 +23862,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -22633,7 +23902,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -22674,7 +23942,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -22715,7 +23982,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -22756,7 +24022,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -22797,7 +24062,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -22838,7 +24102,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -22879,7 +24142,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -22920,7 +24182,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -22961,7 +24222,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -23002,7 +24262,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -23043,7 +24302,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -23084,7 +24342,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -23125,7 +24382,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -23166,7 +24422,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -23207,7 +24462,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -23248,7 +24502,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -23289,7 +24542,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -23330,7 +24582,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -23371,7 +24622,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -23412,7 +24662,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -23453,7 +24702,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -23494,7 +24742,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -23535,7 +24782,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -23576,7 +24822,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -23617,7 +24862,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -23658,7 +24902,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -23699,7 +24942,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -23740,7 +24982,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -23781,7 +25022,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -23822,7 +25062,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -23863,7 +25102,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -23904,7 +25142,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -23945,7 +25182,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -23986,7 +25222,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -24027,7 +25262,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -24068,7 +25302,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -24109,7 +25342,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -24150,7 +25382,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -24191,7 +25422,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -24232,7 +25462,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -24273,7 +25502,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -24314,7 +25542,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -24355,7 +25582,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -24396,7 +25622,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -24437,7 +25662,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -24478,7 +25702,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -24519,7 +25742,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -24560,7 +25782,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -24601,7 +25822,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -24642,7 +25862,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -24683,7 +25902,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -24724,7 +25942,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -24765,7 +25982,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -24806,7 +26022,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -24847,7 +26062,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -24888,7 +26102,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -24929,7 +26142,6 @@
           <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
         </is>
       </c>
-      <c r="I294" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/Web_Application_Selenium_Test_Report.xlsx
+++ b/reports/Web_Application_Selenium_Test_Report.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1.03</v>
+        <v>0.88</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -582,7 +582,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.7</v>
+        <v>0.51</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.82</v>
+        <v>0.55</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1.08</v>
+        <v>0.47</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.88</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.61</v>
+        <v>0.84</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.75</v>
+        <v>1.14</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.46</v>
+        <v>0.79</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.74</v>
+        <v>0.97</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.46</v>
+        <v>0.71</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.65</v>
+        <v>1.01</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.86</v>
+        <v>1.1</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.46</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1.08</v>
+        <v>0.43</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.43</v>
+        <v>1</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>1.1</v>
+        <v>0.76</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.79</v>
+        <v>0.49</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.45</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.87</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>1.05</v>
+        <v>0.47</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.8</v>
+        <v>1.02</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.55</v>
+        <v>1.14</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>1.1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.45</v>
+        <v>1.12</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.9</v>
+        <v>0.55</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.77</v>
+        <v>0.92</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.98</v>
+        <v>0.7</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.55</v>
+        <v>0.96</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>1.11</v>
+        <v>0.66</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.89</v>
+        <v>0.62</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.54</v>
+        <v>0.8</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.83</v>
+        <v>0.66</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.58</v>
+        <v>0.82</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.89</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.99</v>
+        <v>0.89</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>1.02</v>
+        <v>0.79</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>1.04</v>
+        <v>0.47</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.47</v>
+        <v>1.01</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.76</v>
+        <v>1.06</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.55</v>
+        <v>0.82</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.62</v>
+        <v>0.96</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.98</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>1.13</v>
+        <v>0.83</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>1.12</v>
+        <v>0.62</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.54</v>
+        <v>0.45</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.54</v>
+        <v>1.06</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.43</v>
+        <v>0.74</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.91</v>
+        <v>0.58</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.49</v>
+        <v>0.78</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.74</v>
+        <v>0.62</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>1.15</v>
+        <v>0.75</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.71</v>
+        <v>0.84</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>1.14</v>
+        <v>0.67</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.45</v>
+        <v>0.98</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
@@ -3420,7 +3420,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>0.76</v>
+        <v>0.87</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
@@ -3461,7 +3461,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.71</v>
+        <v>1.11</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>1.11</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>0.83</v>
+        <v>0.7</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>1.08</v>
+        <v>0.95</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
@@ -3666,7 +3666,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.49</v>
+        <v>1.11</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0.51</v>
+        <v>1.08</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>1.12</v>
+        <v>0.82</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
@@ -3830,7 +3830,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
@@ -3912,7 +3912,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.64</v>
+        <v>0.45</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>1.03</v>
+        <v>0.75</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0.49</v>
+        <v>0.66</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>0.68</v>
+        <v>0.91</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.48</v>
+        <v>0.76</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.74</v>
+        <v>0.64</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.44</v>
+        <v>1.11</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
@@ -4322,7 +4322,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.86</v>
+        <v>0.66</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.42</v>
+        <v>0.75</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
@@ -4650,7 +4650,7 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
@@ -4691,7 +4691,7 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>1</v>
+        <v>0.61</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>0.46</v>
+        <v>1.03</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>0.9</v>
+        <v>1.08</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>0.98</v>
+        <v>1.01</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
@@ -4937,7 +4937,7 @@
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>0.47</v>
+        <v>1.1</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>1.15</v>
+        <v>0.6</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
@@ -5060,7 +5060,7 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
@@ -5101,7 +5101,7 @@
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.7</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
@@ -5183,7 +5183,7 @@
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>0.72</v>
+        <v>0.93</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>0.43</v>
+        <v>0.96</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>0.73</v>
+        <v>0.47</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>0.63</v>
+        <v>0.48</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
@@ -5470,7 +5470,7 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>0.47</v>
+        <v>1.06</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>0.77</v>
+        <v>1.08</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>0.66</v>
+        <v>0.5</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>0.72</v>
+        <v>0.93</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
@@ -5716,7 +5716,7 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>1.05</v>
+        <v>0.77</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>0.57</v>
+        <v>1.11</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>0.75</v>
+        <v>1.11</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>1.07</v>
+        <v>0.79</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>0.78</v>
+        <v>1.11</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
@@ -6044,7 +6044,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>0.44</v>
+        <v>0.75</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>0.78</v>
+        <v>1.03</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
@@ -6126,7 +6126,7 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
@@ -6167,7 +6167,7 @@
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>1.05</v>
+        <v>0.76</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.54</v>
+        <v>0.66</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
@@ -6249,7 +6249,7 @@
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
@@ -6331,7 +6331,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
@@ -6413,7 +6413,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.43</v>
+        <v>0.96</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
@@ -6454,7 +6454,7 @@
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>0.98</v>
+        <v>0.59</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>0.68</v>
+        <v>1.01</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
@@ -6536,7 +6536,7 @@
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>1.08</v>
+        <v>0.63</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>0.66</v>
+        <v>0.95</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
@@ -6659,7 +6659,7 @@
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
@@ -6700,7 +6700,7 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
@@ -6741,7 +6741,7 @@
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
@@ -6864,7 +6864,7 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>1.07</v>
+        <v>0.59</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>0.87</v>
+        <v>1.14</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>0.79</v>
+        <v>1.12</v>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
@@ -7192,7 +7192,7 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>1.11</v>
+        <v>0.43</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.71</v>
+        <v>0.91</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>0.75</v>
+        <v>0.43</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="G167" s="2" t="n">
-        <v>0.46</v>
+        <v>1.04</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>0.98</v>
+        <v>1.05</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>1.01</v>
+        <v>0.49</v>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
@@ -7438,7 +7438,7 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>0.48</v>
+        <v>0.73</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>0.54</v>
+        <v>0.89</v>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
@@ -7520,7 +7520,7 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         </is>
       </c>
       <c r="G173" s="2" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
@@ -7602,7 +7602,7 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>0.54</v>
+        <v>0.66</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
@@ -7643,7 +7643,7 @@
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
@@ -7684,7 +7684,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>0.89</v>
+        <v>0.57</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F177" s="3" t="inlineStr">
@@ -7725,7 +7725,7 @@
         </is>
       </c>
       <c r="G177" s="2" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>1.04</v>
+        <v>0.58</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="G179" s="2" t="n">
-        <v>0.74</v>
+        <v>0.51</v>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>0.43</v>
+        <v>1.11</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F181" s="3" t="inlineStr">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>0.6</v>
+        <v>0.86</v>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
@@ -7930,7 +7930,7 @@
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
@@ -7971,7 +7971,7 @@
         </is>
       </c>
       <c r="G183" s="2" t="n">
-        <v>0.55</v>
+        <v>0.83</v>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
@@ -8012,7 +8012,7 @@
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>0.87</v>
+        <v>0.93</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>0.97</v>
+        <v>1.06</v>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>0.43</v>
+        <v>0.82</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
@@ -8135,7 +8135,7 @@
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
@@ -8176,7 +8176,7 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>1.11</v>
+        <v>0.85</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>1.1</v>
+        <v>0.45</v>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>0.9</v>
+        <v>0.77</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>0.53</v>
+        <v>1.05</v>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F193" s="3" t="inlineStr">
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F194" s="3" t="inlineStr">
@@ -8422,7 +8422,7 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F195" s="3" t="inlineStr">
@@ -8463,7 +8463,7 @@
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
@@ -8586,7 +8586,7 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>0.68</v>
+        <v>0.95</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>0.7</v>
+        <v>0.89</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>0.74</v>
+        <v>0.67</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>0.59</v>
+        <v>0.73</v>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F203" s="3" t="inlineStr">
@@ -8791,7 +8791,7 @@
         </is>
       </c>
       <c r="G203" s="2" t="n">
-        <v>0.64</v>
+        <v>1.02</v>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
@@ -8832,7 +8832,7 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="G205" s="2" t="n">
-        <v>0.65</v>
+        <v>0.79</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
@@ -8914,7 +8914,7 @@
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="G207" s="2" t="n">
-        <v>0.44</v>
+        <v>0.66</v>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F208" s="3" t="inlineStr">
@@ -8996,7 +8996,7 @@
         </is>
       </c>
       <c r="G208" s="2" t="n">
-        <v>0.91</v>
+        <v>1.01</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F209" s="3" t="inlineStr">
@@ -9037,7 +9037,7 @@
         </is>
       </c>
       <c r="G209" s="2" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F210" s="3" t="inlineStr">
@@ -9078,7 +9078,7 @@
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>1.02</v>
+        <v>0.42</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F211" s="3" t="inlineStr">
@@ -9119,7 +9119,7 @@
         </is>
       </c>
       <c r="G211" s="2" t="n">
-        <v>0.59</v>
+        <v>1.07</v>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr">
@@ -9160,7 +9160,7 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>0.88</v>
+        <v>0.71</v>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
@@ -9201,7 +9201,7 @@
         </is>
       </c>
       <c r="G213" s="2" t="n">
-        <v>0.93</v>
+        <v>0.75</v>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr">
@@ -9242,7 +9242,7 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="G215" s="2" t="n">
-        <v>0.42</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F216" s="3" t="inlineStr">
@@ -9324,7 +9324,7 @@
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>1.1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F217" s="3" t="inlineStr">
@@ -9365,7 +9365,7 @@
         </is>
       </c>
       <c r="G217" s="2" t="n">
-        <v>0.43</v>
+        <v>0.83</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr">
@@ -9406,7 +9406,7 @@
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>0.75</v>
+        <v>1.02</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F219" s="3" t="inlineStr">
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="G219" s="2" t="n">
-        <v>1.11</v>
+        <v>0.48</v>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F220" s="3" t="inlineStr">
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F221" s="3" t="inlineStr">
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="G221" s="2" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F222" s="3" t="inlineStr">
@@ -9570,7 +9570,7 @@
         </is>
       </c>
       <c r="G222" s="2" t="n">
-        <v>1</v>
+        <v>0.48</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F223" s="3" t="inlineStr">
@@ -9611,7 +9611,7 @@
         </is>
       </c>
       <c r="G223" s="2" t="n">
-        <v>0.62</v>
+        <v>1.07</v>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F224" s="3" t="inlineStr">
@@ -9652,7 +9652,7 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F225" s="3" t="inlineStr">
@@ -9693,7 +9693,7 @@
         </is>
       </c>
       <c r="G225" s="2" t="n">
-        <v>0.91</v>
+        <v>1.01</v>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F226" s="3" t="inlineStr">
@@ -9734,7 +9734,7 @@
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F227" s="3" t="inlineStr">
@@ -9775,7 +9775,7 @@
         </is>
       </c>
       <c r="G227" s="2" t="n">
-        <v>0.42</v>
+        <v>0.66</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F228" s="3" t="inlineStr">
@@ -9816,7 +9816,7 @@
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F229" s="3" t="inlineStr">
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="G229" s="2" t="n">
-        <v>0.6</v>
+        <v>0.46</v>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr">
@@ -9898,7 +9898,7 @@
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F231" s="3" t="inlineStr">
@@ -9939,7 +9939,7 @@
         </is>
       </c>
       <c r="G231" s="2" t="n">
-        <v>0.52</v>
+        <v>1.05</v>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         </is>
       </c>
       <c r="G232" s="2" t="n">
-        <v>0.74</v>
+        <v>0.68</v>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F233" s="3" t="inlineStr">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F234" s="3" t="inlineStr">
@@ -10062,7 +10062,7 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>0.59</v>
+        <v>1.11</v>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F235" s="3" t="inlineStr">
@@ -10103,7 +10103,7 @@
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>0.84</v>
+        <v>1.13</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F236" s="3" t="inlineStr">
@@ -10144,7 +10144,7 @@
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>0.84</v>
+        <v>1.15</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F237" s="3" t="inlineStr">
@@ -10185,7 +10185,7 @@
         </is>
       </c>
       <c r="G237" s="2" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F238" s="3" t="inlineStr">
@@ -10226,7 +10226,7 @@
         </is>
       </c>
       <c r="G238" s="2" t="n">
-        <v>0.54</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
@@ -10299,7 +10299,7 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F240" s="3" t="inlineStr">
@@ -10308,7 +10308,7 @@
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>1.07</v>
+        <v>0.7</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -10349,7 +10349,7 @@
         </is>
       </c>
       <c r="G241" s="2" t="n">
-        <v>0.97</v>
+        <v>1.02</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>1.11</v>
+        <v>0.44</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         </is>
       </c>
       <c r="G243" s="2" t="n">
-        <v>0.52</v>
+        <v>0.44</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F244" s="3" t="inlineStr">
@@ -10472,7 +10472,7 @@
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F245" s="3" t="inlineStr">
@@ -10513,7 +10513,7 @@
         </is>
       </c>
       <c r="G245" s="2" t="n">
-        <v>1.07</v>
+        <v>0.59</v>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F246" s="3" t="inlineStr">
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>0.52</v>
+        <v>0.92</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         </is>
       </c>
       <c r="G247" s="2" t="n">
-        <v>0.76</v>
+        <v>1.06</v>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>0.44</v>
+        <v>0.48</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         </is>
       </c>
       <c r="G249" s="2" t="n">
-        <v>0.44</v>
+        <v>0.65</v>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>1.08</v>
+        <v>0.45</v>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F251" s="3" t="inlineStr">
@@ -10759,7 +10759,7 @@
         </is>
       </c>
       <c r="G251" s="2" t="n">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F252" s="3" t="inlineStr">
@@ -10800,7 +10800,7 @@
         </is>
       </c>
       <c r="G252" s="2" t="n">
-        <v>1.14</v>
+        <v>0.86</v>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F253" s="3" t="inlineStr">
@@ -10841,7 +10841,7 @@
         </is>
       </c>
       <c r="G253" s="2" t="n">
-        <v>0.84</v>
+        <v>1.06</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F254" s="3" t="inlineStr">
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>1.08</v>
+        <v>0.91</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F255" s="3" t="inlineStr">
@@ -10923,7 +10923,7 @@
         </is>
       </c>
       <c r="G255" s="2" t="n">
-        <v>0.89</v>
+        <v>0.74</v>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F256" s="3" t="inlineStr">
@@ -10964,7 +10964,7 @@
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>0.61</v>
+        <v>0.75</v>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         </is>
       </c>
       <c r="G257" s="2" t="n">
-        <v>0.46</v>
+        <v>0.71</v>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F258" s="3" t="inlineStr">
@@ -11046,7 +11046,7 @@
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>1.13</v>
+        <v>0.46</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F259" s="3" t="inlineStr">
@@ -11087,7 +11087,7 @@
         </is>
       </c>
       <c r="G259" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.09</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F260" s="3" t="inlineStr">
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>0.8</v>
+        <v>1.07</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         </is>
       </c>
       <c r="G261" s="2" t="n">
-        <v>0.49</v>
+        <v>1.15</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F263" s="3" t="inlineStr">
@@ -11251,7 +11251,7 @@
         </is>
       </c>
       <c r="G263" s="2" t="n">
-        <v>0.99</v>
+        <v>0.78</v>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F264" s="3" t="inlineStr">
@@ -11292,7 +11292,7 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0.52</v>
+        <v>0.44</v>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F265" s="3" t="inlineStr">
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="G265" s="2" t="n">
-        <v>1.1</v>
+        <v>0.87</v>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F266" s="3" t="inlineStr">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>0.77</v>
+        <v>1.13</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F267" s="3" t="inlineStr">
@@ -11415,7 +11415,7 @@
         </is>
       </c>
       <c r="G267" s="2" t="n">
-        <v>0.44</v>
+        <v>0.95</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F268" s="3" t="inlineStr">
@@ -11456,7 +11456,7 @@
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>0.86</v>
+        <v>0.92</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F269" s="3" t="inlineStr">
@@ -11497,7 +11497,7 @@
         </is>
       </c>
       <c r="G269" s="2" t="n">
-        <v>0.48</v>
+        <v>0.88</v>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
@@ -11538,7 +11538,7 @@
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F271" s="3" t="inlineStr">
@@ -11579,7 +11579,7 @@
         </is>
       </c>
       <c r="G271" s="2" t="n">
-        <v>0.6</v>
+        <v>1.11</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F272" s="3" t="inlineStr">
@@ -11620,7 +11620,7 @@
         </is>
       </c>
       <c r="G272" s="2" t="n">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         </is>
       </c>
       <c r="G273" s="2" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F274" s="3" t="inlineStr">
@@ -11702,7 +11702,7 @@
         </is>
       </c>
       <c r="G274" s="2" t="n">
-        <v>1.11</v>
+        <v>0.72</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F275" s="3" t="inlineStr">
@@ -11743,7 +11743,7 @@
         </is>
       </c>
       <c r="G275" s="2" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F276" s="3" t="inlineStr">
@@ -11784,7 +11784,7 @@
         </is>
       </c>
       <c r="G276" s="2" t="n">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         </is>
       </c>
       <c r="G277" s="2" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr">
@@ -11866,7 +11866,7 @@
         </is>
       </c>
       <c r="G278" s="2" t="n">
-        <v>0.87</v>
+        <v>0.5</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F279" s="3" t="inlineStr">
@@ -11907,7 +11907,7 @@
         </is>
       </c>
       <c r="G279" s="2" t="n">
-        <v>1.1</v>
+        <v>0.66</v>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr">
@@ -11948,7 +11948,7 @@
         </is>
       </c>
       <c r="G280" s="2" t="n">
-        <v>0.74</v>
+        <v>0.95</v>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
@@ -11980,7 +11980,7 @@
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F281" s="3" t="inlineStr">
@@ -11989,7 +11989,7 @@
         </is>
       </c>
       <c r="G281" s="2" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F282" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>0.66</v>
+        <v>0.79</v>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F283" s="3" t="inlineStr">
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.49</v>
+        <v>0.72</v>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         </is>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F285" s="3" t="inlineStr">
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="G285" s="2" t="n">
-        <v>0.82</v>
+        <v>0.67</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F286" s="3" t="inlineStr">
@@ -12194,7 +12194,7 @@
         </is>
       </c>
       <c r="G286" s="2" t="n">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         </is>
       </c>
       <c r="G287" s="2" t="n">
-        <v>0.88</v>
+        <v>0.57</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         </is>
       </c>
       <c r="G288" s="2" t="n">
-        <v>0.6</v>
+        <v>0.98</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F289" s="3" t="inlineStr">
@@ -12317,7 +12317,7 @@
         </is>
       </c>
       <c r="G289" s="2" t="n">
-        <v>0.96</v>
+        <v>0.43</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F290" s="3" t="inlineStr">
@@ -12358,7 +12358,7 @@
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>1.15</v>
+        <v>0.5</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F291" s="3" t="inlineStr">
@@ -12399,7 +12399,7 @@
         </is>
       </c>
       <c r="G291" s="2" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F292" s="3" t="inlineStr">
@@ -12440,7 +12440,7 @@
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>0.55</v>
+        <v>0.85</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F293" s="3" t="inlineStr">
@@ -12481,7 +12481,7 @@
         </is>
       </c>
       <c r="G293" s="2" t="n">
-        <v>1.11</v>
+        <v>0.58</v>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F294" s="3" t="inlineStr">
@@ -12522,7 +12522,7 @@
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>0.61</v>
+        <v>0.82</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F295" s="3" t="inlineStr">
@@ -12563,7 +12563,7 @@
         </is>
       </c>
       <c r="G295" s="2" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>0.49</v>
+        <v>0.54</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F297" s="3" t="inlineStr">
@@ -12645,7 +12645,7 @@
         </is>
       </c>
       <c r="G297" s="2" t="n">
-        <v>0.57</v>
+        <v>0.52</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F298" s="3" t="inlineStr">
@@ -12686,7 +12686,7 @@
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>0.63</v>
+        <v>0.87</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         </is>
       </c>
       <c r="G299" s="2" t="n">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F300" s="3" t="inlineStr">
@@ -12768,7 +12768,7 @@
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>0.71</v>
+        <v>0.47</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F301" s="3" t="inlineStr">
@@ -12809,7 +12809,7 @@
         </is>
       </c>
       <c r="G301" s="2" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -12911,7 +12911,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1.03</v>
+        <v>0.88</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.7</v>
+        <v>0.51</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -12993,7 +12993,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.82</v>
+        <v>0.55</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -13034,7 +13034,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.08</v>
+        <v>0.47</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -13116,7 +13116,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.88</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -13157,7 +13157,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.61</v>
+        <v>0.84</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -13198,7 +13198,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -13239,7 +13239,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.75</v>
+        <v>1.14</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -13280,7 +13280,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.46</v>
+        <v>0.79</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.74</v>
+        <v>0.97</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -13362,7 +13362,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -13435,7 +13435,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -13444,7 +13444,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.46</v>
+        <v>0.71</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -13526,7 +13526,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.65</v>
+        <v>1.01</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -13567,7 +13567,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.86</v>
+        <v>1.1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.46</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -13649,7 +13649,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1.08</v>
+        <v>0.43</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -13690,7 +13690,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -13731,7 +13731,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.43</v>
+        <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -13772,7 +13772,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1.1</v>
+        <v>0.76</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -13813,7 +13813,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.79</v>
+        <v>0.49</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -13854,7 +13854,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -13895,7 +13895,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -13927,7 +13927,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -13936,7 +13936,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.45</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -13977,7 +13977,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -14018,7 +14018,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.87</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -14059,7 +14059,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1.05</v>
+        <v>0.47</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -14100,7 +14100,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.8</v>
+        <v>1.02</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -14141,7 +14141,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.55</v>
+        <v>1.14</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -14182,7 +14182,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1.1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.45</v>
+        <v>1.12</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -14264,7 +14264,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0.9</v>
+        <v>0.55</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -14305,7 +14305,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.77</v>
+        <v>0.92</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -14346,7 +14346,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.98</v>
+        <v>0.7</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -14387,7 +14387,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.55</v>
+        <v>0.96</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1.11</v>
+        <v>0.66</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -14469,7 +14469,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.89</v>
+        <v>0.62</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -14510,7 +14510,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.54</v>
+        <v>0.8</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.83</v>
+        <v>0.66</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -14592,7 +14592,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.58</v>
+        <v>0.82</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -14674,7 +14674,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -14706,7 +14706,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -14715,7 +14715,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -14756,7 +14756,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.89</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -14797,7 +14797,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.99</v>
+        <v>0.89</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -14838,7 +14838,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1.02</v>
+        <v>0.79</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -14879,7 +14879,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1.04</v>
+        <v>0.47</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -14920,7 +14920,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0.47</v>
+        <v>1.01</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -14961,7 +14961,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -15002,7 +15002,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0.76</v>
+        <v>1.06</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.55</v>
+        <v>0.82</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -15084,7 +15084,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0.62</v>
+        <v>0.96</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -15125,7 +15125,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0.98</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -15166,7 +15166,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1.13</v>
+        <v>0.83</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -15198,7 +15198,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -15207,7 +15207,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1.12</v>
+        <v>0.62</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -15248,7 +15248,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -15289,7 +15289,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.54</v>
+        <v>0.45</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0.54</v>
+        <v>1.06</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -15371,7 +15371,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.43</v>
+        <v>0.74</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -15412,7 +15412,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.91</v>
+        <v>0.58</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0.49</v>
+        <v>0.78</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -15535,7 +15535,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.74</v>
+        <v>0.62</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>1.15</v>
+        <v>0.75</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -15617,7 +15617,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0.71</v>
+        <v>0.84</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -15658,7 +15658,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -15699,7 +15699,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>1.14</v>
+        <v>0.67</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -15740,7 +15740,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.45</v>
+        <v>0.98</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -15772,7 +15772,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -15781,7 +15781,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.76</v>
+        <v>0.87</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -15813,7 +15813,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -15822,7 +15822,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0.71</v>
+        <v>1.11</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>1.11</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.83</v>
+        <v>0.7</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>1.08</v>
+        <v>0.95</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15986,7 +15986,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.49</v>
+        <v>1.11</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -16068,7 +16068,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0.51</v>
+        <v>1.08</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -16109,7 +16109,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -16150,7 +16150,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>1.12</v>
+        <v>0.82</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -16182,7 +16182,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -16191,7 +16191,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16232,7 +16232,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16273,7 +16273,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.64</v>
+        <v>0.45</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16314,7 +16314,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>1.03</v>
+        <v>0.75</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16355,7 +16355,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>0.49</v>
+        <v>0.66</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>0.68</v>
+        <v>0.91</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>0.48</v>
+        <v>0.76</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -16519,7 +16519,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -16560,7 +16560,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>0.74</v>
+        <v>0.64</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -16601,7 +16601,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -16642,7 +16642,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>0.44</v>
+        <v>1.11</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -16683,7 +16683,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>0.86</v>
+        <v>0.66</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -16724,7 +16724,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -16806,7 +16806,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -16847,7 +16847,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -16888,7 +16888,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -16929,7 +16929,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>0.42</v>
+        <v>0.75</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -16970,7 +16970,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -17011,7 +17011,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -17052,7 +17052,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -17093,7 +17093,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>1</v>
+        <v>0.61</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -17134,7 +17134,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>0.46</v>
+        <v>1.03</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -17175,7 +17175,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>0.9</v>
+        <v>1.08</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -17216,7 +17216,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -17257,7 +17257,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>0.98</v>
+        <v>1.01</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -17298,7 +17298,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>0.47</v>
+        <v>1.1</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -17339,7 +17339,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -17380,7 +17380,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>1.15</v>
+        <v>0.6</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -17421,7 +17421,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -17462,7 +17462,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>0.7</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -17544,7 +17544,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>0.72</v>
+        <v>0.93</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -17585,7 +17585,7 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -17626,7 +17626,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -17667,7 +17667,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -17708,7 +17708,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>0.43</v>
+        <v>0.96</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -17749,7 +17749,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>0.73</v>
+        <v>0.47</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -17790,7 +17790,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>0.63</v>
+        <v>0.48</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -17831,7 +17831,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -17872,7 +17872,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>0.47</v>
+        <v>1.06</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0.77</v>
+        <v>1.08</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>0.66</v>
+        <v>0.5</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -17995,7 +17995,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -18036,7 +18036,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>0.72</v>
+        <v>0.93</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -18077,7 +18077,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>1.05</v>
+        <v>0.77</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -18118,7 +18118,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>0.57</v>
+        <v>1.11</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -18159,7 +18159,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>0.75</v>
+        <v>1.11</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -18200,7 +18200,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -18241,7 +18241,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -18282,7 +18282,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>1.07</v>
+        <v>0.79</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -18323,7 +18323,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>0.78</v>
+        <v>1.11</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -18405,7 +18405,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>0.44</v>
+        <v>0.75</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>0.78</v>
+        <v>1.03</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -18487,7 +18487,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -18528,7 +18528,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>1.05</v>
+        <v>0.76</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>0.54</v>
+        <v>0.66</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -18610,7 +18610,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -18692,7 +18692,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -18774,7 +18774,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>0.43</v>
+        <v>0.96</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -18815,7 +18815,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>0.98</v>
+        <v>0.59</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -18856,7 +18856,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>0.68</v>
+        <v>1.01</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -18897,7 +18897,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>1.08</v>
+        <v>0.63</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -18938,7 +18938,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>0.66</v>
+        <v>0.95</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -19020,7 +19020,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -19061,7 +19061,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -19102,7 +19102,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -19184,7 +19184,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -19225,7 +19225,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>1.07</v>
+        <v>0.59</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -19266,7 +19266,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>0.87</v>
+        <v>1.14</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -19380,7 +19380,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -19389,7 +19389,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -19430,7 +19430,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>0.79</v>
+        <v>1.12</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -19471,7 +19471,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -19553,7 +19553,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>1.11</v>
+        <v>0.43</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>0.71</v>
+        <v>0.91</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -19635,7 +19635,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>0.75</v>
+        <v>0.43</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -19676,7 +19676,7 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>0.46</v>
+        <v>1.04</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -19717,7 +19717,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>0.98</v>
+        <v>1.05</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -19758,7 +19758,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>1.01</v>
+        <v>0.49</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -19799,7 +19799,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>0.48</v>
+        <v>0.73</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -19840,7 +19840,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>0.54</v>
+        <v>0.89</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -19881,7 +19881,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -19963,7 +19963,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>0.54</v>
+        <v>0.66</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -20004,7 +20004,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -20045,7 +20045,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>0.89</v>
+        <v>0.57</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -20086,7 +20086,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -20127,7 +20127,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>1.04</v>
+        <v>0.58</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -20168,7 +20168,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>0.74</v>
+        <v>0.51</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>0.43</v>
+        <v>1.11</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>0.6</v>
+        <v>0.86</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -20291,7 +20291,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -20332,7 +20332,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>0.55</v>
+        <v>0.83</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -20373,7 +20373,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>0.87</v>
+        <v>0.93</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>0.97</v>
+        <v>1.06</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>0.43</v>
+        <v>0.82</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -20496,7 +20496,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -20537,7 +20537,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>1.11</v>
+        <v>0.85</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -20578,7 +20578,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>1.1</v>
+        <v>0.45</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>0.9</v>
+        <v>0.77</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>0.53</v>
+        <v>1.05</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -20742,7 +20742,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -20774,7 +20774,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -20783,7 +20783,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -20824,7 +20824,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -20906,7 +20906,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>0.68</v>
+        <v>0.95</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>0.7</v>
+        <v>0.89</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -21029,7 +21029,7 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -21070,7 +21070,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>0.74</v>
+        <v>0.67</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>0.59</v>
+        <v>0.73</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -21152,7 +21152,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>0.64</v>
+        <v>1.02</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -21193,7 +21193,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>0.65</v>
+        <v>0.79</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -21275,7 +21275,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -21316,7 +21316,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>0.44</v>
+        <v>0.66</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -21357,7 +21357,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>0.91</v>
+        <v>1.01</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -21398,7 +21398,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -21439,7 +21439,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>1.02</v>
+        <v>0.42</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -21471,7 +21471,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -21480,7 +21480,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>0.59</v>
+        <v>1.07</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -21521,7 +21521,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>0.88</v>
+        <v>0.71</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -21562,7 +21562,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>0.93</v>
+        <v>0.75</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -21603,7 +21603,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -21644,7 +21644,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>0.42</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -21685,7 +21685,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>1.1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -21726,7 +21726,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>0.43</v>
+        <v>0.83</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -21767,7 +21767,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>0.75</v>
+        <v>1.02</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -21799,7 +21799,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>1.11</v>
+        <v>0.48</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -21849,7 +21849,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -21890,7 +21890,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -21931,7 +21931,7 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>1</v>
+        <v>0.48</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -21972,7 +21972,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>0.62</v>
+        <v>1.07</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -22013,7 +22013,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -22054,7 +22054,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>0.91</v>
+        <v>1.01</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -22095,7 +22095,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -22136,7 +22136,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>0.42</v>
+        <v>0.66</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -22177,7 +22177,7 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -22209,7 +22209,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -22218,7 +22218,7 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>0.6</v>
+        <v>0.46</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -22259,7 +22259,7 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -22300,7 +22300,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>0.52</v>
+        <v>1.05</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>0.74</v>
+        <v>0.68</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -22382,7 +22382,7 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -22423,7 +22423,7 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>0.59</v>
+        <v>1.11</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -22464,7 +22464,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>0.84</v>
+        <v>1.13</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -22505,7 +22505,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>0.84</v>
+        <v>1.15</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -22546,7 +22546,7 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -22587,7 +22587,7 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>0.54</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -22628,7 +22628,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -22669,7 +22669,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>1.07</v>
+        <v>0.7</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -22710,7 +22710,7 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>0.97</v>
+        <v>1.02</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -22742,7 +22742,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -22751,7 +22751,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>1.11</v>
+        <v>0.44</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -22792,7 +22792,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>0.52</v>
+        <v>0.44</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -22833,7 +22833,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -22865,7 +22865,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -22874,7 +22874,7 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>1.07</v>
+        <v>0.59</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -22915,7 +22915,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>0.52</v>
+        <v>0.92</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>0.76</v>
+        <v>1.06</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>0.44</v>
+        <v>0.48</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -23038,7 +23038,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>0.44</v>
+        <v>0.65</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -23079,7 +23079,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>1.08</v>
+        <v>0.45</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -23120,7 +23120,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -23152,7 +23152,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -23161,7 +23161,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>1.14</v>
+        <v>0.86</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -23202,7 +23202,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>0.84</v>
+        <v>1.06</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -23243,7 +23243,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>1.08</v>
+        <v>0.91</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -23284,7 +23284,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>0.89</v>
+        <v>0.74</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -23325,7 +23325,7 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>0.61</v>
+        <v>0.75</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>0.46</v>
+        <v>0.71</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -23407,7 +23407,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>1.13</v>
+        <v>0.46</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -23448,7 +23448,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.09</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -23489,7 +23489,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>0.8</v>
+        <v>1.07</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>0.49</v>
+        <v>1.15</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -23603,7 +23603,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -23612,7 +23612,7 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>0.99</v>
+        <v>0.78</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -23653,7 +23653,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>0.52</v>
+        <v>0.44</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -23694,7 +23694,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>1.1</v>
+        <v>0.87</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -23735,7 +23735,7 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>0.77</v>
+        <v>1.13</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -23776,7 +23776,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>0.44</v>
+        <v>0.95</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -23817,7 +23817,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>0.86</v>
+        <v>0.92</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -23849,7 +23849,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -23858,7 +23858,7 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>0.48</v>
+        <v>0.88</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -23899,7 +23899,7 @@
         </is>
       </c>
       <c r="G270" t="n">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -23940,7 +23940,7 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>0.6</v>
+        <v>1.11</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -23981,7 +23981,7 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -24063,7 +24063,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>1.11</v>
+        <v>0.72</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -24104,7 +24104,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -24145,7 +24145,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -24227,7 +24227,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>0.87</v>
+        <v>0.5</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -24268,7 +24268,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>1.1</v>
+        <v>0.66</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -24309,7 +24309,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>0.74</v>
+        <v>0.95</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -24350,7 +24350,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -24391,7 +24391,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>0.66</v>
+        <v>0.79</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>0.49</v>
+        <v>0.72</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -24473,7 +24473,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -24514,7 +24514,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>0.82</v>
+        <v>0.67</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -24546,7 +24546,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -24555,7 +24555,7 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -24596,7 +24596,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>0.88</v>
+        <v>0.57</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>0.6</v>
+        <v>0.98</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -24678,7 +24678,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>0.96</v>
+        <v>0.43</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -24710,7 +24710,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -24719,7 +24719,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>1.15</v>
+        <v>0.5</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -24760,7 +24760,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -24801,7 +24801,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>0.55</v>
+        <v>0.85</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -24833,7 +24833,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -24842,7 +24842,7 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>1.11</v>
+        <v>0.58</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -24883,7 +24883,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>0.61</v>
+        <v>0.82</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -24924,7 +24924,7 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>0.49</v>
+        <v>0.54</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -25006,7 +25006,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>0.57</v>
+        <v>0.52</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -25047,7 +25047,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>0.63</v>
+        <v>0.87</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -25129,7 +25129,7 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>0.71</v>
+        <v>0.47</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -25170,7 +25170,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>

--- a/reports/Web_Application_Selenium_Test_Report.xlsx
+++ b/reports/Web_Application_Selenium_Test_Report.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.88</v>
+        <v>0.79</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -582,7 +582,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.51</v>
+        <v>1.07</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.47</v>
+        <v>0.83</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.14</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.84</v>
+        <v>1.08</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.64</v>
+        <v>1.02</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1.14</v>
+        <v>0.64</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.97</v>
+        <v>0.6</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1.06</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.71</v>
+        <v>0.84</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.45</v>
+        <v>1.11</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>1.01</v>
+        <v>0.72</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.71</v>
+        <v>0.51</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.76</v>
+        <v>1.06</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.49</v>
+        <v>0.73</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.87</v>
+        <v>0.78</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.71</v>
+        <v>0.79</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.57</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.47</v>
+        <v>0.89</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>1.14</v>
+        <v>0.61</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>1.12</v>
+        <v>0.73</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.55</v>
+        <v>1.11</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.92</v>
+        <v>0.65</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.7</v>
+        <v>1.08</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.66</v>
+        <v>0.72</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.62</v>
+        <v>0.49</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.82</v>
+        <v>1.1</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -2272,7 +2272,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.84</v>
+        <v>0.99</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.75</v>
+        <v>0.98</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.89</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.47</v>
+        <v>0.77</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>1.11</v>
+        <v>0.97</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>1.06</v>
+        <v>0.72</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.82</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.96</v>
+        <v>0.9</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -2764,7 +2764,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.83</v>
+        <v>0.63</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.62</v>
+        <v>1</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.43</v>
+        <v>0.73</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.45</v>
+        <v>0.73</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -2969,7 +2969,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.74</v>
+        <v>0.88</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.58</v>
+        <v>0.44</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.78</v>
+        <v>1.13</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.44</v>
+        <v>1.06</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.75</v>
+        <v>0.46</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.89</v>
+        <v>0.63</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.67</v>
+        <v>0.98</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
@@ -3420,7 +3420,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>0.87</v>
+        <v>1.15</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>1.11</v>
+        <v>0.97</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
@@ -3502,7 +3502,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0.95</v>
+        <v>1.06</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.92</v>
+        <v>0.87</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
@@ -3666,7 +3666,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>1.11</v>
+        <v>0.64</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.62</v>
+        <v>1.01</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.82</v>
+        <v>0.97</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
@@ -3830,7 +3830,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>1.13</v>
+        <v>0.47</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>1.04</v>
+        <v>0.93</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
@@ -3912,7 +3912,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0.66</v>
+        <v>1.03</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>0.91</v>
+        <v>0.76</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.76</v>
+        <v>0.63</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.65</v>
+        <v>0.48</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.64</v>
+        <v>0.84</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>0.98</v>
+        <v>0.7</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
@@ -4322,7 +4322,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.66</v>
+        <v>0.44</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0.65</v>
+        <v>1.13</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.7</v>
+        <v>0.89</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>0.52</v>
+        <v>1.01</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
@@ -4486,7 +4486,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>1.06</v>
+        <v>0.67</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.43</v>
+        <v>0.91</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>1.14</v>
+        <v>0.54</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
@@ -4691,7 +4691,7 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.76</v>
+        <v>0.99</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>1.03</v>
+        <v>0.79</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>0.65</v>
+        <v>1.14</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>1.01</v>
+        <v>0.66</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
@@ -4937,7 +4937,7 @@
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>1.1</v>
+        <v>0.88</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>0.64</v>
+        <v>0.51</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
@@ -5060,7 +5060,7 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>0.68</v>
+        <v>0.44</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
@@ -5142,7 +5142,7 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0.71</v>
+        <v>1.1</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>0.83</v>
+        <v>0.7</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0.46</v>
+        <v>0.8</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0.57</v>
+        <v>0.51</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>0.47</v>
+        <v>1.02</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>0.48</v>
+        <v>1.01</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>0.97</v>
+        <v>0.48</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>0.5</v>
+        <v>0.77</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>0.93</v>
+        <v>0.73</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
@@ -5716,7 +5716,7 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>0.77</v>
+        <v>0.9</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>1.11</v>
+        <v>0.96</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>1.11</v>
+        <v>0.51</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>1.02</v>
+        <v>0.76</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>1.01</v>
+        <v>0.66</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>0.79</v>
+        <v>1.06</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>1.11</v>
+        <v>0.75</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>0.89</v>
+        <v>0.77</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
@@ -6044,7 +6044,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>1.03</v>
+        <v>0.73</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
@@ -6126,7 +6126,7 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>0.75</v>
+        <v>1.09</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>0.76</v>
+        <v>0.42</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
@@ -6208,7 +6208,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.66</v>
+        <v>0.52</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
@@ -6249,7 +6249,7 @@
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>0.6</v>
+        <v>0.92</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0.89</v>
+        <v>0.48</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>1.1</v>
+        <v>0.92</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>1.06</v>
+        <v>0.88</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>1.01</v>
+        <v>0.55</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
@@ -6536,7 +6536,7 @@
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>0.63</v>
+        <v>1.04</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>1.06</v>
+        <v>0.7</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
@@ -6618,7 +6618,7 @@
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>0.97</v>
+        <v>1.03</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
@@ -6700,7 +6700,7 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
@@ -6782,7 +6782,7 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
@@ -6864,7 +6864,7 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>0.59</v>
+        <v>1.01</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
@@ -6946,7 +6946,7 @@
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>0.93</v>
+        <v>1.08</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
@@ -6987,7 +6987,7 @@
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>0.63</v>
+        <v>0.49</v>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>1.12</v>
+        <v>0.97</v>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
@@ -7110,7 +7110,7 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
@@ -7151,7 +7151,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>1</v>
+        <v>0.51</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>0.43</v>
+        <v>1.08</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="G167" s="2" t="n">
-        <v>1.04</v>
+        <v>0.77</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>1.05</v>
+        <v>0.95</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
@@ -7438,7 +7438,7 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>0.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>0.89</v>
+        <v>1.13</v>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
@@ -7520,7 +7520,7 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>1.13</v>
+        <v>0.57</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
@@ -7561,7 +7561,7 @@
         </is>
       </c>
       <c r="G173" s="2" t="n">
-        <v>0.64</v>
+        <v>0.99</v>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
@@ -7602,7 +7602,7 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>0.66</v>
+        <v>0.42</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
@@ -7643,7 +7643,7 @@
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
@@ -7684,7 +7684,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         </is>
       </c>
       <c r="G177" s="2" t="n">
-        <v>0.58</v>
+        <v>0.48</v>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
@@ -7766,7 +7766,7 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>0.58</v>
+        <v>0.98</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="G179" s="2" t="n">
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
@@ -7848,7 +7848,7 @@
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>1.11</v>
+        <v>0.5</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F181" s="3" t="inlineStr">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>0.86</v>
+        <v>0.64</v>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
@@ -7930,7 +7930,7 @@
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>0.63</v>
+        <v>0.96</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         </is>
       </c>
       <c r="G183" s="2" t="n">
-        <v>0.83</v>
+        <v>0.43</v>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
@@ -8012,7 +8012,7 @@
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>0.93</v>
+        <v>0.57</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
@@ -8053,7 +8053,7 @@
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>1.06</v>
+        <v>0.88</v>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>0.75</v>
+        <v>0.46</v>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>0.45</v>
+        <v>1.07</v>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
@@ -8258,7 +8258,7 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>1.12</v>
+        <v>0.89</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>0.67</v>
+        <v>0.76</v>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F195" s="3" t="inlineStr">
@@ -8463,7 +8463,7 @@
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F196" s="3" t="inlineStr">
@@ -8504,7 +8504,7 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>0.7</v>
+        <v>0.95</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>0.66</v>
+        <v>0.8</v>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
@@ -8586,7 +8586,7 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>0.95</v>
+        <v>0.59</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F199" s="3" t="inlineStr">
@@ -8627,7 +8627,7 @@
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>0.89</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>0.89</v>
+        <v>0.64</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F201" s="3" t="inlineStr">
@@ -8709,7 +8709,7 @@
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
@@ -8750,7 +8750,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>0.73</v>
+        <v>1.01</v>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F203" s="3" t="inlineStr">
@@ -8791,7 +8791,7 @@
         </is>
       </c>
       <c r="G203" s="2" t="n">
-        <v>1.02</v>
+        <v>0.66</v>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr">
@@ -8832,7 +8832,7 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>0.91</v>
+        <v>1.05</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F205" s="3" t="inlineStr">
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="G205" s="2" t="n">
-        <v>0.79</v>
+        <v>1.06</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
@@ -8914,7 +8914,7 @@
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>0.6</v>
+        <v>0.54</v>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F207" s="3" t="inlineStr">
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="G207" s="2" t="n">
-        <v>0.66</v>
+        <v>0.55</v>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F208" s="3" t="inlineStr">
@@ -8996,7 +8996,7 @@
         </is>
       </c>
       <c r="G208" s="2" t="n">
-        <v>1.01</v>
+        <v>0.79</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         </is>
       </c>
       <c r="G209" s="2" t="n">
-        <v>0.93</v>
+        <v>0.51</v>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>0.42</v>
+        <v>1.12</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F211" s="3" t="inlineStr">
@@ -9119,7 +9119,7 @@
         </is>
       </c>
       <c r="G211" s="2" t="n">
-        <v>1.07</v>
+        <v>0.82</v>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr">
@@ -9160,7 +9160,7 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>0.71</v>
+        <v>0.82</v>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
@@ -9201,7 +9201,7 @@
         </is>
       </c>
       <c r="G213" s="2" t="n">
-        <v>0.75</v>
+        <v>1.06</v>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr">
@@ -9242,7 +9242,7 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>0.67</v>
+        <v>0.48</v>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F215" s="3" t="inlineStr">
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="G215" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.54</v>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         </is>
       </c>
       <c r="G217" s="2" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr">
@@ -9406,7 +9406,7 @@
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>1.02</v>
+        <v>0.85</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="G219" s="2" t="n">
-        <v>0.48</v>
+        <v>0.57</v>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F220" s="3" t="inlineStr">
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F221" s="3" t="inlineStr">
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="G221" s="2" t="n">
-        <v>1.07</v>
+        <v>0.51</v>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F222" s="3" t="inlineStr">
@@ -9570,7 +9570,7 @@
         </is>
       </c>
       <c r="G222" s="2" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F223" s="3" t="inlineStr">
@@ -9611,7 +9611,7 @@
         </is>
       </c>
       <c r="G223" s="2" t="n">
-        <v>1.07</v>
+        <v>0.92</v>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F225" s="3" t="inlineStr">
@@ -9693,7 +9693,7 @@
         </is>
       </c>
       <c r="G225" s="2" t="n">
-        <v>1.01</v>
+        <v>0.59</v>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>0.74</v>
+        <v>0.64</v>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         </is>
       </c>
       <c r="G227" s="2" t="n">
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>1.11</v>
+        <v>0.73</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F229" s="3" t="inlineStr">
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="G229" s="2" t="n">
-        <v>0.46</v>
+        <v>1.02</v>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr">
@@ -9898,7 +9898,7 @@
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>0.47</v>
+        <v>0.92</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         </is>
       </c>
       <c r="G231" s="2" t="n">
-        <v>1.05</v>
+        <v>0.84</v>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F232" s="3" t="inlineStr">
@@ -9980,7 +9980,7 @@
         </is>
       </c>
       <c r="G232" s="2" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F233" s="3" t="inlineStr">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>1.05</v>
+        <v>0.48</v>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F234" s="3" t="inlineStr">
@@ -10062,7 +10062,7 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>1.11</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>1.13</v>
+        <v>0.52</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F236" s="3" t="inlineStr">
@@ -10144,7 +10144,7 @@
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>1.15</v>
+        <v>0.58</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F238" s="3" t="inlineStr">
@@ -10226,7 +10226,7 @@
         </is>
       </c>
       <c r="G238" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
@@ -10299,7 +10299,7 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F240" s="3" t="inlineStr">
@@ -10308,7 +10308,7 @@
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>0.7</v>
+        <v>0.47</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F241" s="3" t="inlineStr">
@@ -10349,7 +10349,7 @@
         </is>
       </c>
       <c r="G241" s="2" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         </is>
       </c>
       <c r="G245" s="2" t="n">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F246" s="3" t="inlineStr">
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>0.92</v>
+        <v>0.52</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         </is>
       </c>
       <c r="G247" s="2" t="n">
-        <v>1.06</v>
+        <v>0.92</v>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F248" s="3" t="inlineStr">
@@ -10636,7 +10636,7 @@
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>0.48</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F249" s="3" t="inlineStr">
@@ -10677,7 +10677,7 @@
         </is>
       </c>
       <c r="G249" s="2" t="n">
-        <v>0.65</v>
+        <v>0.45</v>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>0.45</v>
+        <v>1.03</v>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F251" s="3" t="inlineStr">
@@ -10759,7 +10759,7 @@
         </is>
       </c>
       <c r="G251" s="2" t="n">
-        <v>0.95</v>
+        <v>0.52</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F252" s="3" t="inlineStr">
@@ -10800,7 +10800,7 @@
         </is>
       </c>
       <c r="G252" s="2" t="n">
-        <v>0.86</v>
+        <v>1.14</v>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         </is>
       </c>
       <c r="G253" s="2" t="n">
-        <v>1.06</v>
+        <v>0.86</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F254" s="3" t="inlineStr">
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F255" s="3" t="inlineStr">
@@ -10923,7 +10923,7 @@
         </is>
       </c>
       <c r="G255" s="2" t="n">
-        <v>0.74</v>
+        <v>1.13</v>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F256" s="3" t="inlineStr">
@@ -10964,7 +10964,7 @@
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         </is>
       </c>
       <c r="G257" s="2" t="n">
-        <v>0.71</v>
+        <v>0.53</v>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F258" s="3" t="inlineStr">
@@ -11046,7 +11046,7 @@
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>0.46</v>
+        <v>0.72</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F259" s="3" t="inlineStr">
@@ -11087,7 +11087,7 @@
         </is>
       </c>
       <c r="G259" s="2" t="n">
-        <v>1.09</v>
+        <v>0.48</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F260" s="3" t="inlineStr">
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>1.07</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F261" s="3" t="inlineStr">
@@ -11169,7 +11169,7 @@
         </is>
       </c>
       <c r="G261" s="2" t="n">
-        <v>1.15</v>
+        <v>0.58</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F262" s="3" t="inlineStr">
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>1.03</v>
+        <v>0.85</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         </is>
       </c>
       <c r="G263" s="2" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F264" s="3" t="inlineStr">
@@ -11292,7 +11292,7 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0.44</v>
+        <v>0.77</v>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F265" s="3" t="inlineStr">
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="G265" s="2" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>1.13</v>
+        <v>0.5</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F267" s="3" t="inlineStr">
@@ -11415,7 +11415,7 @@
         </is>
       </c>
       <c r="G267" s="2" t="n">
-        <v>0.95</v>
+        <v>0.45</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         </is>
       </c>
       <c r="G269" s="2" t="n">
-        <v>0.88</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F270" s="3" t="inlineStr">
@@ -11538,7 +11538,7 @@
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F271" s="3" t="inlineStr">
@@ -11579,7 +11579,7 @@
         </is>
       </c>
       <c r="G271" s="2" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F272" s="3" t="inlineStr">
@@ -11620,7 +11620,7 @@
         </is>
       </c>
       <c r="G272" s="2" t="n">
-        <v>0.54</v>
+        <v>0.85</v>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F273" s="3" t="inlineStr">
@@ -11661,7 +11661,7 @@
         </is>
       </c>
       <c r="G273" s="2" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F274" s="3" t="inlineStr">
@@ -11702,7 +11702,7 @@
         </is>
       </c>
       <c r="G274" s="2" t="n">
-        <v>0.72</v>
+        <v>1.07</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F275" s="3" t="inlineStr">
@@ -11743,7 +11743,7 @@
         </is>
       </c>
       <c r="G275" s="2" t="n">
-        <v>1.07</v>
+        <v>0.42</v>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F276" s="3" t="inlineStr">
@@ -11784,7 +11784,7 @@
         </is>
       </c>
       <c r="G276" s="2" t="n">
-        <v>0.89</v>
+        <v>0.7</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F277" s="3" t="inlineStr">
@@ -11825,7 +11825,7 @@
         </is>
       </c>
       <c r="G277" s="2" t="n">
-        <v>1.04</v>
+        <v>0.77</v>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr">
@@ -11866,7 +11866,7 @@
         </is>
       </c>
       <c r="G278" s="2" t="n">
-        <v>0.5</v>
+        <v>0.98</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F279" s="3" t="inlineStr">
@@ -11907,7 +11907,7 @@
         </is>
       </c>
       <c r="G279" s="2" t="n">
-        <v>0.66</v>
+        <v>0.47</v>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr">
@@ -11948,7 +11948,7 @@
         </is>
       </c>
       <c r="G280" s="2" t="n">
-        <v>0.95</v>
+        <v>1.03</v>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         </is>
       </c>
       <c r="G281" s="2" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F282" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>0.79</v>
+        <v>1.02</v>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F283" s="3" t="inlineStr">
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.72</v>
+        <v>0.45</v>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         </is>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F285" s="3" t="inlineStr">
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="G285" s="2" t="n">
-        <v>0.67</v>
+        <v>0.98</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F286" s="3" t="inlineStr">
@@ -12194,7 +12194,7 @@
         </is>
       </c>
       <c r="G286" s="2" t="n">
-        <v>0.68</v>
+        <v>0.79</v>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F287" s="3" t="inlineStr">
@@ -12235,7 +12235,7 @@
         </is>
       </c>
       <c r="G287" s="2" t="n">
-        <v>0.57</v>
+        <v>0.79</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F288" s="3" t="inlineStr">
@@ -12276,7 +12276,7 @@
         </is>
       </c>
       <c r="G288" s="2" t="n">
-        <v>0.98</v>
+        <v>0.82</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         </is>
       </c>
       <c r="G289" s="2" t="n">
-        <v>0.43</v>
+        <v>0.71</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F290" s="3" t="inlineStr">
@@ -12358,7 +12358,7 @@
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F291" s="3" t="inlineStr">
@@ -12399,7 +12399,7 @@
         </is>
       </c>
       <c r="G291" s="2" t="n">
-        <v>0.7</v>
+        <v>0.84</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>0.85</v>
+        <v>0.62</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F293" s="3" t="inlineStr">
@@ -12481,7 +12481,7 @@
         </is>
       </c>
       <c r="G293" s="2" t="n">
-        <v>0.58</v>
+        <v>0.52</v>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>0.82</v>
+        <v>0.47</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F295" s="3" t="inlineStr">
@@ -12563,7 +12563,7 @@
         </is>
       </c>
       <c r="G295" s="2" t="n">
-        <v>0.88</v>
+        <v>1.07</v>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F296" s="3" t="inlineStr">
@@ -12604,7 +12604,7 @@
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>0.54</v>
+        <v>0.63</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F297" s="3" t="inlineStr">
@@ -12645,7 +12645,7 @@
         </is>
       </c>
       <c r="G297" s="2" t="n">
-        <v>0.52</v>
+        <v>0.43</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>0.87</v>
+        <v>0.42</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         </is>
       </c>
       <c r="G299" s="2" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F300" s="3" t="inlineStr">
@@ -12768,7 +12768,7 @@
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>0.47</v>
+        <v>0.9</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F301" s="3" t="inlineStr">
@@ -12809,7 +12809,7 @@
         </is>
       </c>
       <c r="G301" s="2" t="n">
-        <v>0.8</v>
+        <v>0.46</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -12911,7 +12911,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.88</v>
+        <v>0.79</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.51</v>
+        <v>1.07</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -12993,7 +12993,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -13034,7 +13034,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.47</v>
+        <v>0.83</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -13116,7 +13116,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.14</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.84</v>
+        <v>1.08</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -13198,7 +13198,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.64</v>
+        <v>1.02</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -13239,7 +13239,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1.14</v>
+        <v>0.64</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -13280,7 +13280,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -13321,7 +13321,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.97</v>
+        <v>0.6</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1.06</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -13444,7 +13444,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.71</v>
+        <v>0.84</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -13485,7 +13485,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.45</v>
+        <v>1.11</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1.01</v>
+        <v>0.72</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -13567,7 +13567,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -13599,7 +13599,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -13608,7 +13608,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -13690,7 +13690,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.71</v>
+        <v>0.51</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -13772,7 +13772,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.76</v>
+        <v>1.06</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -13813,7 +13813,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.49</v>
+        <v>0.73</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -13854,7 +13854,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.87</v>
+        <v>0.78</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -13895,7 +13895,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.71</v>
+        <v>0.79</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -13927,7 +13927,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -13936,7 +13936,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -13977,7 +13977,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -14018,7 +14018,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.57</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -14059,7 +14059,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.47</v>
+        <v>0.89</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -14100,7 +14100,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -14141,7 +14141,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1.14</v>
+        <v>0.61</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -14182,7 +14182,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -14223,7 +14223,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1.12</v>
+        <v>0.73</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -14264,7 +14264,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0.55</v>
+        <v>1.11</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -14305,7 +14305,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.92</v>
+        <v>0.65</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -14346,7 +14346,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.7</v>
+        <v>1.08</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -14387,7 +14387,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.66</v>
+        <v>0.72</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -14469,7 +14469,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.62</v>
+        <v>0.49</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -14510,7 +14510,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -14551,7 +14551,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -14592,7 +14592,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.82</v>
+        <v>1.1</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -14633,7 +14633,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.84</v>
+        <v>0.99</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -14674,7 +14674,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.75</v>
+        <v>0.98</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -14756,7 +14756,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.89</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -14879,7 +14879,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.47</v>
+        <v>0.77</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -14920,7 +14920,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1.11</v>
+        <v>0.97</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -15002,7 +15002,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>1.06</v>
+        <v>0.72</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -15043,7 +15043,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.82</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -15084,7 +15084,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0.96</v>
+        <v>0.9</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -15125,7 +15125,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -15166,7 +15166,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0.83</v>
+        <v>0.63</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -15198,7 +15198,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -15207,7 +15207,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0.62</v>
+        <v>1</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0.43</v>
+        <v>0.73</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -15289,7 +15289,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.45</v>
+        <v>0.73</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -15330,7 +15330,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -15371,7 +15371,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.74</v>
+        <v>0.88</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.58</v>
+        <v>0.44</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0.78</v>
+        <v>1.13</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -15494,7 +15494,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0.44</v>
+        <v>1.06</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -15576,7 +15576,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0.75</v>
+        <v>0.46</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -15617,7 +15617,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -15658,7 +15658,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0.89</v>
+        <v>0.63</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -15699,7 +15699,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.67</v>
+        <v>0.98</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -15740,7 +15740,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -15772,7 +15772,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -15781,7 +15781,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.87</v>
+        <v>1.15</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>1.11</v>
+        <v>0.97</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -15863,7 +15863,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -15904,7 +15904,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.95</v>
+        <v>1.06</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15986,7 +15986,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>0.92</v>
+        <v>0.87</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>1.11</v>
+        <v>0.64</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -16109,7 +16109,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.62</v>
+        <v>1.01</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0.82</v>
+        <v>0.97</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -16182,7 +16182,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -16191,7 +16191,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>1.13</v>
+        <v>0.47</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16232,7 +16232,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>1.04</v>
+        <v>0.93</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16273,7 +16273,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16314,7 +16314,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>0.66</v>
+        <v>1.03</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16437,7 +16437,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>0.91</v>
+        <v>0.76</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>0.76</v>
+        <v>0.63</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -16519,7 +16519,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0.65</v>
+        <v>0.48</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -16560,7 +16560,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>0.64</v>
+        <v>0.84</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -16601,7 +16601,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>0.98</v>
+        <v>0.7</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -16642,7 +16642,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -16683,7 +16683,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>0.66</v>
+        <v>0.44</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -16724,7 +16724,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>0.65</v>
+        <v>1.13</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -16765,7 +16765,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>0.7</v>
+        <v>0.89</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>0.52</v>
+        <v>1.01</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -16847,7 +16847,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>1.06</v>
+        <v>0.67</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -16888,7 +16888,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>0.43</v>
+        <v>0.91</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -16929,7 +16929,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -16970,7 +16970,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>1.14</v>
+        <v>0.54</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -17052,7 +17052,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0.76</v>
+        <v>0.99</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>1.03</v>
+        <v>0.79</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -17216,7 +17216,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>0.65</v>
+        <v>1.14</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -17257,7 +17257,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>1.01</v>
+        <v>0.66</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -17298,7 +17298,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>1.1</v>
+        <v>0.88</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -17339,7 +17339,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>0.64</v>
+        <v>0.51</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -17380,7 +17380,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -17421,7 +17421,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>0.68</v>
+        <v>0.44</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>0.71</v>
+        <v>1.1</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -17585,7 +17585,7 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>0.83</v>
+        <v>0.7</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>0.46</v>
+        <v>0.8</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>0.57</v>
+        <v>0.51</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -17708,7 +17708,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -17749,7 +17749,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>0.47</v>
+        <v>1.02</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -17790,7 +17790,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>0.48</v>
+        <v>1.01</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>0.97</v>
+        <v>0.48</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -17945,7 +17945,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>0.5</v>
+        <v>0.77</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -17995,7 +17995,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -18036,7 +18036,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>0.93</v>
+        <v>0.73</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -18077,7 +18077,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>0.77</v>
+        <v>0.9</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -18118,7 +18118,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>1.11</v>
+        <v>0.96</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -18159,7 +18159,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>1.11</v>
+        <v>0.51</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>1.02</v>
+        <v>0.76</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -18241,7 +18241,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>1.01</v>
+        <v>0.66</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -18282,7 +18282,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>0.79</v>
+        <v>1.06</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -18323,7 +18323,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>1.11</v>
+        <v>0.75</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -18355,7 +18355,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -18364,7 +18364,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>0.89</v>
+        <v>0.77</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -18405,7 +18405,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>1.03</v>
+        <v>0.73</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -18487,7 +18487,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>0.75</v>
+        <v>1.09</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>0.76</v>
+        <v>0.42</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -18569,7 +18569,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>0.66</v>
+        <v>0.52</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -18610,7 +18610,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>0.6</v>
+        <v>0.92</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>0.89</v>
+        <v>0.48</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>1.1</v>
+        <v>0.92</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>1.06</v>
+        <v>0.88</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -18847,7 +18847,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -18856,7 +18856,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>1.01</v>
+        <v>0.55</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -18897,7 +18897,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>0.63</v>
+        <v>1.04</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -18938,7 +18938,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>1.06</v>
+        <v>0.7</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -18979,7 +18979,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>0.97</v>
+        <v>1.03</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -19061,7 +19061,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -19134,7 +19134,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -19143,7 +19143,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -19184,7 +19184,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -19225,7 +19225,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>0.59</v>
+        <v>1.01</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -19266,7 +19266,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -19307,7 +19307,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>0.93</v>
+        <v>1.08</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -19348,7 +19348,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>0.63</v>
+        <v>0.49</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -19430,7 +19430,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>1.12</v>
+        <v>0.97</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -19471,7 +19471,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -19512,7 +19512,7 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>1</v>
+        <v>0.51</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -19553,7 +19553,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>0.43</v>
+        <v>1.08</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -19594,7 +19594,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -19635,7 +19635,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>1.04</v>
+        <v>0.77</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>1.05</v>
+        <v>0.95</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -19758,7 +19758,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -19799,7 +19799,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>0.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -19840,7 +19840,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>0.89</v>
+        <v>1.13</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -19881,7 +19881,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>1.13</v>
+        <v>0.57</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -19922,7 +19922,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>0.64</v>
+        <v>0.99</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -19963,7 +19963,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>0.66</v>
+        <v>0.42</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -20004,7 +20004,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -20045,7 +20045,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>0.58</v>
+        <v>0.48</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -20127,7 +20127,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>0.58</v>
+        <v>0.98</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -20209,7 +20209,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>1.11</v>
+        <v>0.5</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>0.86</v>
+        <v>0.64</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -20291,7 +20291,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>0.63</v>
+        <v>0.96</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>0.83</v>
+        <v>0.43</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -20373,7 +20373,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>0.93</v>
+        <v>0.57</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -20414,7 +20414,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>1.06</v>
+        <v>0.88</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -20496,7 +20496,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>0.75</v>
+        <v>0.46</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -20578,7 +20578,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>0.45</v>
+        <v>1.07</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -20610,7 +20610,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -20619,7 +20619,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>1.12</v>
+        <v>0.89</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -20742,7 +20742,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>0.67</v>
+        <v>0.76</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -20824,7 +20824,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -20865,7 +20865,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>0.7</v>
+        <v>0.95</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -20906,7 +20906,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>0.66</v>
+        <v>0.8</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>0.95</v>
+        <v>0.59</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -20988,7 +20988,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>0.89</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -21029,7 +21029,7 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>0.89</v>
+        <v>0.64</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -21070,7 +21070,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -21111,7 +21111,7 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>0.73</v>
+        <v>1.01</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -21152,7 +21152,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>1.02</v>
+        <v>0.66</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -21193,7 +21193,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>0.91</v>
+        <v>1.05</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -21225,7 +21225,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -21234,7 +21234,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>0.79</v>
+        <v>1.06</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -21275,7 +21275,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>0.6</v>
+        <v>0.54</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -21316,7 +21316,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>0.66</v>
+        <v>0.55</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -21357,7 +21357,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>1.01</v>
+        <v>0.79</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>0.93</v>
+        <v>0.51</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>0.42</v>
+        <v>1.12</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -21471,7 +21471,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -21480,7 +21480,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>1.07</v>
+        <v>0.82</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -21521,7 +21521,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>0.71</v>
+        <v>0.82</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -21562,7 +21562,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>0.75</v>
+        <v>1.06</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -21603,7 +21603,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>0.67</v>
+        <v>0.48</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -21644,7 +21644,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.54</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -21726,7 +21726,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -21767,7 +21767,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>1.02</v>
+        <v>0.85</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>0.48</v>
+        <v>0.57</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -21849,7 +21849,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -21890,7 +21890,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>1.07</v>
+        <v>0.51</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -21931,7 +21931,7 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -21972,7 +21972,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>1.07</v>
+        <v>0.92</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -22013,7 +22013,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -22054,7 +22054,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>1.01</v>
+        <v>0.59</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>0.74</v>
+        <v>0.64</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>1.11</v>
+        <v>0.73</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -22209,7 +22209,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -22218,7 +22218,7 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>0.46</v>
+        <v>1.02</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -22259,7 +22259,7 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>0.47</v>
+        <v>0.92</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>1.05</v>
+        <v>0.84</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -22341,7 +22341,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -22382,7 +22382,7 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>1.05</v>
+        <v>0.48</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -22423,7 +22423,7 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>1.11</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>1.13</v>
+        <v>0.52</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -22505,7 +22505,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>1.15</v>
+        <v>0.58</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -22587,7 +22587,7 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -22628,7 +22628,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -22669,7 +22669,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>0.7</v>
+        <v>0.47</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -22710,7 +22710,7 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -22742,7 +22742,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -22751,7 +22751,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -22874,7 +22874,7 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -22915,7 +22915,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>0.92</v>
+        <v>0.52</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>1.06</v>
+        <v>0.92</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -22988,7 +22988,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -22997,7 +22997,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>0.48</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -23038,7 +23038,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>0.65</v>
+        <v>0.45</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -23079,7 +23079,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>0.45</v>
+        <v>1.03</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -23120,7 +23120,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>0.95</v>
+        <v>0.52</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -23152,7 +23152,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -23161,7 +23161,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>0.86</v>
+        <v>1.14</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>1.06</v>
+        <v>0.86</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -23243,7 +23243,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -23284,7 +23284,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>0.74</v>
+        <v>1.13</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -23325,7 +23325,7 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>0.71</v>
+        <v>0.53</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -23407,7 +23407,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>0.46</v>
+        <v>0.72</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -23448,7 +23448,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>1.09</v>
+        <v>0.48</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -23489,7 +23489,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>1.07</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -23530,7 +23530,7 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>1.15</v>
+        <v>0.58</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -23571,7 +23571,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>1.03</v>
+        <v>0.85</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -23653,7 +23653,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>0.44</v>
+        <v>0.77</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -23694,7 +23694,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -23735,7 +23735,7 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>1.13</v>
+        <v>0.5</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -23776,7 +23776,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>0.95</v>
+        <v>0.45</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>0.88</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -23899,7 +23899,7 @@
         </is>
       </c>
       <c r="G270" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -23940,7 +23940,7 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -23981,7 +23981,7 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>0.54</v>
+        <v>0.85</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -24013,7 +24013,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -24022,7 +24022,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -24063,7 +24063,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>0.72</v>
+        <v>1.07</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -24104,7 +24104,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>1.07</v>
+        <v>0.42</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -24145,7 +24145,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>0.89</v>
+        <v>0.7</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -24186,7 +24186,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>1.04</v>
+        <v>0.77</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -24227,7 +24227,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>0.5</v>
+        <v>0.98</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -24268,7 +24268,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>0.66</v>
+        <v>0.47</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -24309,7 +24309,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>0.95</v>
+        <v>1.03</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -24391,7 +24391,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>0.79</v>
+        <v>1.02</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>0.72</v>
+        <v>0.45</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -24473,7 +24473,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -24514,7 +24514,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>0.67</v>
+        <v>0.98</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -24546,7 +24546,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -24555,7 +24555,7 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>0.68</v>
+        <v>0.79</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -24596,7 +24596,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>0.57</v>
+        <v>0.79</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -24637,7 +24637,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>0.98</v>
+        <v>0.82</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -24678,7 +24678,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>0.43</v>
+        <v>0.71</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -24710,7 +24710,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -24719,7 +24719,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -24760,7 +24760,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>0.7</v>
+        <v>0.84</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>0.85</v>
+        <v>0.62</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -24833,7 +24833,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -24842,7 +24842,7 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>0.58</v>
+        <v>0.52</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>0.82</v>
+        <v>0.47</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -24924,7 +24924,7 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>0.88</v>
+        <v>1.07</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -24965,7 +24965,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>0.54</v>
+        <v>0.63</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -25006,7 +25006,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>0.52</v>
+        <v>0.43</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>0.87</v>
+        <v>0.42</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -25129,7 +25129,7 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>0.47</v>
+        <v>0.9</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -25170,7 +25170,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>0.8</v>
+        <v>0.46</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>

--- a/reports/Web_Application_Selenium_Test_Report.xlsx
+++ b/reports/Web_Application_Selenium_Test_Report.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -582,7 +582,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1.07</v>
+        <v>0.72</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.83</v>
+        <v>1.05</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.76</v>
+        <v>0.44</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1.14</v>
+        <v>0.99</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1.02</v>
+        <v>0.5</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.64</v>
+        <v>0.96</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.95</v>
+        <v>0.67</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.61</v>
+        <v>0.47</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.84</v>
+        <v>0.64</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>1.11</v>
+        <v>0.76</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.72</v>
+        <v>0.49</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>1.07</v>
+        <v>0.66</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.59</v>
+        <v>0.47</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.47</v>
+        <v>0.7</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.51</v>
+        <v>1.13</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.6</v>
+        <v>0.91</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>1.06</v>
+        <v>0.62</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.73</v>
+        <v>1.08</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.78</v>
+        <v>0.55</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.89</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>1.04</v>
+        <v>0.6</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.61</v>
+        <v>0.52</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.5</v>
+        <v>0.66</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.73</v>
+        <v>0.6</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.65</v>
+        <v>0.84</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>1.08</v>
+        <v>0.45</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.91</v>
+        <v>1.15</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.72</v>
+        <v>0.89</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.49</v>
+        <v>0.9</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.93</v>
+        <v>0.68</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.63</v>
+        <v>0.45</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>1.1</v>
+        <v>0.76</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -2272,7 +2272,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.98</v>
+        <v>0.86</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>1.14</v>
+        <v>0.46</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.72</v>
+        <v>1.13</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.77</v>
+        <v>0.47</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.72</v>
+        <v>0.54</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.9</v>
+        <v>0.44</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -2764,7 +2764,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.63</v>
+        <v>0.55</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.73</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.73</v>
+        <v>1.13</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>1.1</v>
+        <v>0.99</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.88</v>
+        <v>0.64</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>1.06</v>
+        <v>0.93</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.63</v>
+        <v>1.13</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.98</v>
+        <v>0.65</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.93</v>
+        <v>1.08</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
@@ -3420,7 +3420,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>1.15</v>
+        <v>0.55</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
@@ -3461,7 +3461,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.97</v>
+        <v>1.13</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
@@ -3502,7 +3502,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>0.68</v>
+        <v>0.55</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>1.06</v>
+        <v>0.89</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
@@ -3666,7 +3666,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.64</v>
+        <v>0.78</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0.92</v>
+        <v>0.59</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>1.01</v>
+        <v>0.46</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.97</v>
+        <v>0.53</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>0.47</v>
+        <v>1.15</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.93</v>
+        <v>0.6</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.78</v>
+        <v>1.03</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>1.03</v>
+        <v>0.87</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>0.73</v>
+        <v>1.12</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>0.76</v>
+        <v>0.91</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.63</v>
+        <v>0.82</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.48</v>
+        <v>0.52</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.84</v>
+        <v>0.52</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>0.7</v>
+        <v>1.03</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
@@ -4322,7 +4322,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.44</v>
+        <v>1.03</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.89</v>
+        <v>0.44</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>1.01</v>
+        <v>0.57</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
@@ -4486,7 +4486,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.83</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>1.03</v>
+        <v>0.92</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
@@ -4650,7 +4650,7 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>0.54</v>
+        <v>0.77</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
@@ -4691,7 +4691,7 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>0.79</v>
+        <v>1.06</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>1.14</v>
+        <v>0.52</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>0.66</v>
+        <v>1.05</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>0.88</v>
+        <v>0.65</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>0.51</v>
+        <v>0.61</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
@@ -5060,7 +5060,7 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>0.44</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.76</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
@@ -5142,7 +5142,7 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>1.1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
@@ -5183,7 +5183,7 @@
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>0.93</v>
+        <v>0.83</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>0.7</v>
+        <v>1.08</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0.51</v>
+        <v>0.74</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>0.98</v>
+        <v>0.84</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>1.02</v>
+        <v>0.85</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>1.01</v>
+        <v>0.46</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
@@ -5470,7 +5470,7 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>1.09</v>
+        <v>0.92</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>1.08</v>
+        <v>0.98</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>0.77</v>
+        <v>0.67</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>0.67</v>
+        <v>0.91</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>0.73</v>
+        <v>1.04</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
@@ -5716,7 +5716,7 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>0.9</v>
+        <v>1.03</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>0.51</v>
+        <v>0.98</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>0.76</v>
+        <v>1.02</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>0.66</v>
+        <v>0.98</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>0.77</v>
+        <v>0.62</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
@@ -6044,7 +6044,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>0.7</v>
+        <v>0.86</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>0.73</v>
+        <v>1.13</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>0.42</v>
+        <v>0.74</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
@@ -6208,7 +6208,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.52</v>
+        <v>0.66</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
@@ -6249,7 +6249,7 @@
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>0.92</v>
+        <v>0.87</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0.48</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
@@ -6331,7 +6331,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>0.92</v>
+        <v>0.84</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
@@ -6413,7 +6413,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>0.59</v>
+        <v>0.92</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>0.55</v>
+        <v>0.96</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
@@ -6536,7 +6536,7 @@
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>0.7</v>
+        <v>1.11</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>0.97</v>
+        <v>0.58</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
@@ -6659,7 +6659,7 @@
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
@@ -6700,7 +6700,7 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
@@ -6741,7 +6741,7 @@
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>1.14</v>
+        <v>0.64</v>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
@@ -6782,7 +6782,7 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>0.97</v>
+        <v>0.66</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
@@ -6864,7 +6864,7 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>1.01</v>
+        <v>0.86</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>0.89</v>
+        <v>0.57</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
@@ -6946,7 +6946,7 @@
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>0.49</v>
+        <v>0.58</v>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>1.13</v>
+        <v>0.47</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>0.97</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>0.57</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
@@ -7151,7 +7151,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>0.51</v>
+        <v>1.11</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>1.08</v>
+        <v>0.67</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.98</v>
+        <v>0.82</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="G167" s="2" t="n">
-        <v>0.77</v>
+        <v>0.65</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>0.95</v>
+        <v>0.61</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>0.48</v>
+        <v>0.77</v>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>1.13</v>
+        <v>0.62</v>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
@@ -7520,7 +7520,7 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>0.57</v>
+        <v>0.83</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
@@ -7561,7 +7561,7 @@
         </is>
       </c>
       <c r="G173" s="2" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
@@ -7602,7 +7602,7 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>0.42</v>
+        <v>1.08</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
@@ -7643,7 +7643,7 @@
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>0.61</v>
+        <v>0.45</v>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
@@ -7684,7 +7684,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>0.72</v>
+        <v>0.96</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         </is>
       </c>
       <c r="G177" s="2" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>0.98</v>
+        <v>1.05</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="G179" s="2" t="n">
-        <v>0.49</v>
+        <v>0.67</v>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
@@ -7848,7 +7848,7 @@
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F181" s="3" t="inlineStr">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
@@ -7930,7 +7930,7 @@
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
@@ -7971,7 +7971,7 @@
         </is>
       </c>
       <c r="G183" s="2" t="n">
-        <v>0.43</v>
+        <v>1.05</v>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>0.57</v>
+        <v>0.91</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
@@ -8053,7 +8053,7 @@
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>0.88</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
@@ -8135,7 +8135,7 @@
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>0.46</v>
+        <v>0.68</v>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>1.07</v>
+        <v>0.54</v>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
@@ -8258,7 +8258,7 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>0.71</v>
+        <v>0.82</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>0.89</v>
+        <v>0.53</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>0.76</v>
+        <v>0.43</v>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F194" s="3" t="inlineStr">
@@ -8422,7 +8422,7 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F195" s="3" t="inlineStr">
@@ -8463,7 +8463,7 @@
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>0.64</v>
+        <v>1.11</v>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>0.95</v>
+        <v>0.6</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F197" s="3" t="inlineStr">
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>0.8</v>
+        <v>0.59</v>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
@@ -8586,7 +8586,7 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>0.59</v>
+        <v>1.14</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.43</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>0.64</v>
+        <v>0.84</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F201" s="3" t="inlineStr">
@@ -8709,7 +8709,7 @@
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
@@ -8750,7 +8750,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>1.01</v>
+        <v>0.76</v>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F203" s="3" t="inlineStr">
@@ -8791,7 +8791,7 @@
         </is>
       </c>
       <c r="G203" s="2" t="n">
-        <v>0.66</v>
+        <v>1.09</v>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr">
@@ -8832,7 +8832,7 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>1.05</v>
+        <v>0.72</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="G205" s="2" t="n">
-        <v>1.06</v>
+        <v>0.65</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
@@ -8914,7 +8914,7 @@
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>0.54</v>
+        <v>1.09</v>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="G207" s="2" t="n">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         </is>
       </c>
       <c r="G208" s="2" t="n">
-        <v>0.79</v>
+        <v>0.9</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F209" s="3" t="inlineStr">
@@ -9037,7 +9037,7 @@
         </is>
       </c>
       <c r="G209" s="2" t="n">
-        <v>0.51</v>
+        <v>0.65</v>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F210" s="3" t="inlineStr">
@@ -9078,7 +9078,7 @@
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>1.12</v>
+        <v>0.57</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F211" s="3" t="inlineStr">
@@ -9119,7 +9119,7 @@
         </is>
       </c>
       <c r="G211" s="2" t="n">
-        <v>0.82</v>
+        <v>0.5</v>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr">
@@ -9160,7 +9160,7 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
@@ -9201,7 +9201,7 @@
         </is>
       </c>
       <c r="G213" s="2" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr">
@@ -9242,7 +9242,7 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>0.48</v>
+        <v>1.06</v>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F215" s="3" t="inlineStr">
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="G215" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>0.54</v>
+        <v>1.08</v>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         </is>
       </c>
       <c r="G217" s="2" t="n">
-        <v>0.92</v>
+        <v>0.58</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr">
@@ -9406,7 +9406,7 @@
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>0.85</v>
+        <v>1.04</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="G219" s="2" t="n">
-        <v>0.57</v>
+        <v>1.13</v>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F220" s="3" t="inlineStr">
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>0.87</v>
+        <v>0.49</v>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F221" s="3" t="inlineStr">
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="G221" s="2" t="n">
-        <v>0.51</v>
+        <v>0.78</v>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F222" s="3" t="inlineStr">
@@ -9570,7 +9570,7 @@
         </is>
       </c>
       <c r="G222" s="2" t="n">
-        <v>0.49</v>
+        <v>1.08</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F223" s="3" t="inlineStr">
@@ -9611,7 +9611,7 @@
         </is>
       </c>
       <c r="G223" s="2" t="n">
-        <v>0.92</v>
+        <v>1.14</v>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F224" s="3" t="inlineStr">
@@ -9652,7 +9652,7 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>0.59</v>
+        <v>0.79</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         </is>
       </c>
       <c r="G225" s="2" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F226" s="3" t="inlineStr">
@@ -9734,7 +9734,7 @@
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F227" s="3" t="inlineStr">
@@ -9775,7 +9775,7 @@
         </is>
       </c>
       <c r="G227" s="2" t="n">
-        <v>0.6</v>
+        <v>1.01</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>0.73</v>
+        <v>1.14</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F229" s="3" t="inlineStr">
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="G229" s="2" t="n">
-        <v>1.02</v>
+        <v>0.79</v>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr">
@@ -9898,7 +9898,7 @@
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F231" s="3" t="inlineStr">
@@ -9939,7 +9939,7 @@
         </is>
       </c>
       <c r="G231" s="2" t="n">
-        <v>0.84</v>
+        <v>0.96</v>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F232" s="3" t="inlineStr">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F233" s="3" t="inlineStr">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>0.48</v>
+        <v>1.06</v>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F234" s="3" t="inlineStr">
@@ -10062,7 +10062,7 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.14</v>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F235" s="3" t="inlineStr">
@@ -10103,7 +10103,7 @@
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>0.52</v>
+        <v>0.84</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>0.58</v>
+        <v>1.06</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F237" s="3" t="inlineStr">
@@ -10185,7 +10185,7 @@
         </is>
       </c>
       <c r="G237" s="2" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F238" s="3" t="inlineStr">
@@ -10226,7 +10226,7 @@
         </is>
       </c>
       <c r="G238" s="2" t="n">
-        <v>0.99</v>
+        <v>0.59</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F241" s="3" t="inlineStr">
@@ -10349,7 +10349,7 @@
         </is>
       </c>
       <c r="G241" s="2" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>0.53</v>
+        <v>1</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F243" s="3" t="inlineStr">
@@ -10431,7 +10431,7 @@
         </is>
       </c>
       <c r="G243" s="2" t="n">
-        <v>0.44</v>
+        <v>1.06</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F244" s="3" t="inlineStr">
@@ -10472,7 +10472,7 @@
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>1</v>
+        <v>0.62</v>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F245" s="3" t="inlineStr">
@@ -10513,7 +10513,7 @@
         </is>
       </c>
       <c r="G245" s="2" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>0.52</v>
+        <v>1.04</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         </is>
       </c>
       <c r="G247" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F248" s="3" t="inlineStr">
@@ -10636,7 +10636,7 @@
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.49</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F249" s="3" t="inlineStr">
@@ -10677,7 +10677,7 @@
         </is>
       </c>
       <c r="G249" s="2" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>1.03</v>
+        <v>0.59</v>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F251" s="3" t="inlineStr">
@@ -10759,7 +10759,7 @@
         </is>
       </c>
       <c r="G251" s="2" t="n">
-        <v>0.52</v>
+        <v>1.11</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F252" s="3" t="inlineStr">
@@ -10800,7 +10800,7 @@
         </is>
       </c>
       <c r="G252" s="2" t="n">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         </is>
       </c>
       <c r="G253" s="2" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F254" s="3" t="inlineStr">
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F255" s="3" t="inlineStr">
@@ -10955,7 +10955,7 @@
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F256" s="3" t="inlineStr">
@@ -10964,7 +10964,7 @@
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>0.74</v>
+        <v>0.43</v>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F257" s="3" t="inlineStr">
@@ -11005,7 +11005,7 @@
         </is>
       </c>
       <c r="G257" s="2" t="n">
-        <v>0.53</v>
+        <v>1</v>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F258" s="3" t="inlineStr">
@@ -11046,7 +11046,7 @@
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>0.72</v>
+        <v>0.48</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F259" s="3" t="inlineStr">
@@ -11087,7 +11087,7 @@
         </is>
       </c>
       <c r="G259" s="2" t="n">
-        <v>0.48</v>
+        <v>0.8</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F260" s="3" t="inlineStr">
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.98</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F261" s="3" t="inlineStr">
@@ -11169,7 +11169,7 @@
         </is>
       </c>
       <c r="G261" s="2" t="n">
-        <v>0.58</v>
+        <v>1.08</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F263" s="3" t="inlineStr">
@@ -11251,7 +11251,7 @@
         </is>
       </c>
       <c r="G263" s="2" t="n">
-        <v>0.82</v>
+        <v>0.68</v>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0.77</v>
+        <v>0.6</v>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="G265" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F266" s="3" t="inlineStr">
@@ -11406,7 +11406,7 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F267" s="3" t="inlineStr">
@@ -11415,7 +11415,7 @@
         </is>
       </c>
       <c r="G267" s="2" t="n">
-        <v>0.45</v>
+        <v>1.09</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F268" s="3" t="inlineStr">
@@ -11456,7 +11456,7 @@
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>0.96</v>
+        <v>1.07</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F269" s="3" t="inlineStr">
@@ -11497,7 +11497,7 @@
         </is>
       </c>
       <c r="G269" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F270" s="3" t="inlineStr">
@@ -11538,7 +11538,7 @@
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>1.08</v>
+        <v>0.52</v>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F271" s="3" t="inlineStr">
@@ -11579,7 +11579,7 @@
         </is>
       </c>
       <c r="G271" s="2" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F272" s="3" t="inlineStr">
@@ -11661,7 +11661,7 @@
         </is>
       </c>
       <c r="G273" s="2" t="n">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F274" s="3" t="inlineStr">
@@ -11702,7 +11702,7 @@
         </is>
       </c>
       <c r="G274" s="2" t="n">
-        <v>1.07</v>
+        <v>0.44</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F275" s="3" t="inlineStr">
@@ -11743,7 +11743,7 @@
         </is>
       </c>
       <c r="G275" s="2" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         </is>
       </c>
       <c r="G276" s="2" t="n">
-        <v>0.7</v>
+        <v>1.04</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F277" s="3" t="inlineStr">
@@ -11825,7 +11825,7 @@
         </is>
       </c>
       <c r="G277" s="2" t="n">
-        <v>0.77</v>
+        <v>0.42</v>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr">
@@ -11866,7 +11866,7 @@
         </is>
       </c>
       <c r="G278" s="2" t="n">
-        <v>0.98</v>
+        <v>0.8</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F279" s="3" t="inlineStr">
@@ -11907,7 +11907,7 @@
         </is>
       </c>
       <c r="G279" s="2" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr">
@@ -11948,7 +11948,7 @@
         </is>
       </c>
       <c r="G280" s="2" t="n">
-        <v>1.03</v>
+        <v>0.68</v>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         </is>
       </c>
       <c r="G281" s="2" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F282" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>1.02</v>
+        <v>0.9</v>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F283" s="3" t="inlineStr">
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.45</v>
+        <v>0.89</v>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F284" s="3" t="inlineStr">
@@ -12112,7 +12112,7 @@
         </is>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0.92</v>
+        <v>0.54</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="G285" s="2" t="n">
-        <v>0.98</v>
+        <v>1.11</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         </is>
       </c>
       <c r="G286" s="2" t="n">
-        <v>0.79</v>
+        <v>0.66</v>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         </is>
       </c>
       <c r="G287" s="2" t="n">
-        <v>0.79</v>
+        <v>0.92</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F288" s="3" t="inlineStr">
@@ -12276,7 +12276,7 @@
         </is>
       </c>
       <c r="G288" s="2" t="n">
-        <v>0.82</v>
+        <v>1.05</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F289" s="3" t="inlineStr">
@@ -12317,7 +12317,7 @@
         </is>
       </c>
       <c r="G289" s="2" t="n">
-        <v>0.71</v>
+        <v>1.03</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F290" s="3" t="inlineStr">
@@ -12358,7 +12358,7 @@
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>0.9</v>
+        <v>0.52</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
@@ -12399,7 +12399,7 @@
         </is>
       </c>
       <c r="G291" s="2" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F292" s="3" t="inlineStr">
@@ -12440,7 +12440,7 @@
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>0.62</v>
+        <v>1.09</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F293" s="3" t="inlineStr">
@@ -12481,7 +12481,7 @@
         </is>
       </c>
       <c r="G293" s="2" t="n">
-        <v>0.52</v>
+        <v>0.84</v>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>0.47</v>
+        <v>1.05</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F295" s="3" t="inlineStr">
@@ -12563,7 +12563,7 @@
         </is>
       </c>
       <c r="G295" s="2" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F296" s="3" t="inlineStr">
@@ -12604,7 +12604,7 @@
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>0.63</v>
+        <v>1.01</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         </is>
       </c>
       <c r="G297" s="2" t="n">
-        <v>0.43</v>
+        <v>0.97</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F298" s="3" t="inlineStr">
@@ -12686,7 +12686,7 @@
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F299" s="3" t="inlineStr">
@@ -12727,7 +12727,7 @@
         </is>
       </c>
       <c r="G299" s="2" t="n">
-        <v>0.66</v>
+        <v>0.79</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F300" s="3" t="inlineStr">
@@ -12768,7 +12768,7 @@
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F301" s="3" t="inlineStr">
@@ -12809,7 +12809,7 @@
         </is>
       </c>
       <c r="G301" s="2" t="n">
-        <v>0.46</v>
+        <v>0.79</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -12911,7 +12911,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1.07</v>
+        <v>0.72</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -12993,7 +12993,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.83</v>
+        <v>1.05</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -13075,7 +13075,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.76</v>
+        <v>0.44</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -13116,7 +13116,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.14</v>
+        <v>0.99</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -13157,7 +13157,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -13198,7 +13198,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1.02</v>
+        <v>0.5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -13239,7 +13239,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.64</v>
+        <v>0.96</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -13280,7 +13280,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.95</v>
+        <v>0.67</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.61</v>
+        <v>0.47</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -13403,7 +13403,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -13444,7 +13444,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.84</v>
+        <v>0.64</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -13485,7 +13485,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1.11</v>
+        <v>0.76</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -13526,7 +13526,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.72</v>
+        <v>0.49</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -13567,7 +13567,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1.07</v>
+        <v>0.66</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -13599,7 +13599,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -13608,7 +13608,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.59</v>
+        <v>0.47</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.47</v>
+        <v>0.7</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.51</v>
+        <v>1.13</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -13731,7 +13731,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.6</v>
+        <v>0.91</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -13772,7 +13772,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1.06</v>
+        <v>0.62</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -13813,7 +13813,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.73</v>
+        <v>1.08</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -13854,7 +13854,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.78</v>
+        <v>0.55</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -13895,7 +13895,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -13927,7 +13927,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -13936,7 +13936,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -14018,7 +14018,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -14059,7 +14059,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.89</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -14100,7 +14100,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1.04</v>
+        <v>0.6</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -14141,7 +14141,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.61</v>
+        <v>0.52</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -14182,7 +14182,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.5</v>
+        <v>0.66</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -14223,7 +14223,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.73</v>
+        <v>0.6</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -14264,7 +14264,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -14305,7 +14305,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.65</v>
+        <v>0.84</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -14346,7 +14346,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1.08</v>
+        <v>0.45</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.91</v>
+        <v>1.15</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.72</v>
+        <v>0.89</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -14469,7 +14469,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.49</v>
+        <v>0.9</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -14510,7 +14510,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.93</v>
+        <v>0.68</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -14551,7 +14551,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.63</v>
+        <v>0.45</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1.1</v>
+        <v>0.76</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -14633,7 +14633,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -14674,7 +14674,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.98</v>
+        <v>0.86</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -14756,7 +14756,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1.14</v>
+        <v>0.46</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -14838,7 +14838,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0.72</v>
+        <v>1.13</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -14879,7 +14879,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.77</v>
+        <v>0.47</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -14920,7 +14920,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -14961,7 +14961,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -15002,7 +15002,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0.72</v>
+        <v>0.54</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -15043,7 +15043,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -15084,7 +15084,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0.9</v>
+        <v>0.44</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -15125,7 +15125,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0.63</v>
+        <v>0.55</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -15198,7 +15198,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -15207,7 +15207,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0.73</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -15289,7 +15289,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.73</v>
+        <v>1.13</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1.1</v>
+        <v>0.99</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -15371,7 +15371,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.88</v>
+        <v>0.64</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -15494,7 +15494,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1.06</v>
+        <v>0.93</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -15535,7 +15535,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -15576,7 +15576,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -15617,7 +15617,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -15658,7 +15658,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0.63</v>
+        <v>1.13</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -15699,7 +15699,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.98</v>
+        <v>0.65</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -15740,7 +15740,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.93</v>
+        <v>1.08</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -15772,7 +15772,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -15781,7 +15781,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>1.15</v>
+        <v>0.55</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -15813,7 +15813,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -15822,7 +15822,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0.97</v>
+        <v>1.13</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -15863,7 +15863,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -15904,7 +15904,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.68</v>
+        <v>0.55</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>1.06</v>
+        <v>0.89</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15986,7 +15986,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.64</v>
+        <v>0.78</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -16068,7 +16068,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0.92</v>
+        <v>0.59</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -16109,7 +16109,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>1.01</v>
+        <v>0.46</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0.97</v>
+        <v>0.53</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>0.47</v>
+        <v>1.15</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>0.93</v>
+        <v>0.6</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16314,7 +16314,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>0.78</v>
+        <v>1.03</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>1.03</v>
+        <v>0.87</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16396,7 +16396,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>0.73</v>
+        <v>1.12</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16437,7 +16437,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>0.76</v>
+        <v>0.91</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>0.63</v>
+        <v>0.82</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -16519,7 +16519,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0.48</v>
+        <v>0.52</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -16560,7 +16560,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>0.84</v>
+        <v>0.52</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -16601,7 +16601,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>0.7</v>
+        <v>1.03</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -16683,7 +16683,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>0.44</v>
+        <v>1.03</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -16724,7 +16724,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -16765,7 +16765,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>0.89</v>
+        <v>0.44</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -16806,7 +16806,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>1.01</v>
+        <v>0.57</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -16847,7 +16847,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -16888,7 +16888,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -16929,7 +16929,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>0.83</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -16970,7 +16970,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>1.03</v>
+        <v>0.92</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -17011,7 +17011,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>0.54</v>
+        <v>0.77</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -17052,7 +17052,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -17093,7 +17093,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -17134,7 +17134,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>0.79</v>
+        <v>1.06</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -17175,7 +17175,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>1.14</v>
+        <v>0.52</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -17257,7 +17257,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>0.66</v>
+        <v>1.05</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>0.88</v>
+        <v>0.65</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -17339,7 +17339,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>0.51</v>
+        <v>0.61</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -17380,7 +17380,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -17421,7 +17421,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>0.44</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>0.76</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>1.1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -17544,7 +17544,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>0.93</v>
+        <v>0.83</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -17585,7 +17585,7 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>0.7</v>
+        <v>1.08</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -17626,7 +17626,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -17667,7 +17667,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>0.51</v>
+        <v>0.74</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>0.98</v>
+        <v>0.84</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>1.02</v>
+        <v>0.85</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>1.01</v>
+        <v>0.46</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -17831,7 +17831,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -17872,7 +17872,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>1.09</v>
+        <v>0.92</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -17913,7 +17913,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>1.08</v>
+        <v>0.98</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>0.77</v>
+        <v>0.67</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -17995,7 +17995,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>0.67</v>
+        <v>0.91</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -18036,7 +18036,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>0.73</v>
+        <v>1.04</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -18077,7 +18077,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>0.9</v>
+        <v>1.03</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -18159,7 +18159,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>0.51</v>
+        <v>0.98</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>0.76</v>
+        <v>1.02</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -18241,7 +18241,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>0.66</v>
+        <v>0.98</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -18282,7 +18282,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -18323,7 +18323,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -18355,7 +18355,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -18364,7 +18364,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>0.77</v>
+        <v>0.62</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -18405,7 +18405,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>0.7</v>
+        <v>0.86</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>0.73</v>
+        <v>1.13</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>0.42</v>
+        <v>0.74</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -18569,7 +18569,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>0.52</v>
+        <v>0.66</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -18610,7 +18610,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>0.92</v>
+        <v>0.87</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -18651,7 +18651,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>0.48</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -18692,7 +18692,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>0.92</v>
+        <v>0.84</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -18774,7 +18774,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -18815,7 +18815,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>0.59</v>
+        <v>0.92</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -18856,7 +18856,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>0.55</v>
+        <v>0.96</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -18897,7 +18897,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -18938,7 +18938,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>0.7</v>
+        <v>1.11</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>0.97</v>
+        <v>0.58</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -19020,7 +19020,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -19061,7 +19061,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -19102,7 +19102,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>1.14</v>
+        <v>0.64</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -19134,7 +19134,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -19143,7 +19143,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>0.97</v>
+        <v>0.66</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -19184,7 +19184,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -19225,7 +19225,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>1.01</v>
+        <v>0.86</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -19266,7 +19266,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>0.89</v>
+        <v>0.57</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -19307,7 +19307,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>0.49</v>
+        <v>0.58</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -19389,7 +19389,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>1.13</v>
+        <v>0.47</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -19430,7 +19430,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>0.97</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -19471,7 +19471,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>0.57</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -19512,7 +19512,7 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>0.51</v>
+        <v>1.11</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -19553,7 +19553,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>1.08</v>
+        <v>0.67</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -19594,7 +19594,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>0.98</v>
+        <v>0.82</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>0.77</v>
+        <v>0.65</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -19717,7 +19717,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>0.95</v>
+        <v>0.61</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -19758,7 +19758,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>0.48</v>
+        <v>0.77</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -19840,7 +19840,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>1.13</v>
+        <v>0.62</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -19881,7 +19881,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>0.57</v>
+        <v>0.83</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -19922,7 +19922,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -19963,7 +19963,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>0.42</v>
+        <v>1.08</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -20004,7 +20004,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>0.61</v>
+        <v>0.45</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -20045,7 +20045,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>0.72</v>
+        <v>0.96</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -20127,7 +20127,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>0.98</v>
+        <v>1.05</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>0.49</v>
+        <v>0.67</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -20209,7 +20209,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -20291,7 +20291,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -20332,7 +20332,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>0.43</v>
+        <v>1.05</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>0.57</v>
+        <v>0.91</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -20414,7 +20414,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>0.88</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -20496,7 +20496,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>0.46</v>
+        <v>0.68</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>1.07</v>
+        <v>0.54</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -20610,7 +20610,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -20619,7 +20619,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>0.71</v>
+        <v>0.82</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>0.89</v>
+        <v>0.53</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -20742,7 +20742,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>0.76</v>
+        <v>0.43</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -20774,7 +20774,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -20783,7 +20783,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -20824,7 +20824,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>0.64</v>
+        <v>1.11</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>0.95</v>
+        <v>0.6</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -20906,7 +20906,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>0.8</v>
+        <v>0.59</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>0.59</v>
+        <v>1.14</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.43</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -21029,7 +21029,7 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>0.64</v>
+        <v>0.84</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -21070,7 +21070,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -21111,7 +21111,7 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>1.01</v>
+        <v>0.76</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -21152,7 +21152,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>0.66</v>
+        <v>1.09</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -21193,7 +21193,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>1.05</v>
+        <v>0.72</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>1.06</v>
+        <v>0.65</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -21275,7 +21275,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>0.54</v>
+        <v>1.09</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -21316,7 +21316,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>0.79</v>
+        <v>0.9</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -21398,7 +21398,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>0.51</v>
+        <v>0.65</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -21439,7 +21439,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>1.12</v>
+        <v>0.57</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -21471,7 +21471,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -21480,7 +21480,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>0.82</v>
+        <v>0.5</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -21521,7 +21521,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -21562,7 +21562,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -21603,7 +21603,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>0.48</v>
+        <v>1.06</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -21644,7 +21644,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>0.54</v>
+        <v>1.08</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -21726,7 +21726,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>0.92</v>
+        <v>0.58</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -21767,7 +21767,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>0.85</v>
+        <v>1.04</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>0.57</v>
+        <v>1.13</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -21849,7 +21849,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>0.87</v>
+        <v>0.49</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -21890,7 +21890,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>0.51</v>
+        <v>0.78</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -21931,7 +21931,7 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>0.49</v>
+        <v>1.08</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -21972,7 +21972,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>0.92</v>
+        <v>1.14</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -22013,7 +22013,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>0.59</v>
+        <v>0.79</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -22054,7 +22054,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -22095,7 +22095,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -22136,7 +22136,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>0.6</v>
+        <v>1.01</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>0.73</v>
+        <v>1.14</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -22209,7 +22209,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -22218,7 +22218,7 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>1.02</v>
+        <v>0.79</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -22259,7 +22259,7 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -22300,7 +22300,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>0.84</v>
+        <v>0.96</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -22373,7 +22373,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -22382,7 +22382,7 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>0.48</v>
+        <v>1.06</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -22423,7 +22423,7 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.14</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -22464,7 +22464,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>0.52</v>
+        <v>0.84</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -22505,7 +22505,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>0.58</v>
+        <v>1.06</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -22546,7 +22546,7 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -22587,7 +22587,7 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>0.99</v>
+        <v>0.59</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -22628,7 +22628,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -22710,7 +22710,7 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -22742,7 +22742,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -22751,7 +22751,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>0.53</v>
+        <v>1</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -22783,7 +22783,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -22792,7 +22792,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>0.44</v>
+        <v>1.06</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -22833,7 +22833,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>1</v>
+        <v>0.62</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -22865,7 +22865,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -22874,7 +22874,7 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>0.52</v>
+        <v>1.04</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -22988,7 +22988,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -22997,7 +22997,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.49</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -23038,7 +23038,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -23079,7 +23079,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>1.03</v>
+        <v>0.59</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -23120,7 +23120,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>0.52</v>
+        <v>1.11</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -23152,7 +23152,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -23161,7 +23161,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -23243,7 +23243,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -23316,7 +23316,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -23325,7 +23325,7 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>0.74</v>
+        <v>0.43</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>0.53</v>
+        <v>1</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -23407,7 +23407,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>0.72</v>
+        <v>0.48</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -23448,7 +23448,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>0.48</v>
+        <v>0.8</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -23489,7 +23489,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.98</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -23530,7 +23530,7 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>0.58</v>
+        <v>1.08</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -23603,7 +23603,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -23612,7 +23612,7 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>0.82</v>
+        <v>0.68</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>0.77</v>
+        <v>0.6</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -23767,7 +23767,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -23776,7 +23776,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>0.45</v>
+        <v>1.09</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -23817,7 +23817,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>0.96</v>
+        <v>1.07</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -23849,7 +23849,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -23858,7 +23858,7 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -23899,7 +23899,7 @@
         </is>
       </c>
       <c r="G270" t="n">
-        <v>1.08</v>
+        <v>0.52</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -23940,7 +23940,7 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -24022,7 +24022,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -24063,7 +24063,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>1.07</v>
+        <v>0.44</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -24104,7 +24104,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>0.7</v>
+        <v>1.04</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -24186,7 +24186,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>0.77</v>
+        <v>0.42</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -24227,7 +24227,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>0.98</v>
+        <v>0.8</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -24268,7 +24268,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -24309,7 +24309,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>1.03</v>
+        <v>0.68</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -24391,7 +24391,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>1.02</v>
+        <v>0.9</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>0.45</v>
+        <v>0.89</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -24473,7 +24473,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>0.92</v>
+        <v>0.54</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -24514,7 +24514,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>0.98</v>
+        <v>1.11</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>0.79</v>
+        <v>0.66</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -24596,7 +24596,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>0.79</v>
+        <v>0.92</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -24637,7 +24637,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>0.82</v>
+        <v>1.05</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -24678,7 +24678,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>0.71</v>
+        <v>1.03</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -24710,7 +24710,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -24719,7 +24719,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>0.9</v>
+        <v>0.52</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -24801,7 +24801,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>0.62</v>
+        <v>1.09</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -24833,7 +24833,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -24842,7 +24842,7 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>0.52</v>
+        <v>0.84</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>0.47</v>
+        <v>1.05</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -24924,7 +24924,7 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -24965,7 +24965,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>0.63</v>
+        <v>1.01</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>0.43</v>
+        <v>0.97</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -25047,7 +25047,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -25079,7 +25079,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -25088,7 +25088,7 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>0.66</v>
+        <v>0.79</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -25129,7 +25129,7 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -25170,7 +25170,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>0.46</v>
+        <v>0.79</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>

--- a/reports/Web_Application_Selenium_Test_Report.xlsx
+++ b/reports/Web_Application_Selenium_Test_Report.xlsx
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.95</v>
+        <v>0.61</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -582,7 +582,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.72</v>
+        <v>0.46</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.51</v>
+        <v>1.07</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1.05</v>
+        <v>0.83</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.99</v>
+        <v>1.13</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1.06</v>
+        <v>0.6</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.96</v>
+        <v>0.84</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.67</v>
+        <v>1.01</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.57</v>
+        <v>0.89</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.47</v>
+        <v>0.57</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1.02</v>
+        <v>0.58</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.76</v>
+        <v>0.98</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.49</v>
+        <v>0.87</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.66</v>
+        <v>0.87</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.47</v>
+        <v>0.79</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.7</v>
+        <v>1.11</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1.13</v>
+        <v>0.55</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.55</v>
+        <v>0.49</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.75</v>
+        <v>0.49</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.7</v>
+        <v>0.55</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.55</v>
+        <v>1.14</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.6</v>
+        <v>0.76</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.52</v>
+        <v>0.43</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.66</v>
+        <v>0.53</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.6</v>
+        <v>0.77</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>1.06</v>
+        <v>0.84</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.84</v>
+        <v>0.62</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.45</v>
+        <v>0.93</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>1.15</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.89</v>
+        <v>0.59</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.76</v>
+        <v>0.45</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -2272,7 +2272,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.95</v>
+        <v>0.53</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.86</v>
+        <v>1.04</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.46</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.75</v>
+        <v>1.1</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>1.13</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.47</v>
+        <v>0.93</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>1.02</v>
+        <v>0.74</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>1</v>
+        <v>0.48</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.52</v>
+        <v>0.59</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.44</v>
+        <v>0.52</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -2764,7 +2764,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.55</v>
+        <v>0.99</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.98</v>
+        <v>0.45</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.77</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>1.13</v>
+        <v>0.45</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -2969,7 +2969,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.99</v>
+        <v>0.43</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.47</v>
+        <v>1.1</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>1.09</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.48</v>
+        <v>0.92</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>1.13</v>
+        <v>0.68</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
@@ -3420,7 +3420,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>0.55</v>
+        <v>0.44</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
@@ -3461,7 +3461,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>1.13</v>
+        <v>0.87</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
@@ -3502,7 +3502,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>1.01</v>
+        <v>0.87</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>0.55</v>
+        <v>0.43</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0.89</v>
+        <v>0.64</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.86</v>
+        <v>0.7</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
@@ -3666,7 +3666,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.78</v>
+        <v>0.65</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0.59</v>
+        <v>1.02</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.46</v>
+        <v>0.78</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.6</v>
+        <v>1.04</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
@@ -3912,7 +3912,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>1.03</v>
+        <v>0.76</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0.87</v>
+        <v>0.45</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.82</v>
+        <v>0.46</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.52</v>
+        <v>0.43</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
@@ -4322,7 +4322,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>1.03</v>
+        <v>0.84</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>1.05</v>
+        <v>0.44</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.44</v>
+        <v>0.64</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>0.57</v>
+        <v>1.02</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
@@ -4486,7 +4486,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.97</v>
+        <v>0.68</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0.92</v>
+        <v>0.52</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
@@ -4691,7 +4691,7 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.97</v>
+        <v>0.82</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>1.06</v>
+        <v>0.53</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>1.03</v>
+        <v>0.76</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>0.52</v>
+        <v>0.57</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>1.05</v>
+        <v>0.72</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
@@ -4937,7 +4937,7 @@
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>0.61</v>
+        <v>1.12</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
@@ -5060,7 +5060,7 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.08</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
@@ -5101,7 +5101,7 @@
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.43</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
@@ -5142,7 +5142,7 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
@@ -5183,7 +5183,7 @@
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>0.83</v>
+        <v>1.01</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0.76</v>
+        <v>0.51</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0.74</v>
+        <v>1.08</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>0.85</v>
+        <v>1.03</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>0.46</v>
+        <v>1.15</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
@@ -5470,7 +5470,7 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>0.45</v>
+        <v>0.57</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>0.92</v>
+        <v>1.02</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>0.98</v>
+        <v>0.51</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>0.91</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>1.04</v>
+        <v>0.8</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
@@ -5716,7 +5716,7 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>0.98</v>
+        <v>0.77</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>1.02</v>
+        <v>0.91</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>1.08</v>
+        <v>0.62</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>0.62</v>
+        <v>0.84</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>0.86</v>
+        <v>0.77</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>1.13</v>
+        <v>0.75</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
@@ -6126,7 +6126,7 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>1.12</v>
+        <v>0.45</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>0.74</v>
+        <v>1.09</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
@@ -6208,7 +6208,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.66</v>
+        <v>0.92</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
@@ -6249,7 +6249,7 @@
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>0.87</v>
+        <v>1.06</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>0.84</v>
+        <v>0.66</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>0.96</v>
+        <v>1.14</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
@@ -6536,7 +6536,7 @@
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>0.75</v>
+        <v>0.49</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>1.11</v>
+        <v>0.61</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
@@ -6618,7 +6618,7 @@
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>0.58</v>
+        <v>0.52</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
@@ -6659,7 +6659,7 @@
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>1.01</v>
+        <v>0.63</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
@@ -6700,7 +6700,7 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>0.78</v>
+        <v>0.87</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
@@ -6741,7 +6741,7 @@
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>0.64</v>
+        <v>1.05</v>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>0.86</v>
+        <v>0.65</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>1</v>
+        <v>0.46</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
@@ -6987,7 +6987,7 @@
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>0.58</v>
+        <v>1.02</v>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>0.47</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>1.11</v>
+        <v>0.49</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>0.67</v>
+        <v>0.55</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="G167" s="2" t="n">
-        <v>0.65</v>
+        <v>0.96</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>0.77</v>
+        <v>0.6</v>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>0.95</v>
+        <v>0.54</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>0.62</v>
+        <v>1.06</v>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
@@ -7520,7 +7520,7 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>0.83</v>
+        <v>1.11</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
@@ -7561,7 +7561,7 @@
         </is>
       </c>
       <c r="G173" s="2" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
@@ -7602,7 +7602,7 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>1.08</v>
+        <v>0.93</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>0.45</v>
+        <v>1.07</v>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
@@ -7684,7 +7684,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>0.96</v>
+        <v>0.51</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F177" s="3" t="inlineStr">
@@ -7725,7 +7725,7 @@
         </is>
       </c>
       <c r="G177" s="2" t="n">
-        <v>0.47</v>
+        <v>0.57</v>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
@@ -7766,7 +7766,7 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>1.05</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="G179" s="2" t="n">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
@@ -7848,7 +7848,7 @@
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>0.72</v>
+        <v>1.03</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>0.73</v>
+        <v>0.89</v>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
@@ -7930,7 +7930,7 @@
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
@@ -7971,7 +7971,7 @@
         </is>
       </c>
       <c r="G183" s="2" t="n">
-        <v>1.05</v>
+        <v>0.73</v>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
@@ -8012,7 +8012,7 @@
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>0.91</v>
+        <v>0.42</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
@@ -8053,7 +8053,7 @@
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>0.85</v>
+        <v>0.52</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
@@ -8135,7 +8135,7 @@
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>0.68</v>
+        <v>0.84</v>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
@@ -8176,7 +8176,7 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>0.89</v>
+        <v>0.62</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>0.54</v>
+        <v>0.7</v>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
@@ -8258,7 +8258,7 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr">
@@ -8299,7 +8299,7 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>0.53</v>
+        <v>0.66</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F193" s="3" t="inlineStr">
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>0.43</v>
+        <v>0.91</v>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F194" s="3" t="inlineStr">
@@ -8422,7 +8422,7 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>0.5</v>
+        <v>0.92</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F195" s="3" t="inlineStr">
@@ -8463,7 +8463,7 @@
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>1.11</v>
+        <v>0.53</v>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F197" s="3" t="inlineStr">
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>0.59</v>
+        <v>0.68</v>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
@@ -8586,7 +8586,7 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>1.14</v>
+        <v>0.87</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>0.43</v>
+        <v>0.8</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>0.84</v>
+        <v>0.68</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F203" s="3" t="inlineStr">
@@ -8791,7 +8791,7 @@
         </is>
       </c>
       <c r="G203" s="2" t="n">
-        <v>1.09</v>
+        <v>0.92</v>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr">
@@ -8832,7 +8832,7 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="G205" s="2" t="n">
-        <v>0.65</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
@@ -8914,7 +8914,7 @@
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F207" s="3" t="inlineStr">
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="G207" s="2" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F208" s="3" t="inlineStr">
@@ -8996,7 +8996,7 @@
         </is>
       </c>
       <c r="G208" s="2" t="n">
-        <v>0.9</v>
+        <v>1.14</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F209" s="3" t="inlineStr">
@@ -9037,7 +9037,7 @@
         </is>
       </c>
       <c r="G209" s="2" t="n">
-        <v>0.65</v>
+        <v>0.46</v>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F210" s="3" t="inlineStr">
@@ -9078,7 +9078,7 @@
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         </is>
       </c>
       <c r="G211" s="2" t="n">
-        <v>0.5</v>
+        <v>0.91</v>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr">
@@ -9160,7 +9160,7 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>0.95</v>
+        <v>1.02</v>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
@@ -9201,7 +9201,7 @@
         </is>
       </c>
       <c r="G213" s="2" t="n">
-        <v>1.1</v>
+        <v>0.48</v>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr">
@@ -9242,7 +9242,7 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>1.06</v>
+        <v>0.53</v>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F215" s="3" t="inlineStr">
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="G215" s="2" t="n">
-        <v>0.6</v>
+        <v>0.93</v>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F217" s="3" t="inlineStr">
@@ -9365,7 +9365,7 @@
         </is>
       </c>
       <c r="G217" s="2" t="n">
-        <v>0.58</v>
+        <v>1.04</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>1.04</v>
+        <v>0.66</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F219" s="3" t="inlineStr">
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="G219" s="2" t="n">
-        <v>1.13</v>
+        <v>0.99</v>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>0.49</v>
+        <v>1.1</v>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F221" s="3" t="inlineStr">
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="G221" s="2" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F222" s="3" t="inlineStr">
@@ -9570,7 +9570,7 @@
         </is>
       </c>
       <c r="G222" s="2" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F223" s="3" t="inlineStr">
@@ -9611,7 +9611,7 @@
         </is>
       </c>
       <c r="G223" s="2" t="n">
-        <v>1.14</v>
+        <v>0.62</v>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>0.79</v>
+        <v>0.51</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F225" s="3" t="inlineStr">
@@ -9693,7 +9693,7 @@
         </is>
       </c>
       <c r="G225" s="2" t="n">
-        <v>0.6</v>
+        <v>1.05</v>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F227" s="3" t="inlineStr">
@@ -9775,7 +9775,7 @@
         </is>
       </c>
       <c r="G227" s="2" t="n">
-        <v>1.01</v>
+        <v>0.42</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>1.14</v>
+        <v>0.82</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="G229" s="2" t="n">
-        <v>0.79</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr">
@@ -9898,7 +9898,7 @@
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>0.96</v>
+        <v>0.73</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F231" s="3" t="inlineStr">
@@ -9939,7 +9939,7 @@
         </is>
       </c>
       <c r="G231" s="2" t="n">
-        <v>0.96</v>
+        <v>0.75</v>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F232" s="3" t="inlineStr">
@@ -9980,7 +9980,7 @@
         </is>
       </c>
       <c r="G232" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>1.06</v>
+        <v>0.55</v>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F234" s="3" t="inlineStr">
@@ -10062,7 +10062,7 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>0.84</v>
+        <v>1.09</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F237" s="3" t="inlineStr">
@@ -10185,7 +10185,7 @@
         </is>
       </c>
       <c r="G237" s="2" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
@@ -10226,7 +10226,7 @@
         </is>
       </c>
       <c r="G238" s="2" t="n">
-        <v>0.59</v>
+        <v>0.52</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>1.06</v>
+        <v>0.98</v>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
@@ -10299,7 +10299,7 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F240" s="3" t="inlineStr">
@@ -10308,7 +10308,7 @@
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>0.46</v>
+        <v>0.78</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F241" s="3" t="inlineStr">
@@ -10349,7 +10349,7 @@
         </is>
       </c>
       <c r="G241" s="2" t="n">
-        <v>1.09</v>
+        <v>0.72</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         </is>
       </c>
       <c r="G243" s="2" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F244" s="3" t="inlineStr">
@@ -10472,7 +10472,7 @@
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>0.62</v>
+        <v>0.43</v>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F245" s="3" t="inlineStr">
@@ -10513,7 +10513,7 @@
         </is>
       </c>
       <c r="G245" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>1.04</v>
+        <v>0.58</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F247" s="3" t="inlineStr">
@@ -10595,7 +10595,7 @@
         </is>
       </c>
       <c r="G247" s="2" t="n">
-        <v>0.98</v>
+        <v>1.05</v>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F248" s="3" t="inlineStr">
@@ -10636,7 +10636,7 @@
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F249" s="3" t="inlineStr">
@@ -10677,7 +10677,7 @@
         </is>
       </c>
       <c r="G249" s="2" t="n">
-        <v>0.44</v>
+        <v>0.74</v>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F250" s="3" t="inlineStr">
@@ -10718,7 +10718,7 @@
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>0.59</v>
+        <v>0.89</v>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F251" s="3" t="inlineStr">
@@ -10759,7 +10759,7 @@
         </is>
       </c>
       <c r="G251" s="2" t="n">
-        <v>1.11</v>
+        <v>0.98</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         </is>
       </c>
       <c r="G252" s="2" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F253" s="3" t="inlineStr">
@@ -10841,7 +10841,7 @@
         </is>
       </c>
       <c r="G253" s="2" t="n">
-        <v>0.8</v>
+        <v>1.11</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F254" s="3" t="inlineStr">
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>0.72</v>
+        <v>0.42</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         </is>
       </c>
       <c r="G255" s="2" t="n">
-        <v>1.13</v>
+        <v>0.83</v>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>0.43</v>
+        <v>1</v>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F257" s="3" t="inlineStr">
@@ -11005,7 +11005,7 @@
         </is>
       </c>
       <c r="G257" s="2" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>0.48</v>
+        <v>1.1</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         </is>
       </c>
       <c r="G259" s="2" t="n">
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F260" s="3" t="inlineStr">
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>0.98</v>
+        <v>0.59</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F261" s="3" t="inlineStr">
@@ -11169,7 +11169,7 @@
         </is>
       </c>
       <c r="G261" s="2" t="n">
-        <v>1.08</v>
+        <v>0.64</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F262" s="3" t="inlineStr">
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         </is>
       </c>
       <c r="G263" s="2" t="n">
-        <v>0.68</v>
+        <v>0.54</v>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F264" s="3" t="inlineStr">
@@ -11292,7 +11292,7 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="G265" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.53</v>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>0.5</v>
+        <v>0.61</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F267" s="3" t="inlineStr">
@@ -11415,7 +11415,7 @@
         </is>
       </c>
       <c r="G267" s="2" t="n">
-        <v>1.09</v>
+        <v>0.44</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F269" s="3" t="inlineStr">
@@ -11497,7 +11497,7 @@
         </is>
       </c>
       <c r="G269" s="2" t="n">
-        <v>0.89</v>
+        <v>1.09</v>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F270" s="3" t="inlineStr">
@@ -11538,7 +11538,7 @@
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>0.52</v>
+        <v>0.49</v>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F271" s="3" t="inlineStr">
@@ -11579,7 +11579,7 @@
         </is>
       </c>
       <c r="G271" s="2" t="n">
-        <v>1.05</v>
+        <v>0.8</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F272" s="3" t="inlineStr">
@@ -11620,7 +11620,7 @@
         </is>
       </c>
       <c r="G272" s="2" t="n">
-        <v>0.85</v>
+        <v>0.55</v>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         </is>
       </c>
       <c r="G273" s="2" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F274" s="3" t="inlineStr">
@@ -11702,7 +11702,7 @@
         </is>
       </c>
       <c r="G274" s="2" t="n">
-        <v>0.44</v>
+        <v>1.12</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F275" s="3" t="inlineStr">
@@ -11743,7 +11743,7 @@
         </is>
       </c>
       <c r="G275" s="2" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F276" s="3" t="inlineStr">
@@ -11784,7 +11784,7 @@
         </is>
       </c>
       <c r="G276" s="2" t="n">
-        <v>1.04</v>
+        <v>0.52</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F277" s="3" t="inlineStr">
@@ -11825,7 +11825,7 @@
         </is>
       </c>
       <c r="G277" s="2" t="n">
-        <v>0.42</v>
+        <v>1.12</v>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr">
@@ -11866,7 +11866,7 @@
         </is>
       </c>
       <c r="G278" s="2" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F279" s="3" t="inlineStr">
@@ -11907,7 +11907,7 @@
         </is>
       </c>
       <c r="G279" s="2" t="n">
-        <v>0.55</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr">
@@ -11948,7 +11948,7 @@
         </is>
       </c>
       <c r="G280" s="2" t="n">
-        <v>0.68</v>
+        <v>1.05</v>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
@@ -11980,7 +11980,7 @@
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F281" s="3" t="inlineStr">
@@ -11989,7 +11989,7 @@
         </is>
       </c>
       <c r="G281" s="2" t="n">
-        <v>0.5</v>
+        <v>0.77</v>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F282" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>0.9</v>
+        <v>0.46</v>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F283" s="3" t="inlineStr">
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.89</v>
+        <v>0.43</v>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F284" s="3" t="inlineStr">
@@ -12112,7 +12112,7 @@
         </is>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0.54</v>
+        <v>0.75</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="G285" s="2" t="n">
-        <v>1.11</v>
+        <v>0.71</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F286" s="3" t="inlineStr">
@@ -12194,7 +12194,7 @@
         </is>
       </c>
       <c r="G286" s="2" t="n">
-        <v>0.66</v>
+        <v>0.96</v>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F287" s="3" t="inlineStr">
@@ -12235,7 +12235,7 @@
         </is>
       </c>
       <c r="G287" s="2" t="n">
-        <v>0.92</v>
+        <v>0.62</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F288" s="3" t="inlineStr">
@@ -12276,7 +12276,7 @@
         </is>
       </c>
       <c r="G288" s="2" t="n">
-        <v>1.05</v>
+        <v>0.62</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F289" s="3" t="inlineStr">
@@ -12317,7 +12317,7 @@
         </is>
       </c>
       <c r="G289" s="2" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F290" s="3" t="inlineStr">
@@ -12358,7 +12358,7 @@
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>0.52</v>
+        <v>0.42</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
@@ -12399,7 +12399,7 @@
         </is>
       </c>
       <c r="G291" s="2" t="n">
-        <v>0.86</v>
+        <v>0.47</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F292" s="3" t="inlineStr">
@@ -12440,7 +12440,7 @@
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>1.09</v>
+        <v>0.79</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F293" s="3" t="inlineStr">
@@ -12481,7 +12481,7 @@
         </is>
       </c>
       <c r="G293" s="2" t="n">
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F294" s="3" t="inlineStr">
@@ -12522,7 +12522,7 @@
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F295" s="3" t="inlineStr">
@@ -12563,7 +12563,7 @@
         </is>
       </c>
       <c r="G295" s="2" t="n">
-        <v>1.03</v>
+        <v>0.87</v>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F296" s="3" t="inlineStr">
@@ -12604,7 +12604,7 @@
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>1.01</v>
+        <v>0.89</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F297" s="3" t="inlineStr">
@@ -12645,7 +12645,7 @@
         </is>
       </c>
       <c r="G297" s="2" t="n">
-        <v>0.97</v>
+        <v>1.06</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>0.54</v>
+        <v>0.9</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F299" s="3" t="inlineStr">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F300" s="3" t="inlineStr">
@@ -12768,7 +12768,7 @@
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>0.89</v>
+        <v>0.62</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F301" s="3" t="inlineStr">
@@ -12809,7 +12809,7 @@
         </is>
       </c>
       <c r="G301" s="2" t="n">
-        <v>0.79</v>
+        <v>0.57</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.95</v>
+        <v>0.61</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.72</v>
+        <v>0.46</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.51</v>
+        <v>1.07</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -13034,7 +13034,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.05</v>
+        <v>0.83</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -13116,7 +13116,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.99</v>
+        <v>1.13</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -13157,7 +13157,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.06</v>
+        <v>0.6</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -13198,7 +13198,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -13239,7 +13239,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.96</v>
+        <v>0.84</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -13280,7 +13280,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.67</v>
+        <v>1.01</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -13321,7 +13321,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.57</v>
+        <v>0.89</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.47</v>
+        <v>0.57</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1.02</v>
+        <v>0.58</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -13444,7 +13444,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.76</v>
+        <v>0.98</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -13526,7 +13526,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.49</v>
+        <v>0.87</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -13567,7 +13567,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.66</v>
+        <v>0.87</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.47</v>
+        <v>0.79</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -13649,7 +13649,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.7</v>
+        <v>1.11</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -13690,7 +13690,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1.13</v>
+        <v>0.55</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -13731,7 +13731,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -13772,7 +13772,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -13813,7 +13813,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -13854,7 +13854,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.55</v>
+        <v>0.49</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -13895,7 +13895,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.75</v>
+        <v>0.49</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -13977,7 +13977,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.7</v>
+        <v>0.55</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -14018,7 +14018,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.55</v>
+        <v>1.14</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.6</v>
+        <v>0.76</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -14141,7 +14141,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.52</v>
+        <v>0.43</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.66</v>
+        <v>0.53</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.6</v>
+        <v>0.77</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -14264,7 +14264,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1.06</v>
+        <v>0.84</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -14305,7 +14305,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.84</v>
+        <v>0.62</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -14346,7 +14346,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.45</v>
+        <v>0.93</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -14387,7 +14387,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1.15</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.89</v>
+        <v>0.59</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -14592,7 +14592,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.76</v>
+        <v>0.45</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -14633,7 +14633,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -14674,7 +14674,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.95</v>
+        <v>0.53</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -14706,7 +14706,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -14715,7 +14715,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.86</v>
+        <v>1.04</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -14756,7 +14756,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.46</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -14797,7 +14797,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.75</v>
+        <v>1.1</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -14838,7 +14838,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1.13</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -14879,7 +14879,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.47</v>
+        <v>0.93</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -14920,7 +14920,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1.02</v>
+        <v>0.74</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -14961,7 +14961,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>0.48</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -15002,7 +15002,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -15043,7 +15043,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.52</v>
+        <v>0.59</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -15084,7 +15084,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0.44</v>
+        <v>0.52</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -15125,7 +15125,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -15166,7 +15166,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0.55</v>
+        <v>0.99</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -15198,7 +15198,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -15207,7 +15207,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0.98</v>
+        <v>0.45</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -15248,7 +15248,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.77</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -15289,7 +15289,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>1.13</v>
+        <v>0.45</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -15330,7 +15330,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0.99</v>
+        <v>0.43</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -15371,7 +15371,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -15412,7 +15412,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.47</v>
+        <v>1.1</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>1.09</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -15526,7 +15526,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -15535,7 +15535,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0.48</v>
+        <v>0.92</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -15617,7 +15617,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -15658,7 +15658,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>1.13</v>
+        <v>0.68</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -15699,7 +15699,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -15740,7 +15740,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -15772,7 +15772,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -15781,7 +15781,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.55</v>
+        <v>0.44</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -15813,7 +15813,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -15822,7 +15822,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>1.13</v>
+        <v>0.87</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -15863,7 +15863,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>1.01</v>
+        <v>0.87</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -15904,7 +15904,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.55</v>
+        <v>0.43</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.89</v>
+        <v>0.64</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>0.86</v>
+        <v>0.7</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.78</v>
+        <v>0.65</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -16068,7 +16068,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0.59</v>
+        <v>1.02</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -16109,7 +16109,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.46</v>
+        <v>0.78</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -16150,7 +16150,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>0.6</v>
+        <v>1.04</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16273,7 +16273,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16314,7 +16314,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>1.03</v>
+        <v>0.76</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>0.87</v>
+        <v>0.45</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16396,7 +16396,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16437,7 +16437,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -16478,7 +16478,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>0.82</v>
+        <v>0.46</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -16519,7 +16519,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -16560,7 +16560,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>0.52</v>
+        <v>0.43</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -16601,7 +16601,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -16642,7 +16642,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -16683,7 +16683,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>1.03</v>
+        <v>0.84</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -16724,7 +16724,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>1.05</v>
+        <v>0.44</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -16765,7 +16765,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>0.44</v>
+        <v>0.64</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -16806,7 +16806,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>0.57</v>
+        <v>1.02</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -16847,7 +16847,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -16888,7 +16888,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>0.97</v>
+        <v>0.68</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -16929,7 +16929,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -16970,7 +16970,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>0.92</v>
+        <v>0.52</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -17052,7 +17052,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0.97</v>
+        <v>0.82</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -17093,7 +17093,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -17134,7 +17134,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>1.06</v>
+        <v>0.53</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -17175,7 +17175,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>1.03</v>
+        <v>0.76</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -17216,7 +17216,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>0.52</v>
+        <v>0.57</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -17257,7 +17257,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>1.05</v>
+        <v>0.72</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -17298,7 +17298,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -17339,7 +17339,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>0.61</v>
+        <v>1.12</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -17380,7 +17380,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -17421,7 +17421,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.08</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -17462,7 +17462,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.43</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -17544,7 +17544,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>0.83</v>
+        <v>1.01</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -17585,7 +17585,7 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -17626,7 +17626,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>0.76</v>
+        <v>0.51</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>0.74</v>
+        <v>1.08</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -17708,7 +17708,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -17749,7 +17749,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>0.85</v>
+        <v>1.03</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -17790,7 +17790,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>0.46</v>
+        <v>1.15</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -17831,7 +17831,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>0.45</v>
+        <v>0.57</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -17872,7 +17872,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>0.92</v>
+        <v>1.02</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -17913,7 +17913,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0.98</v>
+        <v>0.51</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -17995,7 +17995,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>0.91</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -18036,7 +18036,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>1.04</v>
+        <v>0.8</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -18077,7 +18077,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -18118,7 +18118,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -18159,7 +18159,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>0.98</v>
+        <v>0.77</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -18200,7 +18200,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>1.02</v>
+        <v>0.91</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -18241,7 +18241,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -18282,7 +18282,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>1.08</v>
+        <v>0.62</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -18323,7 +18323,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -18355,7 +18355,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -18364,7 +18364,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>0.62</v>
+        <v>0.84</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -18405,7 +18405,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>0.86</v>
+        <v>0.77</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>1.13</v>
+        <v>0.75</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -18487,7 +18487,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>1.12</v>
+        <v>0.45</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>0.74</v>
+        <v>1.09</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -18569,7 +18569,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>0.66</v>
+        <v>0.92</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -18610,7 +18610,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>0.87</v>
+        <v>1.06</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -18651,7 +18651,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>0.84</v>
+        <v>0.66</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -18815,7 +18815,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -18856,7 +18856,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>0.96</v>
+        <v>1.14</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -18897,7 +18897,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>0.75</v>
+        <v>0.49</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>1.11</v>
+        <v>0.61</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -18979,7 +18979,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>0.58</v>
+        <v>0.52</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -19020,7 +19020,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>1.01</v>
+        <v>0.63</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -19061,7 +19061,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>0.78</v>
+        <v>0.87</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -19102,7 +19102,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>0.64</v>
+        <v>1.05</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -19184,7 +19184,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>0.86</v>
+        <v>0.65</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -19307,7 +19307,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>1</v>
+        <v>0.46</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -19348,7 +19348,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>0.58</v>
+        <v>1.02</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -19389,7 +19389,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>0.47</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -19430,7 +19430,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -19471,7 +19471,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>1.11</v>
+        <v>0.49</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -19553,7 +19553,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>0.67</v>
+        <v>0.55</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -19594,7 +19594,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -19635,7 +19635,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -19676,7 +19676,7 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>0.65</v>
+        <v>0.96</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -19717,7 +19717,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -19758,7 +19758,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>0.77</v>
+        <v>0.6</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>0.95</v>
+        <v>0.54</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>0.62</v>
+        <v>1.06</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -19881,7 +19881,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>0.83</v>
+        <v>1.11</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -19922,7 +19922,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -19963,7 +19963,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>1.08</v>
+        <v>0.93</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>0.45</v>
+        <v>1.07</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -20045,7 +20045,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>0.96</v>
+        <v>0.51</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -20086,7 +20086,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>0.47</v>
+        <v>0.57</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -20127,7 +20127,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>1.05</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -20168,7 +20168,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -20209,7 +20209,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>0.72</v>
+        <v>1.03</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>0.73</v>
+        <v>0.89</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -20291,7 +20291,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -20332,7 +20332,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>1.05</v>
+        <v>0.73</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -20373,7 +20373,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>0.91</v>
+        <v>0.42</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -20414,7 +20414,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>0.85</v>
+        <v>0.52</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -20496,7 +20496,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>0.68</v>
+        <v>0.84</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -20537,7 +20537,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>0.89</v>
+        <v>0.62</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -20578,7 +20578,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>0.54</v>
+        <v>0.7</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -20610,7 +20610,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -20619,7 +20619,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -20660,7 +20660,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>0.53</v>
+        <v>0.66</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -20742,7 +20742,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>0.43</v>
+        <v>0.91</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -20774,7 +20774,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -20783,7 +20783,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>0.5</v>
+        <v>0.92</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -20824,7 +20824,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>1.11</v>
+        <v>0.53</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -20906,7 +20906,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>0.59</v>
+        <v>0.68</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>1.14</v>
+        <v>0.87</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>0.43</v>
+        <v>0.8</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -21029,7 +21029,7 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>0.84</v>
+        <v>0.68</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -21070,7 +21070,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -21152,7 +21152,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>1.09</v>
+        <v>0.92</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -21193,7 +21193,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>0.65</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -21275,7 +21275,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -21316,7 +21316,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -21357,7 +21357,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>0.9</v>
+        <v>1.14</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -21398,7 +21398,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>0.65</v>
+        <v>0.46</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -21439,7 +21439,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>0.5</v>
+        <v>0.91</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -21521,7 +21521,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>0.95</v>
+        <v>1.02</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -21562,7 +21562,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>1.1</v>
+        <v>0.48</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -21603,7 +21603,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>1.06</v>
+        <v>0.53</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -21644,7 +21644,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>0.6</v>
+        <v>0.93</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -21726,7 +21726,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>0.58</v>
+        <v>1.04</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>1.04</v>
+        <v>0.66</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -21799,7 +21799,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>1.13</v>
+        <v>0.99</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>0.49</v>
+        <v>1.1</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -21890,7 +21890,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -21931,7 +21931,7 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -21972,7 +21972,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>1.14</v>
+        <v>0.62</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -22013,7 +22013,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>0.79</v>
+        <v>0.51</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -22054,7 +22054,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>0.6</v>
+        <v>1.05</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -22136,7 +22136,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>1.01</v>
+        <v>0.42</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>1.14</v>
+        <v>0.82</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>0.79</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -22259,7 +22259,7 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>0.96</v>
+        <v>0.73</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -22300,7 +22300,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>0.96</v>
+        <v>0.75</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -22341,7 +22341,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>1.06</v>
+        <v>0.55</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -22423,7 +22423,7 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>0.84</v>
+        <v>1.09</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -22505,7 +22505,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -22546,7 +22546,7 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>0.59</v>
+        <v>0.52</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -22628,7 +22628,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>1.06</v>
+        <v>0.98</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -22669,7 +22669,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>0.46</v>
+        <v>0.78</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -22710,7 +22710,7 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>1.09</v>
+        <v>0.72</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -22742,7 +22742,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -22751,7 +22751,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -22792,7 +22792,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -22833,7 +22833,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>0.62</v>
+        <v>0.43</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -22865,7 +22865,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -22874,7 +22874,7 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>1.04</v>
+        <v>0.58</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -22947,7 +22947,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>0.98</v>
+        <v>1.05</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -22988,7 +22988,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -22997,7 +22997,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -23038,7 +23038,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>0.44</v>
+        <v>0.74</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -23079,7 +23079,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>0.59</v>
+        <v>0.89</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -23120,7 +23120,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>1.11</v>
+        <v>0.98</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -23161,7 +23161,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -23202,7 +23202,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>0.8</v>
+        <v>1.11</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -23243,7 +23243,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>0.72</v>
+        <v>0.42</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>1.13</v>
+        <v>0.83</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -23325,7 +23325,7 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>0.43</v>
+        <v>1</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -23407,7 +23407,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>0.48</v>
+        <v>1.1</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -23489,7 +23489,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>0.98</v>
+        <v>0.59</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -23530,7 +23530,7 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>1.08</v>
+        <v>0.64</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -23571,7 +23571,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>0.68</v>
+        <v>0.54</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -23653,7 +23653,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.53</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -23735,7 +23735,7 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>0.5</v>
+        <v>0.61</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -23776,7 +23776,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>1.09</v>
+        <v>0.44</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -23849,7 +23849,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -23858,7 +23858,7 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>0.89</v>
+        <v>1.09</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -23899,7 +23899,7 @@
         </is>
       </c>
       <c r="G270" t="n">
-        <v>0.52</v>
+        <v>0.49</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -23940,7 +23940,7 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>1.05</v>
+        <v>0.8</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -23981,7 +23981,7 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>0.85</v>
+        <v>0.55</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -24063,7 +24063,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>0.44</v>
+        <v>1.12</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -24104,7 +24104,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -24145,7 +24145,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>1.04</v>
+        <v>0.52</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -24186,7 +24186,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>0.42</v>
+        <v>1.12</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -24227,7 +24227,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -24268,7 +24268,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>0.55</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -24309,7 +24309,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>0.68</v>
+        <v>1.05</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -24350,7 +24350,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>0.5</v>
+        <v>0.77</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -24391,7 +24391,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>0.9</v>
+        <v>0.46</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>0.89</v>
+        <v>0.43</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -24473,7 +24473,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>0.54</v>
+        <v>0.75</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -24514,7 +24514,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>1.11</v>
+        <v>0.71</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -24546,7 +24546,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -24555,7 +24555,7 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>0.66</v>
+        <v>0.96</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -24596,7 +24596,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>0.92</v>
+        <v>0.62</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -24637,7 +24637,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>1.05</v>
+        <v>0.62</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -24678,7 +24678,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -24710,7 +24710,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -24719,7 +24719,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>0.52</v>
+        <v>0.42</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>0.86</v>
+        <v>0.47</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -24801,7 +24801,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>1.09</v>
+        <v>0.79</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -24833,7 +24833,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -24842,7 +24842,7 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -24883,7 +24883,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -24924,7 +24924,7 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>1.03</v>
+        <v>0.87</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -24965,7 +24965,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>1.01</v>
+        <v>0.89</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -25006,7 +25006,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>0.97</v>
+        <v>1.06</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>0.54</v>
+        <v>0.9</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -25079,7 +25079,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -25120,7 +25120,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -25129,7 +25129,7 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>0.89</v>
+        <v>0.62</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -25170,7 +25170,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>0.79</v>
+        <v>0.57</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>

--- a/reports/Web_Application_Selenium_Test_Report.xlsx
+++ b/reports/Web_Application_Selenium_Test_Report.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.61</v>
+        <v>0.93</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -582,7 +582,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1.07</v>
+        <v>0.85</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.83</v>
+        <v>1.05</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.46</v>
+        <v>0.58</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1.13</v>
+        <v>0.63</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.6</v>
+        <v>1.13</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.64</v>
+        <v>1.1</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.84</v>
+        <v>1.01</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>1.01</v>
+        <v>0.59</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.89</v>
+        <v>0.53</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.57</v>
+        <v>0.96</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.58</v>
+        <v>0.74</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.79</v>
+        <v>1.11</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.55</v>
+        <v>0.43</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.54</v>
+        <v>1.14</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>1.1</v>
+        <v>0.93</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.49</v>
+        <v>0.76</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.6</v>
+        <v>0.51</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.49</v>
+        <v>0.62</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.55</v>
+        <v>0.93</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.96</v>
+        <v>0.55</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.76</v>
+        <v>0.52</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.43</v>
+        <v>0.77</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.53</v>
+        <v>1.1</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.84</v>
+        <v>1.05</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.62</v>
+        <v>0.83</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.93</v>
+        <v>1.12</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.68</v>
+        <v>1.12</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.43</v>
+        <v>1.04</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -2272,7 +2272,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.79</v>
+        <v>0.61</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.53</v>
+        <v>0.65</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>1.04</v>
+        <v>0.44</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>1.1</v>
+        <v>0.76</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.14</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.74</v>
+        <v>0.93</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.59</v>
+        <v>0.82</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.52</v>
+        <v>1.05</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -2764,7 +2764,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.65</v>
+        <v>1.04</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.99</v>
+        <v>1.14</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.45</v>
+        <v>0.79</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.77</v>
+        <v>0.42</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.45</v>
+        <v>0.99</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -2969,7 +2969,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.43</v>
+        <v>0.92</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>1.1</v>
+        <v>0.87</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.93</v>
+        <v>0.63</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.92</v>
+        <v>0.64</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>1.12</v>
+        <v>0.53</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.68</v>
+        <v>0.89</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.67</v>
+        <v>0.44</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>1.02</v>
+        <v>0.44</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>0.44</v>
+        <v>1.09</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
@@ -3461,7 +3461,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.87</v>
+        <v>0.75</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
@@ -3502,7 +3502,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>0.43</v>
+        <v>0.64</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0.64</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.7</v>
+        <v>0.97</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
@@ -3666,7 +3666,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>1.02</v>
+        <v>0.45</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.55</v>
+        <v>0.87</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
@@ -3912,7 +3912,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.76</v>
+        <v>0.59</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0.45</v>
+        <v>1.06</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>1.01</v>
+        <v>0.51</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>0.96</v>
+        <v>0.7</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.46</v>
+        <v>0.58</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.51</v>
+        <v>0.66</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.43</v>
+        <v>0.79</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>1.04</v>
+        <v>0.99</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
@@ -4322,7 +4322,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.84</v>
+        <v>1.09</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0.44</v>
+        <v>0.76</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.64</v>
+        <v>1.06</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>1.02</v>
+        <v>0.88</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
@@ -4486,7 +4486,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>1.14</v>
+        <v>0.88</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.68</v>
+        <v>0.76</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0.52</v>
+        <v>1.14</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
@@ -4650,7 +4650,7 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
@@ -4691,7 +4691,7 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.82</v>
+        <v>0.47</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>0.47</v>
+        <v>0.98</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>0.53</v>
+        <v>0.57</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>0.76</v>
+        <v>0.89</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
@@ -4937,7 +4937,7 @@
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>1.12</v>
+        <v>0.89</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
@@ -5060,7 +5060,7 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>1.08</v>
+        <v>0.79</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
@@ -5101,7 +5101,7 @@
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.43</v>
+        <v>0.92</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
@@ -5142,7 +5142,7 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0.71</v>
+        <v>0.43</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
@@ -5183,7 +5183,7 @@
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>1.01</v>
+        <v>0.86</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>1.14</v>
+        <v>0.78</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0.51</v>
+        <v>0.91</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>1.08</v>
+        <v>0.9</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>0.95</v>
+        <v>0.59</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>1.15</v>
+        <v>0.57</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
@@ -5470,7 +5470,7 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>1.02</v>
+        <v>0.58</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>0.51</v>
+        <v>0.88</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>1.01</v>
+        <v>0.89</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>0.98</v>
+        <v>0.87</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>0.77</v>
+        <v>0.47</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>0.91</v>
+        <v>0.67</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>0.93</v>
+        <v>0.57</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>0.62</v>
+        <v>1.04</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>0.84</v>
+        <v>0.67</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
@@ -6044,7 +6044,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
@@ -6126,7 +6126,7 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>0.45</v>
+        <v>1.07</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>1.09</v>
+        <v>0.54</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
@@ -6249,7 +6249,7 @@
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>1.06</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
@@ -6331,7 +6331,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>0.77</v>
+        <v>0.98</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
@@ -6454,7 +6454,7 @@
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>0.95</v>
+        <v>0.45</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>1.14</v>
+        <v>0.75</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
@@ -6536,7 +6536,7 @@
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>0.49</v>
+        <v>0.97</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>0.61</v>
+        <v>0.45</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
@@ -6618,7 +6618,7 @@
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>0.63</v>
+        <v>1.12</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
@@ -6700,7 +6700,7 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>0.87</v>
+        <v>1.13</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>1.05</v>
+        <v>0.72</v>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
@@ -6864,7 +6864,7 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>0.65</v>
+        <v>1.15</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>0.72</v>
+        <v>0.44</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
@@ -6946,7 +6946,7 @@
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>0.46</v>
+        <v>1.15</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
@@ -6987,7 +6987,7 @@
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>1.02</v>
+        <v>0.48</v>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>1.06</v>
+        <v>0.97</v>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
@@ -7110,7 +7110,7 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
@@ -7151,7 +7151,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>0.49</v>
+        <v>0.52</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
@@ -7192,7 +7192,7 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>0.55</v>
+        <v>1.03</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.87</v>
+        <v>0.43</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>0.72</v>
+        <v>0.99</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="G167" s="2" t="n">
-        <v>0.96</v>
+        <v>0.52</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>0.58</v>
+        <v>0.96</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
@@ -7438,7 +7438,7 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>0.54</v>
+        <v>0.48</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>1.06</v>
+        <v>0.71</v>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>1.11</v>
+        <v>0.49</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         </is>
       </c>
       <c r="G173" s="2" t="n">
-        <v>1.06</v>
+        <v>0.61</v>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
@@ -7602,7 +7602,7 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>0.93</v>
+        <v>1.05</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
@@ -7643,7 +7643,7 @@
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
@@ -7684,7 +7684,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>0.51</v>
+        <v>1.09</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F177" s="3" t="inlineStr">
@@ -7725,7 +7725,7 @@
         </is>
       </c>
       <c r="G177" s="2" t="n">
-        <v>0.57</v>
+        <v>0.86</v>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
@@ -7766,7 +7766,7 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="G179" s="2" t="n">
-        <v>0.78</v>
+        <v>0.61</v>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
@@ -7848,7 +7848,7 @@
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>0.89</v>
+        <v>0.52</v>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
@@ -7930,7 +7930,7 @@
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
@@ -8012,7 +8012,7 @@
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>0.42</v>
+        <v>1.11</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
@@ -8053,7 +8053,7 @@
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>0.68</v>
+        <v>1.08</v>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>0.52</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
@@ -8135,7 +8135,7 @@
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>0.84</v>
+        <v>0.98</v>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
@@ -8176,7 +8176,7 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>0.7</v>
+        <v>0.96</v>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
@@ -8258,7 +8258,7 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>1.11</v>
+        <v>0.73</v>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr">
@@ -8340,7 +8340,7 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>0.66</v>
+        <v>0.82</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>0.91</v>
+        <v>0.61</v>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>0.92</v>
+        <v>0.55</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F195" s="3" t="inlineStr">
@@ -8463,7 +8463,7 @@
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>0.53</v>
+        <v>1.07</v>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F197" s="3" t="inlineStr">
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>0.68</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
@@ -8586,7 +8586,7 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>0.87</v>
+        <v>0.5</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F199" s="3" t="inlineStr">
@@ -8627,7 +8627,7 @@
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>0.8</v>
+        <v>0.49</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>0.68</v>
+        <v>1.05</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F201" s="3" t="inlineStr">
@@ -8709,7 +8709,7 @@
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>0.7</v>
+        <v>1.12</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
@@ -8750,7 +8750,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F203" s="3" t="inlineStr">
@@ -8791,7 +8791,7 @@
         </is>
       </c>
       <c r="G203" s="2" t="n">
-        <v>0.92</v>
+        <v>0.62</v>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr">
@@ -8832,7 +8832,7 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>0.61</v>
+        <v>0.79</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F205" s="3" t="inlineStr">
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="G205" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
@@ -8914,7 +8914,7 @@
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="G207" s="2" t="n">
-        <v>0.97</v>
+        <v>1.08</v>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F208" s="3" t="inlineStr">
@@ -8996,7 +8996,7 @@
         </is>
       </c>
       <c r="G208" s="2" t="n">
-        <v>1.14</v>
+        <v>0.48</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         </is>
       </c>
       <c r="G209" s="2" t="n">
-        <v>0.46</v>
+        <v>1</v>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>0.7</v>
+        <v>0.43</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         </is>
       </c>
       <c r="G211" s="2" t="n">
-        <v>0.91</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>1.02</v>
+        <v>0.42</v>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
@@ -9201,7 +9201,7 @@
         </is>
       </c>
       <c r="G213" s="2" t="n">
-        <v>0.48</v>
+        <v>0.78</v>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr">
@@ -9242,7 +9242,7 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F215" s="3" t="inlineStr">
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="G215" s="2" t="n">
-        <v>0.93</v>
+        <v>1.14</v>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F216" s="3" t="inlineStr">
@@ -9324,7 +9324,7 @@
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>1.05</v>
+        <v>0.7</v>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F217" s="3" t="inlineStr">
@@ -9365,7 +9365,7 @@
         </is>
       </c>
       <c r="G217" s="2" t="n">
-        <v>1.04</v>
+        <v>0.64</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr">
@@ -9406,7 +9406,7 @@
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>0.66</v>
+        <v>1.03</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F219" s="3" t="inlineStr">
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="G219" s="2" t="n">
-        <v>0.99</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>1.1</v>
+        <v>0.51</v>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F221" s="3" t="inlineStr">
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="G221" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         </is>
       </c>
       <c r="G222" s="2" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F223" s="3" t="inlineStr">
@@ -9611,7 +9611,7 @@
         </is>
       </c>
       <c r="G223" s="2" t="n">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F224" s="3" t="inlineStr">
@@ -9652,7 +9652,7 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>0.51</v>
+        <v>0.64</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F225" s="3" t="inlineStr">
@@ -9693,7 +9693,7 @@
         </is>
       </c>
       <c r="G225" s="2" t="n">
-        <v>1.05</v>
+        <v>0.73</v>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F226" s="3" t="inlineStr">
@@ -9734,7 +9734,7 @@
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>0.85</v>
+        <v>1.04</v>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         </is>
       </c>
       <c r="G227" s="2" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F228" s="3" t="inlineStr">
@@ -9816,7 +9816,7 @@
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>0.82</v>
+        <v>0.54</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F229" s="3" t="inlineStr">
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="G229" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.77</v>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr">
@@ -9898,7 +9898,7 @@
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         </is>
       </c>
       <c r="G231" s="2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F232" s="3" t="inlineStr">
@@ -9980,7 +9980,7 @@
         </is>
       </c>
       <c r="G232" s="2" t="n">
-        <v>0.76</v>
+        <v>0.96</v>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F233" s="3" t="inlineStr">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>0.55</v>
+        <v>0.74</v>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F236" s="3" t="inlineStr">
@@ -10144,7 +10144,7 @@
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>1.11</v>
+        <v>0.92</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F237" s="3" t="inlineStr">
@@ -10185,7 +10185,7 @@
         </is>
       </c>
       <c r="G237" s="2" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F238" s="3" t="inlineStr">
@@ -10226,7 +10226,7 @@
         </is>
       </c>
       <c r="G238" s="2" t="n">
-        <v>0.52</v>
+        <v>1.15</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F239" s="3" t="inlineStr">
@@ -10267,7 +10267,7 @@
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>0.98</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>0.78</v>
+        <v>0.54</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F241" s="3" t="inlineStr">
@@ -10349,7 +10349,7 @@
         </is>
       </c>
       <c r="G241" s="2" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F243" s="3" t="inlineStr">
@@ -10431,7 +10431,7 @@
         </is>
       </c>
       <c r="G243" s="2" t="n">
-        <v>1.07</v>
+        <v>0.57</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>0.43</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F245" s="3" t="inlineStr">
@@ -10513,7 +10513,7 @@
         </is>
       </c>
       <c r="G245" s="2" t="n">
-        <v>1.11</v>
+        <v>0.77</v>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F246" s="3" t="inlineStr">
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>0.58</v>
+        <v>0.84</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F247" s="3" t="inlineStr">
@@ -10595,7 +10595,7 @@
         </is>
       </c>
       <c r="G247" s="2" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F248" s="3" t="inlineStr">
@@ -10636,7 +10636,7 @@
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>0.51</v>
+        <v>0.48</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F249" s="3" t="inlineStr">
@@ -10677,7 +10677,7 @@
         </is>
       </c>
       <c r="G249" s="2" t="n">
-        <v>0.74</v>
+        <v>1.02</v>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F250" s="3" t="inlineStr">
@@ -10718,7 +10718,7 @@
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>0.89</v>
+        <v>0.48</v>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         </is>
       </c>
       <c r="G251" s="2" t="n">
-        <v>0.98</v>
+        <v>0.82</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         </is>
       </c>
       <c r="G252" s="2" t="n">
-        <v>0.84</v>
+        <v>0.74</v>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F253" s="3" t="inlineStr">
@@ -10841,7 +10841,7 @@
         </is>
       </c>
       <c r="G253" s="2" t="n">
-        <v>1.11</v>
+        <v>0.82</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F254" s="3" t="inlineStr">
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F255" s="3" t="inlineStr">
@@ -10923,7 +10923,7 @@
         </is>
       </c>
       <c r="G255" s="2" t="n">
-        <v>0.83</v>
+        <v>0.55</v>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F256" s="3" t="inlineStr">
@@ -10964,7 +10964,7 @@
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         </is>
       </c>
       <c r="G257" s="2" t="n">
-        <v>1.07</v>
+        <v>0.44</v>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F258" s="3" t="inlineStr">
@@ -11046,7 +11046,7 @@
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F259" s="3" t="inlineStr">
@@ -11087,7 +11087,7 @@
         </is>
       </c>
       <c r="G259" s="2" t="n">
-        <v>0.93</v>
+        <v>0.65</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F260" s="3" t="inlineStr">
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>0.59</v>
+        <v>0.52</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F261" s="3" t="inlineStr">
@@ -11169,7 +11169,7 @@
         </is>
       </c>
       <c r="G261" s="2" t="n">
-        <v>0.64</v>
+        <v>0.95</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F262" s="3" t="inlineStr">
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>0.8</v>
+        <v>0.54</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         </is>
       </c>
       <c r="G263" s="2" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F264" s="3" t="inlineStr">
@@ -11292,7 +11292,7 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F265" s="3" t="inlineStr">
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="G265" s="2" t="n">
-        <v>0.53</v>
+        <v>0.57</v>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F266" s="3" t="inlineStr">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>0.61</v>
+        <v>0.8</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F267" s="3" t="inlineStr">
@@ -11415,7 +11415,7 @@
         </is>
       </c>
       <c r="G267" s="2" t="n">
-        <v>0.44</v>
+        <v>0.67</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F268" s="3" t="inlineStr">
@@ -11456,7 +11456,7 @@
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         </is>
       </c>
       <c r="G269" s="2" t="n">
-        <v>1.09</v>
+        <v>0.87</v>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F270" s="3" t="inlineStr">
@@ -11538,7 +11538,7 @@
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F271" s="3" t="inlineStr">
@@ -11579,7 +11579,7 @@
         </is>
       </c>
       <c r="G271" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F272" s="3" t="inlineStr">
@@ -11620,7 +11620,7 @@
         </is>
       </c>
       <c r="G272" s="2" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F273" s="3" t="inlineStr">
@@ -11661,7 +11661,7 @@
         </is>
       </c>
       <c r="G273" s="2" t="n">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F274" s="3" t="inlineStr">
@@ -11702,7 +11702,7 @@
         </is>
       </c>
       <c r="G274" s="2" t="n">
-        <v>1.12</v>
+        <v>0.95</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F275" s="3" t="inlineStr">
@@ -11743,7 +11743,7 @@
         </is>
       </c>
       <c r="G275" s="2" t="n">
-        <v>0.42</v>
+        <v>0.6</v>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F276" s="3" t="inlineStr">
@@ -11784,7 +11784,7 @@
         </is>
       </c>
       <c r="G276" s="2" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         </is>
       </c>
       <c r="G277" s="2" t="n">
-        <v>1.12</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr">
@@ -11866,7 +11866,7 @@
         </is>
       </c>
       <c r="G278" s="2" t="n">
-        <v>0.82</v>
+        <v>0.46</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F279" s="3" t="inlineStr">
@@ -11907,7 +11907,7 @@
         </is>
       </c>
       <c r="G279" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.09</v>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr">
@@ -11948,7 +11948,7 @@
         </is>
       </c>
       <c r="G280" s="2" t="n">
-        <v>1.05</v>
+        <v>0.61</v>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         </is>
       </c>
       <c r="G281" s="2" t="n">
-        <v>0.77</v>
+        <v>0.98</v>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F282" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>0.46</v>
+        <v>1.08</v>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F283" s="3" t="inlineStr">
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.43</v>
+        <v>0.54</v>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F284" s="3" t="inlineStr">
@@ -12112,7 +12112,7 @@
         </is>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F285" s="3" t="inlineStr">
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="G285" s="2" t="n">
-        <v>0.71</v>
+        <v>0.95</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         </is>
       </c>
       <c r="G286" s="2" t="n">
-        <v>0.96</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F287" s="3" t="inlineStr">
@@ -12235,7 +12235,7 @@
         </is>
       </c>
       <c r="G287" s="2" t="n">
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F288" s="3" t="inlineStr">
@@ -12276,7 +12276,7 @@
         </is>
       </c>
       <c r="G288" s="2" t="n">
-        <v>0.62</v>
+        <v>0.9</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F289" s="3" t="inlineStr">
@@ -12317,7 +12317,7 @@
         </is>
       </c>
       <c r="G289" s="2" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F290" s="3" t="inlineStr">
@@ -12358,7 +12358,7 @@
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>0.42</v>
+        <v>1.05</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F291" s="3" t="inlineStr">
@@ -12399,7 +12399,7 @@
         </is>
       </c>
       <c r="G291" s="2" t="n">
-        <v>0.47</v>
+        <v>0.89</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F292" s="3" t="inlineStr">
@@ -12440,7 +12440,7 @@
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         </is>
       </c>
       <c r="G293" s="2" t="n">
-        <v>0.92</v>
+        <v>0.73</v>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>1.11</v>
+        <v>0.67</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F295" s="3" t="inlineStr">
@@ -12563,7 +12563,7 @@
         </is>
       </c>
       <c r="G295" s="2" t="n">
-        <v>0.87</v>
+        <v>0.53</v>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F296" s="3" t="inlineStr">
@@ -12604,7 +12604,7 @@
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>0.89</v>
+        <v>0.98</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F297" s="3" t="inlineStr">
@@ -12645,7 +12645,7 @@
         </is>
       </c>
       <c r="G297" s="2" t="n">
-        <v>1.06</v>
+        <v>0.86</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F298" s="3" t="inlineStr">
@@ -12686,7 +12686,7 @@
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F299" s="3" t="inlineStr">
@@ -12727,7 +12727,7 @@
         </is>
       </c>
       <c r="G299" s="2" t="n">
-        <v>0.79</v>
+        <v>0.7</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F300" s="3" t="inlineStr">
@@ -12768,7 +12768,7 @@
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         </is>
       </c>
       <c r="G301" s="2" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -12911,7 +12911,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.61</v>
+        <v>0.93</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -12993,7 +12993,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.07</v>
+        <v>0.85</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -13034,7 +13034,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.83</v>
+        <v>1.05</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -13075,7 +13075,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.46</v>
+        <v>0.58</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -13116,7 +13116,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.13</v>
+        <v>0.63</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -13157,7 +13157,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.6</v>
+        <v>1.13</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -13198,7 +13198,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.64</v>
+        <v>1.1</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -13239,7 +13239,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.84</v>
+        <v>1.01</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -13280,7 +13280,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1.01</v>
+        <v>0.59</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -13321,7 +13321,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.89</v>
+        <v>0.53</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.57</v>
+        <v>0.96</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -13403,7 +13403,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.58</v>
+        <v>0.74</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -13444,7 +13444,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -13567,7 +13567,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -13599,7 +13599,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -13608,7 +13608,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.79</v>
+        <v>1.11</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -13649,7 +13649,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -13690,7 +13690,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.55</v>
+        <v>0.43</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -13731,7 +13731,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -13772,7 +13772,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.54</v>
+        <v>1.14</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -13813,7 +13813,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1.1</v>
+        <v>0.93</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -13854,7 +13854,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.49</v>
+        <v>0.76</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -13895,7 +13895,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.6</v>
+        <v>0.51</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -13927,7 +13927,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -13936,7 +13936,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.49</v>
+        <v>0.62</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -13977,7 +13977,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.55</v>
+        <v>0.93</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -14018,7 +14018,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -14059,7 +14059,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.96</v>
+        <v>0.55</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -14100,7 +14100,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.76</v>
+        <v>0.52</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -14141,7 +14141,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.43</v>
+        <v>0.77</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -14182,7 +14182,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.53</v>
+        <v>1.1</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -14223,7 +14223,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -14264,7 +14264,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0.84</v>
+        <v>1.05</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -14305,7 +14305,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.62</v>
+        <v>0.83</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.93</v>
+        <v>1.12</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -14387,7 +14387,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.68</v>
+        <v>1.12</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.43</v>
+        <v>1.04</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -14633,7 +14633,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.79</v>
+        <v>0.61</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -14674,7 +14674,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.53</v>
+        <v>0.65</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1.04</v>
+        <v>0.44</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -14756,7 +14756,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -14797,7 +14797,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1.1</v>
+        <v>0.76</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.14</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -14879,7 +14879,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -14920,7 +14920,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0.74</v>
+        <v>0.93</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -15043,7 +15043,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.59</v>
+        <v>0.82</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -15084,7 +15084,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0.52</v>
+        <v>1.05</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -15125,7 +15125,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0.65</v>
+        <v>1.04</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -15166,7 +15166,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0.99</v>
+        <v>1.14</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -15198,7 +15198,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -15207,7 +15207,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0.45</v>
+        <v>0.79</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -15248,7 +15248,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0.77</v>
+        <v>0.42</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -15289,7 +15289,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.45</v>
+        <v>0.99</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -15330,7 +15330,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0.43</v>
+        <v>0.92</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -15371,7 +15371,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -15412,7 +15412,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>1.1</v>
+        <v>0.87</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0.93</v>
+        <v>0.63</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -15535,7 +15535,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0.92</v>
+        <v>0.64</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -15617,7 +15617,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>1.12</v>
+        <v>0.53</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -15658,7 +15658,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0.68</v>
+        <v>0.89</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -15699,7 +15699,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.67</v>
+        <v>0.44</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -15740,7 +15740,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>1.02</v>
+        <v>0.44</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.44</v>
+        <v>1.09</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -15813,7 +15813,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -15822,7 +15822,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0.87</v>
+        <v>0.75</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -15863,7 +15863,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -15904,7 +15904,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.43</v>
+        <v>0.64</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.64</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15986,7 +15986,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>0.7</v>
+        <v>0.97</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>1.02</v>
+        <v>0.45</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -16109,7 +16109,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0.55</v>
+        <v>0.87</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16232,7 +16232,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16273,7 +16273,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16314,7 +16314,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>0.76</v>
+        <v>0.59</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>0.45</v>
+        <v>1.06</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16396,7 +16396,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1.01</v>
+        <v>0.51</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16437,7 +16437,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>0.96</v>
+        <v>0.7</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -16478,7 +16478,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>0.46</v>
+        <v>0.58</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -16519,7 +16519,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0.51</v>
+        <v>0.66</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -16560,7 +16560,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>0.43</v>
+        <v>0.79</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -16601,7 +16601,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>1.04</v>
+        <v>0.99</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -16642,7 +16642,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -16683,7 +16683,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>0.84</v>
+        <v>1.09</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -16724,7 +16724,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>0.44</v>
+        <v>0.76</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -16765,7 +16765,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>0.64</v>
+        <v>1.06</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -16806,7 +16806,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>1.02</v>
+        <v>0.88</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -16847,7 +16847,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>1.14</v>
+        <v>0.88</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -16888,7 +16888,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>0.68</v>
+        <v>0.76</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -16970,7 +16970,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>0.52</v>
+        <v>1.14</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -17011,7 +17011,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -17052,7 +17052,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0.82</v>
+        <v>0.47</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>0.47</v>
+        <v>0.98</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -17134,7 +17134,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>0.53</v>
+        <v>0.57</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -17175,7 +17175,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>0.76</v>
+        <v>0.89</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -17298,7 +17298,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -17339,7 +17339,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>1.12</v>
+        <v>0.89</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -17380,7 +17380,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -17421,7 +17421,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>1.08</v>
+        <v>0.79</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -17462,7 +17462,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>0.43</v>
+        <v>0.92</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>0.71</v>
+        <v>0.43</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -17544,7 +17544,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>1.01</v>
+        <v>0.86</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -17585,7 +17585,7 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>1.14</v>
+        <v>0.78</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -17626,7 +17626,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>0.51</v>
+        <v>0.91</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>1.08</v>
+        <v>0.9</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -17708,7 +17708,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>0.95</v>
+        <v>0.59</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -17790,7 +17790,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>1.15</v>
+        <v>0.57</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -17831,7 +17831,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -17872,7 +17872,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>1.02</v>
+        <v>0.58</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -17913,7 +17913,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0.51</v>
+        <v>0.88</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -17995,7 +17995,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -18036,7 +18036,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -18077,7 +18077,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>1.01</v>
+        <v>0.89</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -18118,7 +18118,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>0.98</v>
+        <v>0.87</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -18159,7 +18159,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>0.77</v>
+        <v>0.47</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -18200,7 +18200,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>0.91</v>
+        <v>0.67</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -18241,7 +18241,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>0.93</v>
+        <v>0.57</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -18282,7 +18282,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>0.62</v>
+        <v>1.04</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -18323,7 +18323,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -18355,7 +18355,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -18364,7 +18364,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>0.84</v>
+        <v>0.67</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -18405,7 +18405,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -18487,7 +18487,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>0.45</v>
+        <v>1.07</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>1.09</v>
+        <v>0.54</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -18610,7 +18610,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>1.06</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -18692,7 +18692,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>0.77</v>
+        <v>0.98</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -18815,7 +18815,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>0.95</v>
+        <v>0.45</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>1.14</v>
+        <v>0.75</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -18897,7 +18897,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>0.49</v>
+        <v>0.97</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -18938,7 +18938,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>0.61</v>
+        <v>0.45</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -18979,7 +18979,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>0.63</v>
+        <v>1.12</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -19061,7 +19061,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>0.87</v>
+        <v>1.13</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>1.05</v>
+        <v>0.72</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -19225,7 +19225,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>0.65</v>
+        <v>1.15</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -19266,7 +19266,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>0.72</v>
+        <v>0.44</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -19307,7 +19307,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>0.46</v>
+        <v>1.15</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -19348,7 +19348,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>1.02</v>
+        <v>0.48</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -19389,7 +19389,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -19430,7 +19430,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>1.06</v>
+        <v>0.97</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -19471,7 +19471,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -19512,7 +19512,7 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>0.49</v>
+        <v>0.52</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -19553,7 +19553,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>0.55</v>
+        <v>1.03</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -19594,7 +19594,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>0.87</v>
+        <v>0.43</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -19635,7 +19635,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>0.72</v>
+        <v>0.99</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>0.96</v>
+        <v>0.52</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>0.58</v>
+        <v>0.96</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -19758,7 +19758,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -19799,7 +19799,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>0.54</v>
+        <v>0.48</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>1.06</v>
+        <v>0.71</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>1.11</v>
+        <v>0.49</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>1.06</v>
+        <v>0.61</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -19963,7 +19963,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>0.93</v>
+        <v>1.05</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -20004,7 +20004,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -20045,7 +20045,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>0.51</v>
+        <v>1.09</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -20086,7 +20086,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>0.57</v>
+        <v>0.86</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -20127,7 +20127,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>0.78</v>
+        <v>0.61</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -20209,7 +20209,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>0.89</v>
+        <v>0.52</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -20291,7 +20291,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -20364,7 +20364,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -20373,7 +20373,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>0.42</v>
+        <v>1.11</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -20414,7 +20414,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>0.68</v>
+        <v>1.08</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>0.52</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -20496,7 +20496,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>0.84</v>
+        <v>0.98</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -20537,7 +20537,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -20578,7 +20578,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>0.7</v>
+        <v>0.96</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -20610,7 +20610,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -20619,7 +20619,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>1.11</v>
+        <v>0.73</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -20701,7 +20701,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>0.66</v>
+        <v>0.82</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -20742,7 +20742,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>0.91</v>
+        <v>0.61</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>0.92</v>
+        <v>0.55</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -20824,7 +20824,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>0.53</v>
+        <v>1.07</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -20906,7 +20906,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>0.68</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>0.87</v>
+        <v>0.5</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -20988,7 +20988,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>0.8</v>
+        <v>0.49</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -21029,7 +21029,7 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>0.68</v>
+        <v>1.05</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -21070,7 +21070,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>0.7</v>
+        <v>1.12</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -21111,7 +21111,7 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -21152,7 +21152,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>0.92</v>
+        <v>0.62</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -21193,7 +21193,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>0.61</v>
+        <v>0.79</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -21225,7 +21225,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -21234,7 +21234,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -21275,7 +21275,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -21316,7 +21316,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>0.97</v>
+        <v>1.08</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -21357,7 +21357,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>1.14</v>
+        <v>0.48</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>0.46</v>
+        <v>1</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>0.7</v>
+        <v>0.43</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>0.91</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -21521,7 +21521,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>1.02</v>
+        <v>0.42</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -21562,7 +21562,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>0.48</v>
+        <v>0.78</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -21603,7 +21603,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -21644,7 +21644,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>0.93</v>
+        <v>1.14</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -21685,7 +21685,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>1.05</v>
+        <v>0.7</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -21726,7 +21726,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>1.04</v>
+        <v>0.64</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -21767,7 +21767,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>0.66</v>
+        <v>1.03</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -21799,7 +21799,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>0.99</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>1.1</v>
+        <v>0.51</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -21890,7 +21890,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -21972,7 +21972,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -22013,7 +22013,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>0.51</v>
+        <v>0.64</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -22054,7 +22054,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>1.05</v>
+        <v>0.73</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -22095,7 +22095,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>0.85</v>
+        <v>1.04</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -22177,7 +22177,7 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>0.82</v>
+        <v>0.54</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -22209,7 +22209,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -22218,7 +22218,7 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.77</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -22259,7 +22259,7 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -22341,7 +22341,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>0.76</v>
+        <v>0.96</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -22382,7 +22382,7 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>0.55</v>
+        <v>0.74</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -22505,7 +22505,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>1.11</v>
+        <v>0.92</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -22546,7 +22546,7 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -22587,7 +22587,7 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>0.52</v>
+        <v>1.15</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -22628,7 +22628,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>0.98</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>0.78</v>
+        <v>0.54</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -22710,7 +22710,7 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -22742,7 +22742,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -22751,7 +22751,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -22783,7 +22783,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -22792,7 +22792,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>1.07</v>
+        <v>0.57</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>0.43</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -22865,7 +22865,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -22874,7 +22874,7 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>1.11</v>
+        <v>0.77</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -22915,7 +22915,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>0.58</v>
+        <v>0.84</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -22947,7 +22947,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -22988,7 +22988,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -22997,7 +22997,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>0.51</v>
+        <v>0.48</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -23038,7 +23038,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>0.74</v>
+        <v>1.02</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -23079,7 +23079,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>0.89</v>
+        <v>0.48</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>0.98</v>
+        <v>0.82</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -23161,7 +23161,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>0.84</v>
+        <v>0.74</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -23202,7 +23202,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>1.11</v>
+        <v>0.82</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -23243,7 +23243,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -23284,7 +23284,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>0.83</v>
+        <v>0.55</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -23325,7 +23325,7 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>1.07</v>
+        <v>0.44</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -23407,7 +23407,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -23448,7 +23448,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>0.93</v>
+        <v>0.65</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -23489,7 +23489,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>0.59</v>
+        <v>0.52</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -23530,7 +23530,7 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>0.64</v>
+        <v>0.95</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -23571,7 +23571,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>0.8</v>
+        <v>0.54</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -23653,7 +23653,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -23694,7 +23694,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>0.53</v>
+        <v>0.57</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -23735,7 +23735,7 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>0.61</v>
+        <v>0.8</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -23776,7 +23776,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>0.44</v>
+        <v>0.67</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -23817,7 +23817,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>1.09</v>
+        <v>0.87</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -23899,7 +23899,7 @@
         </is>
       </c>
       <c r="G270" t="n">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -23940,7 +23940,7 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -23981,7 +23981,7 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -24013,7 +24013,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -24022,7 +24022,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -24063,7 +24063,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>1.12</v>
+        <v>0.95</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -24104,7 +24104,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>0.42</v>
+        <v>0.6</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -24145,7 +24145,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>1.12</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -24227,7 +24227,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>0.82</v>
+        <v>0.46</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -24268,7 +24268,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.09</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -24309,7 +24309,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>1.05</v>
+        <v>0.61</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>0.77</v>
+        <v>0.98</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -24391,7 +24391,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>0.46</v>
+        <v>1.08</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>0.43</v>
+        <v>0.54</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -24473,7 +24473,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -24514,7 +24514,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>0.71</v>
+        <v>0.95</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>0.96</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -24596,7 +24596,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -24637,7 +24637,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>0.62</v>
+        <v>0.9</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -24678,7 +24678,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -24710,7 +24710,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -24719,7 +24719,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>0.42</v>
+        <v>1.05</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -24760,7 +24760,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>0.47</v>
+        <v>0.89</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -24801,7 +24801,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -24842,7 +24842,7 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>0.92</v>
+        <v>0.73</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>1.11</v>
+        <v>0.67</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -24924,7 +24924,7 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>0.87</v>
+        <v>0.53</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -24965,7 +24965,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>0.89</v>
+        <v>0.98</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -25006,7 +25006,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>1.06</v>
+        <v>0.86</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -25047,7 +25047,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -25079,7 +25079,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -25088,7 +25088,7 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>0.79</v>
+        <v>0.7</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -25129,7 +25129,7 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
@@ -25170,7 +25170,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>

--- a/reports/Web_Application_Selenium_Test_Report.xlsx
+++ b/reports/Web_Application_Selenium_Test_Report.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.93</v>
+        <v>0.54</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -582,7 +582,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.47</v>
+        <v>0.71</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.85</v>
+        <v>1.02</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1.05</v>
+        <v>0.88</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.58</v>
+        <v>0.43</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1.13</v>
+        <v>0.7</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1.01</v>
+        <v>0.44</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.53</v>
+        <v>0.79</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.96</v>
+        <v>0.76</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.74</v>
+        <v>0.55</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.8</v>
+        <v>1.05</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.99</v>
+        <v>1.04</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.89</v>
+        <v>0.43</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1.11</v>
+        <v>0.79</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1.13</v>
+        <v>0.59</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.43</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.91</v>
+        <v>1.14</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>1.14</v>
+        <v>0.88</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.93</v>
+        <v>0.46</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.76</v>
+        <v>0.47</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.51</v>
+        <v>0.97</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.62</v>
+        <v>0.92</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.93</v>
+        <v>0.55</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.89</v>
+        <v>0.47</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.55</v>
+        <v>0.48</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.52</v>
+        <v>0.86</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>1.1</v>
+        <v>0.68</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>1.05</v>
+        <v>0.43</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.83</v>
+        <v>0.62</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>1.12</v>
+        <v>0.53</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.98</v>
+        <v>1.15</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.57</v>
+        <v>1.12</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.47</v>
+        <v>0.74</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>1.12</v>
+        <v>0.46</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>1.04</v>
+        <v>0.54</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.67</v>
+        <v>0.98</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -2272,7 +2272,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.61</v>
+        <v>0.83</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.65</v>
+        <v>1.06</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.44</v>
+        <v>0.63</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.76</v>
+        <v>1.13</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>1.14</v>
+        <v>0.5</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.92</v>
+        <v>0.64</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.46</v>
+        <v>1</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.53</v>
+        <v>1</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.82</v>
+        <v>0.55</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>1.05</v>
+        <v>0.72</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -2764,7 +2764,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>1.14</v>
+        <v>0.5</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.79</v>
+        <v>0.71</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.42</v>
+        <v>1.03</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.99</v>
+        <v>0.76</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -2969,7 +2969,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.92</v>
+        <v>1.12</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.71</v>
+        <v>1.07</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.87</v>
+        <v>0.47</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.51</v>
+        <v>1.07</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.63</v>
+        <v>1.12</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.68</v>
+        <v>0.52</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.64</v>
+        <v>0.84</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.53</v>
+        <v>0.98</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.44</v>
+        <v>0.84</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.44</v>
+        <v>0.87</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
@@ -3420,7 +3420,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>1.09</v>
+        <v>0.54</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
@@ -3461,7 +3461,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
@@ -3502,7 +3502,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.73</v>
+        <v>0.98</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>0.64</v>
+        <v>0.46</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.97</v>
+        <v>0.43</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
@@ -3666,7 +3666,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0.45</v>
+        <v>0.89</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.72</v>
+        <v>0.54</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.87</v>
+        <v>1.12</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>1.14</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>1.13</v>
+        <v>0.53</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.8</v>
+        <v>0.45</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.59</v>
+        <v>0.99</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>1.06</v>
+        <v>0.85</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>0.7</v>
+        <v>0.51</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.66</v>
+        <v>0.85</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.79</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>0.99</v>
+        <v>0.68</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.6</v>
+        <v>1.01</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
@@ -4322,7 +4322,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>1.09</v>
+        <v>0.88</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>1.06</v>
+        <v>0.95</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>0.88</v>
+        <v>0.98</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
@@ -4486,7 +4486,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.88</v>
+        <v>0.67</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.76</v>
+        <v>1.1</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.51</v>
+        <v>0.83</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>1.14</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
@@ -4650,7 +4650,7 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
@@ -4691,7 +4691,7 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.47</v>
+        <v>0.99</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>0.98</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>0.89</v>
+        <v>0.97</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>0.53</v>
+        <v>0.72</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>0.61</v>
+        <v>0.47</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
@@ -4937,7 +4937,7 @@
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>0.88</v>
+        <v>1.06</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>0.89</v>
+        <v>0.53</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
@@ -5060,7 +5060,7 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
@@ -5101,7 +5101,7 @@
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.92</v>
+        <v>0.45</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0.43</v>
+        <v>0.54</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
@@ -5183,7 +5183,7 @@
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>0.86</v>
+        <v>1.02</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0.91</v>
+        <v>1.06</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0.9</v>
+        <v>1.11</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>0.59</v>
+        <v>0.73</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>1.13</v>
+        <v>0.49</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>0.57</v>
+        <v>1.01</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
@@ -5470,7 +5470,7 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>0.62</v>
+        <v>0.9</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>0.88</v>
+        <v>0.59</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>0.83</v>
+        <v>0.61</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>1.13</v>
+        <v>0.54</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>0.89</v>
+        <v>1.14</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>0.47</v>
+        <v>0.93</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>0.67</v>
+        <v>0.89</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>1.04</v>
+        <v>0.92</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>0.99</v>
+        <v>0.91</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>0.67</v>
+        <v>0.43</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
@@ -6044,7 +6044,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>0.75</v>
+        <v>0.97</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>0.92</v>
+        <v>0.76</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
@@ -6208,7 +6208,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
@@ -6249,7 +6249,7 @@
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0.8</v>
+        <v>1.09</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
@@ -6331,7 +6331,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>0.63</v>
+        <v>0.55</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>0.98</v>
+        <v>0.88</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
@@ -6413,7 +6413,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.87</v>
+        <v>0.7</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
@@ -6454,7 +6454,7 @@
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>0.75</v>
+        <v>1.07</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -6536,7 +6536,7 @@
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>0.97</v>
+        <v>0.82</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
@@ -6618,7 +6618,7 @@
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>0.55</v>
+        <v>0.95</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
@@ -6659,7 +6659,7 @@
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>1.12</v>
+        <v>0.84</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
@@ -6700,7 +6700,7 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>1.13</v>
+        <v>0.63</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
@@ -6741,7 +6741,7 @@
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>0.72</v>
+        <v>1.11</v>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>0.65</v>
+        <v>0.55</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
@@ -6864,7 +6864,7 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>1.15</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
@@ -6946,7 +6946,7 @@
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>1.15</v>
+        <v>0.53</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
@@ -6987,7 +6987,7 @@
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>0.48</v>
+        <v>1.06</v>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>0.97</v>
+        <v>0.57</v>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
@@ -7110,7 +7110,7 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
@@ -7151,7 +7151,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>0.52</v>
+        <v>0.59</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
@@ -7192,7 +7192,7 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>1.03</v>
+        <v>0.63</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.43</v>
+        <v>0.66</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>0.99</v>
+        <v>0.53</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>0.96</v>
+        <v>0.54</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
@@ -7438,7 +7438,7 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>0.48</v>
+        <v>1</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>0.71</v>
+        <v>0.96</v>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>0.49</v>
+        <v>0.87</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
@@ -7561,7 +7561,7 @@
         </is>
       </c>
       <c r="G173" s="2" t="n">
-        <v>0.61</v>
+        <v>0.98</v>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
@@ -7602,7 +7602,7 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>1.05</v>
+        <v>0.75</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
@@ -7643,7 +7643,7 @@
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>1.08</v>
+        <v>0.57</v>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
@@ -7684,7 +7684,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         </is>
       </c>
       <c r="G177" s="2" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
@@ -7766,7 +7766,7 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>0.64</v>
+        <v>0.77</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="G179" s="2" t="n">
-        <v>0.61</v>
+        <v>0.78</v>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
@@ -7848,7 +7848,7 @@
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F181" s="3" t="inlineStr">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>0.52</v>
+        <v>0.67</v>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
@@ -7930,7 +7930,7 @@
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>0.75</v>
+        <v>0.43</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
@@ -7971,7 +7971,7 @@
         </is>
       </c>
       <c r="G183" s="2" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
@@ -8012,7 +8012,7 @@
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
@@ -8053,7 +8053,7 @@
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>1.08</v>
+        <v>0.47</v>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.09</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
@@ -8135,7 +8135,7 @@
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>0.98</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
@@ -8176,7 +8176,7 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>0.65</v>
+        <v>1.08</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>0.96</v>
+        <v>0.67</v>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
@@ -8258,7 +8258,7 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>0.99</v>
+        <v>1.06</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr">
@@ -8299,7 +8299,7 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>0.73</v>
+        <v>0.52</v>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr">
@@ -8340,7 +8340,7 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>0.82</v>
+        <v>0.61</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F193" s="3" t="inlineStr">
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>0.61</v>
+        <v>0.72</v>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F194" s="3" t="inlineStr">
@@ -8422,7 +8422,7 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>0.55</v>
+        <v>0.91</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F195" s="3" t="inlineStr">
@@ -8463,7 +8463,7 @@
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>1.07</v>
+        <v>0.93</v>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F196" s="3" t="inlineStr">
@@ -8504,7 +8504,7 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>0.61</v>
+        <v>1.05</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F197" s="3" t="inlineStr">
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
@@ -8586,7 +8586,7 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F199" s="3" t="inlineStr">
@@ -8627,7 +8627,7 @@
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>0.49</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>1.05</v>
+        <v>0.95</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F201" s="3" t="inlineStr">
@@ -8709,7 +8709,7 @@
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>1.12</v>
+        <v>0.68</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
@@ -8750,7 +8750,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>0.73</v>
+        <v>0.47</v>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F203" s="3" t="inlineStr">
@@ -8791,7 +8791,7 @@
         </is>
       </c>
       <c r="G203" s="2" t="n">
-        <v>0.62</v>
+        <v>0.98</v>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr">
@@ -8832,7 +8832,7 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F205" s="3" t="inlineStr">
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="G205" s="2" t="n">
-        <v>0.83</v>
+        <v>0.96</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
@@ -8914,7 +8914,7 @@
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>1.04</v>
+        <v>0.66</v>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F207" s="3" t="inlineStr">
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="G207" s="2" t="n">
-        <v>1.08</v>
+        <v>0.83</v>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F208" s="3" t="inlineStr">
@@ -8996,7 +8996,7 @@
         </is>
       </c>
       <c r="G208" s="2" t="n">
-        <v>0.48</v>
+        <v>1.14</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F209" s="3" t="inlineStr">
@@ -9037,7 +9037,7 @@
         </is>
       </c>
       <c r="G209" s="2" t="n">
-        <v>1</v>
+        <v>0.51</v>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>0.43</v>
+        <v>1.03</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         </is>
       </c>
       <c r="G211" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>0.42</v>
+        <v>0.8</v>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
@@ -9201,7 +9201,7 @@
         </is>
       </c>
       <c r="G213" s="2" t="n">
-        <v>0.78</v>
+        <v>1.08</v>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr">
@@ -9242,7 +9242,7 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>0.75</v>
+        <v>0.46</v>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F215" s="3" t="inlineStr">
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="G215" s="2" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F216" s="3" t="inlineStr">
@@ -9324,7 +9324,7 @@
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>0.7</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F217" s="3" t="inlineStr">
@@ -9365,7 +9365,7 @@
         </is>
       </c>
       <c r="G217" s="2" t="n">
-        <v>0.64</v>
+        <v>0.95</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr">
@@ -9406,7 +9406,7 @@
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>1.03</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="G219" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F220" s="3" t="inlineStr">
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>0.51</v>
+        <v>0.44</v>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F221" s="3" t="inlineStr">
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="G221" s="2" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F223" s="3" t="inlineStr">
@@ -9611,7 +9611,7 @@
         </is>
       </c>
       <c r="G223" s="2" t="n">
-        <v>0.73</v>
+        <v>0.97</v>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F224" s="3" t="inlineStr">
@@ -9652,7 +9652,7 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F225" s="3" t="inlineStr">
@@ -9693,7 +9693,7 @@
         </is>
       </c>
       <c r="G225" s="2" t="n">
-        <v>0.73</v>
+        <v>1.07</v>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F226" s="3" t="inlineStr">
@@ -9734,7 +9734,7 @@
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>1.04</v>
+        <v>0.98</v>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F227" s="3" t="inlineStr">
@@ -9775,7 +9775,7 @@
         </is>
       </c>
       <c r="G227" s="2" t="n">
-        <v>0.47</v>
+        <v>1.15</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F228" s="3" t="inlineStr">
@@ -9816,7 +9816,7 @@
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>0.54</v>
+        <v>0.76</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F229" s="3" t="inlineStr">
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="G229" s="2" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>0.92</v>
+        <v>0.77</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F231" s="3" t="inlineStr">
@@ -9939,7 +9939,7 @@
         </is>
       </c>
       <c r="G231" s="2" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F232" s="3" t="inlineStr">
@@ -9980,7 +9980,7 @@
         </is>
       </c>
       <c r="G232" s="2" t="n">
-        <v>0.96</v>
+        <v>1.12</v>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F233" s="3" t="inlineStr">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>0.74</v>
+        <v>0.53</v>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F234" s="3" t="inlineStr">
@@ -10062,7 +10062,7 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>1.11</v>
+        <v>0.84</v>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F235" s="3" t="inlineStr">
@@ -10103,7 +10103,7 @@
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>1.07</v>
+        <v>0.83</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F236" s="3" t="inlineStr">
@@ -10144,7 +10144,7 @@
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>0.92</v>
+        <v>1.06</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F237" s="3" t="inlineStr">
@@ -10185,7 +10185,7 @@
         </is>
       </c>
       <c r="G237" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
@@ -10226,7 +10226,7 @@
         </is>
       </c>
       <c r="G238" s="2" t="n">
-        <v>1.15</v>
+        <v>0.83</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F239" s="3" t="inlineStr">
@@ -10267,7 +10267,7 @@
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
@@ -10299,7 +10299,7 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F240" s="3" t="inlineStr">
@@ -10308,7 +10308,7 @@
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>0.54</v>
+        <v>0.97</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F241" s="3" t="inlineStr">
@@ -10349,7 +10349,7 @@
         </is>
       </c>
       <c r="G241" s="2" t="n">
-        <v>0.79</v>
+        <v>0.48</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>0.84</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F243" s="3" t="inlineStr">
@@ -10431,7 +10431,7 @@
         </is>
       </c>
       <c r="G243" s="2" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F244" s="3" t="inlineStr">
@@ -10472,7 +10472,7 @@
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.98</v>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F245" s="3" t="inlineStr">
@@ -10513,7 +10513,7 @@
         </is>
       </c>
       <c r="G245" s="2" t="n">
-        <v>0.77</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F246" s="3" t="inlineStr">
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>0.84</v>
+        <v>0.71</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F247" s="3" t="inlineStr">
@@ -10595,7 +10595,7 @@
         </is>
       </c>
       <c r="G247" s="2" t="n">
-        <v>1.01</v>
+        <v>0.85</v>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>0.48</v>
+        <v>0.99</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F249" s="3" t="inlineStr">
@@ -10677,7 +10677,7 @@
         </is>
       </c>
       <c r="G249" s="2" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F250" s="3" t="inlineStr">
@@ -10718,7 +10718,7 @@
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>0.48</v>
+        <v>0.64</v>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         </is>
       </c>
       <c r="G251" s="2" t="n">
-        <v>0.82</v>
+        <v>0.58</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F252" s="3" t="inlineStr">
@@ -10800,7 +10800,7 @@
         </is>
       </c>
       <c r="G252" s="2" t="n">
-        <v>0.74</v>
+        <v>0.63</v>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F253" s="3" t="inlineStr">
@@ -10841,7 +10841,7 @@
         </is>
       </c>
       <c r="G253" s="2" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>0.53</v>
+        <v>1.15</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         </is>
       </c>
       <c r="G255" s="2" t="n">
-        <v>0.55</v>
+        <v>1.07</v>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>0.98</v>
+        <v>0.79</v>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         </is>
       </c>
       <c r="G257" s="2" t="n">
-        <v>0.44</v>
+        <v>0.77</v>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F258" s="3" t="inlineStr">
@@ -11046,7 +11046,7 @@
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>1.11</v>
+        <v>0.65</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F259" s="3" t="inlineStr">
@@ -11087,7 +11087,7 @@
         </is>
       </c>
       <c r="G259" s="2" t="n">
-        <v>0.65</v>
+        <v>1.03</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F260" s="3" t="inlineStr">
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>0.52</v>
+        <v>0.64</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F261" s="3" t="inlineStr">
@@ -11169,7 +11169,7 @@
         </is>
       </c>
       <c r="G261" s="2" t="n">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F262" s="3" t="inlineStr">
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>0.54</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         </is>
       </c>
       <c r="G263" s="2" t="n">
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F264" s="3" t="inlineStr">
@@ -11292,7 +11292,7 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0.48</v>
+        <v>0.77</v>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F265" s="3" t="inlineStr">
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="G265" s="2" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>0.8</v>
+        <v>0.87</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
         </is>
       </c>
       <c r="G267" s="2" t="n">
-        <v>0.67</v>
+        <v>0.98</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F268" s="3" t="inlineStr">
@@ -11456,7 +11456,7 @@
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F269" s="3" t="inlineStr">
@@ -11497,7 +11497,7 @@
         </is>
       </c>
       <c r="G269" s="2" t="n">
-        <v>0.87</v>
+        <v>1.08</v>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F270" s="3" t="inlineStr">
@@ -11538,7 +11538,7 @@
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>0.51</v>
+        <v>0.55</v>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F271" s="3" t="inlineStr">
@@ -11579,7 +11579,7 @@
         </is>
       </c>
       <c r="G271" s="2" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F272" s="3" t="inlineStr">
@@ -11620,7 +11620,7 @@
         </is>
       </c>
       <c r="G272" s="2" t="n">
-        <v>0.53</v>
+        <v>0.99</v>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F273" s="3" t="inlineStr">
@@ -11661,7 +11661,7 @@
         </is>
       </c>
       <c r="G273" s="2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F274" s="3" t="inlineStr">
@@ -11702,7 +11702,7 @@
         </is>
       </c>
       <c r="G274" s="2" t="n">
-        <v>0.95</v>
+        <v>1.11</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F275" s="3" t="inlineStr">
@@ -11743,7 +11743,7 @@
         </is>
       </c>
       <c r="G275" s="2" t="n">
-        <v>0.6</v>
+        <v>1.11</v>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         </is>
       </c>
       <c r="G276" s="2" t="n">
-        <v>0.54</v>
+        <v>0.61</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         </is>
       </c>
       <c r="G277" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.11</v>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr">
@@ -11866,7 +11866,7 @@
         </is>
       </c>
       <c r="G278" s="2" t="n">
-        <v>0.46</v>
+        <v>0.86</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         </is>
       </c>
       <c r="G279" s="2" t="n">
-        <v>1.09</v>
+        <v>0.59</v>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr">
@@ -11948,7 +11948,7 @@
         </is>
       </c>
       <c r="G280" s="2" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         </is>
       </c>
       <c r="G281" s="2" t="n">
-        <v>0.98</v>
+        <v>0.8</v>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F282" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>1.08</v>
+        <v>0.85</v>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F283" s="3" t="inlineStr">
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.54</v>
+        <v>0.73</v>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F284" s="3" t="inlineStr">
@@ -12112,7 +12112,7 @@
         </is>
       </c>
       <c r="G284" s="2" t="n">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F285" s="3" t="inlineStr">
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="G285" s="2" t="n">
-        <v>0.95</v>
+        <v>0.71</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         </is>
       </c>
       <c r="G286" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.87</v>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F287" s="3" t="inlineStr">
@@ -12235,7 +12235,7 @@
         </is>
       </c>
       <c r="G287" s="2" t="n">
-        <v>0.54</v>
+        <v>0.84</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F288" s="3" t="inlineStr">
@@ -12276,7 +12276,7 @@
         </is>
       </c>
       <c r="G288" s="2" t="n">
-        <v>0.9</v>
+        <v>0.49</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         </is>
       </c>
       <c r="G289" s="2" t="n">
-        <v>1.07</v>
+        <v>0.86</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F290" s="3" t="inlineStr">
@@ -12358,7 +12358,7 @@
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F291" s="3" t="inlineStr">
@@ -12399,7 +12399,7 @@
         </is>
       </c>
       <c r="G291" s="2" t="n">
-        <v>0.89</v>
+        <v>0.96</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>0.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         </is>
       </c>
       <c r="G293" s="2" t="n">
-        <v>0.73</v>
+        <v>0.96</v>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F294" s="3" t="inlineStr">
@@ -12522,7 +12522,7 @@
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>0.67</v>
+        <v>0.92</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F295" s="3" t="inlineStr">
@@ -12563,7 +12563,7 @@
         </is>
       </c>
       <c r="G295" s="2" t="n">
-        <v>0.53</v>
+        <v>0.92</v>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F296" s="3" t="inlineStr">
@@ -12604,7 +12604,7 @@
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>0.98</v>
+        <v>1.13</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F297" s="3" t="inlineStr">
@@ -12645,7 +12645,7 @@
         </is>
       </c>
       <c r="G297" s="2" t="n">
-        <v>0.86</v>
+        <v>1.08</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F298" s="3" t="inlineStr">
@@ -12686,7 +12686,7 @@
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>0.6</v>
+        <v>1.03</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F299" s="3" t="inlineStr">
@@ -12727,7 +12727,7 @@
         </is>
       </c>
       <c r="G299" s="2" t="n">
-        <v>0.7</v>
+        <v>1.13</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F300" s="3" t="inlineStr">
@@ -12768,7 +12768,7 @@
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>0.58</v>
+        <v>0.96</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         </is>
       </c>
       <c r="G301" s="2" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -12911,7 +12911,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.93</v>
+        <v>0.54</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.47</v>
+        <v>0.71</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -12993,7 +12993,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.85</v>
+        <v>1.02</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -13034,7 +13034,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.05</v>
+        <v>0.88</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -13075,7 +13075,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.58</v>
+        <v>0.43</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -13116,7 +13116,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -13157,7 +13157,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.13</v>
+        <v>0.7</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -13239,7 +13239,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1.01</v>
+        <v>0.44</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -13312,7 +13312,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -13321,7 +13321,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.53</v>
+        <v>0.79</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -13362,7 +13362,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.96</v>
+        <v>0.76</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -13403,7 +13403,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.74</v>
+        <v>0.55</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -13444,7 +13444,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.8</v>
+        <v>1.05</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.99</v>
+        <v>1.04</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -13526,7 +13526,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.89</v>
+        <v>0.43</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -13567,7 +13567,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1.11</v>
+        <v>0.79</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -13649,7 +13649,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1.13</v>
+        <v>0.59</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -13690,7 +13690,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.43</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.91</v>
+        <v>1.14</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -13772,7 +13772,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1.14</v>
+        <v>0.88</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -13813,7 +13813,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.93</v>
+        <v>0.46</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -13854,7 +13854,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.76</v>
+        <v>0.47</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -13895,7 +13895,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.51</v>
+        <v>0.97</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -13927,7 +13927,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -13936,7 +13936,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.62</v>
+        <v>0.92</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.93</v>
+        <v>0.55</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.89</v>
+        <v>0.47</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -14059,7 +14059,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.55</v>
+        <v>0.48</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -14100,7 +14100,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.52</v>
+        <v>0.86</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -14141,7 +14141,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1.1</v>
+        <v>0.68</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -14223,7 +14223,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -14264,7 +14264,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1.05</v>
+        <v>0.43</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -14305,7 +14305,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.83</v>
+        <v>0.62</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1.12</v>
+        <v>0.53</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -14387,7 +14387,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.98</v>
+        <v>1.15</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.57</v>
+        <v>1.12</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -14469,7 +14469,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.47</v>
+        <v>0.74</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -14510,7 +14510,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1.12</v>
+        <v>0.46</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -14551,7 +14551,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1.04</v>
+        <v>0.54</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -14592,7 +14592,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.67</v>
+        <v>0.98</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -14633,7 +14633,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.61</v>
+        <v>0.83</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -14674,7 +14674,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.65</v>
+        <v>1.06</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.44</v>
+        <v>0.63</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -14756,7 +14756,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -14797,7 +14797,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.76</v>
+        <v>1.13</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -14838,7 +14838,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1.14</v>
+        <v>0.5</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -14879,7 +14879,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.92</v>
+        <v>0.64</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -14920,7 +14920,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -14961,7 +14961,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0.46</v>
+        <v>1</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -15002,7 +15002,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0.53</v>
+        <v>1</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.82</v>
+        <v>0.55</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -15084,7 +15084,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1.05</v>
+        <v>0.72</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -15125,7 +15125,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -15166,7 +15166,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1.14</v>
+        <v>0.5</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0.79</v>
+        <v>0.71</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0.42</v>
+        <v>1.03</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -15289,7 +15289,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.99</v>
+        <v>0.76</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -15330,7 +15330,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0.92</v>
+        <v>1.12</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -15371,7 +15371,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.71</v>
+        <v>1.07</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -15412,7 +15412,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.87</v>
+        <v>0.47</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0.51</v>
+        <v>1.07</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -15494,7 +15494,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0.63</v>
+        <v>1.12</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.68</v>
+        <v>0.52</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -15576,7 +15576,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0.64</v>
+        <v>0.84</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -15617,7 +15617,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0.53</v>
+        <v>0.98</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -15658,7 +15658,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -15699,7 +15699,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.44</v>
+        <v>0.84</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -15740,7 +15740,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.44</v>
+        <v>0.87</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -15772,7 +15772,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -15781,7 +15781,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>1.09</v>
+        <v>0.54</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -15813,7 +15813,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -15822,7 +15822,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -15863,7 +15863,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>0.73</v>
+        <v>0.98</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -15904,7 +15904,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.64</v>
+        <v>0.46</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15986,7 +15986,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>0.97</v>
+        <v>0.43</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -16068,7 +16068,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0.45</v>
+        <v>0.89</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -16109,7 +16109,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.72</v>
+        <v>0.54</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -16150,7 +16150,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0.87</v>
+        <v>1.12</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>1.14</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>1.13</v>
+        <v>0.53</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.8</v>
+        <v>0.45</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16314,7 +16314,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>0.59</v>
+        <v>0.99</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16355,7 +16355,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>1.06</v>
+        <v>0.85</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16396,7 +16396,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16437,7 +16437,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>0.7</v>
+        <v>0.51</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -16519,7 +16519,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0.66</v>
+        <v>0.85</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -16560,7 +16560,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>0.79</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -16601,7 +16601,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>0.99</v>
+        <v>0.68</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -16642,7 +16642,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>0.6</v>
+        <v>1.01</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -16683,7 +16683,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>1.09</v>
+        <v>0.88</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -16724,7 +16724,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -16765,7 +16765,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>1.06</v>
+        <v>0.95</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -16806,7 +16806,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>0.88</v>
+        <v>0.98</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -16847,7 +16847,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>0.88</v>
+        <v>0.67</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>0.76</v>
+        <v>1.1</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>0.51</v>
+        <v>0.83</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -16970,7 +16970,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>1.14</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -17011,7 +17011,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -17052,7 +17052,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0.47</v>
+        <v>0.99</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -17093,7 +17093,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>0.98</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -17175,7 +17175,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>0.89</v>
+        <v>0.97</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -17216,7 +17216,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>0.53</v>
+        <v>0.72</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>0.61</v>
+        <v>0.47</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -17298,7 +17298,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>0.88</v>
+        <v>1.06</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -17339,7 +17339,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>0.89</v>
+        <v>0.53</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -17380,7 +17380,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -17421,7 +17421,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -17462,7 +17462,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>0.92</v>
+        <v>0.45</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>0.43</v>
+        <v>0.54</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -17544,7 +17544,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>0.86</v>
+        <v>1.02</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -17585,7 +17585,7 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>0.91</v>
+        <v>1.06</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -17667,7 +17667,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>0.9</v>
+        <v>1.11</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -17708,7 +17708,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>0.59</v>
+        <v>0.73</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -17749,7 +17749,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>1.13</v>
+        <v>0.49</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -17790,7 +17790,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>0.57</v>
+        <v>1.01</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -17831,7 +17831,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>0.62</v>
+        <v>0.9</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -17913,7 +17913,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0.88</v>
+        <v>0.59</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>0.83</v>
+        <v>0.61</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -17995,7 +17995,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>1.13</v>
+        <v>0.54</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -18036,7 +18036,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -18077,7 +18077,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>0.89</v>
+        <v>1.14</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -18118,7 +18118,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -18159,7 +18159,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>0.47</v>
+        <v>0.93</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -18200,7 +18200,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>0.67</v>
+        <v>0.89</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -18241,7 +18241,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -18282,7 +18282,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>1.04</v>
+        <v>0.92</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -18323,7 +18323,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>0.99</v>
+        <v>0.91</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -18355,7 +18355,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -18364,7 +18364,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>0.67</v>
+        <v>0.43</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -18405,7 +18405,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>0.75</v>
+        <v>0.97</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>0.92</v>
+        <v>0.76</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -18569,7 +18569,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -18610,7 +18610,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -18651,7 +18651,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>0.8</v>
+        <v>1.09</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -18692,7 +18692,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>0.63</v>
+        <v>0.55</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>0.98</v>
+        <v>0.88</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -18774,7 +18774,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>0.87</v>
+        <v>0.7</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -18815,7 +18815,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -18856,7 +18856,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>0.75</v>
+        <v>1.07</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>0.97</v>
+        <v>0.82</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -18979,7 +18979,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>0.55</v>
+        <v>0.95</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -19020,7 +19020,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>1.12</v>
+        <v>0.84</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -19061,7 +19061,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>1.13</v>
+        <v>0.63</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -19102,7 +19102,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>0.72</v>
+        <v>1.11</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -19184,7 +19184,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>0.65</v>
+        <v>0.55</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -19225,7 +19225,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>1.15</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -19266,7 +19266,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -19307,7 +19307,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>1.15</v>
+        <v>0.53</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -19348,7 +19348,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>0.48</v>
+        <v>1.06</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -19430,7 +19430,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>0.97</v>
+        <v>0.57</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -19471,7 +19471,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -19512,7 +19512,7 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>0.52</v>
+        <v>0.59</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -19553,7 +19553,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>1.03</v>
+        <v>0.63</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -19594,7 +19594,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>0.43</v>
+        <v>0.66</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>0.99</v>
+        <v>0.53</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -19708,7 +19708,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -19717,7 +19717,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>0.96</v>
+        <v>0.54</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -19758,7 +19758,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -19799,7 +19799,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>0.48</v>
+        <v>1</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>0.71</v>
+        <v>0.96</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>0.49</v>
+        <v>0.87</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -19922,7 +19922,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>0.61</v>
+        <v>0.98</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -19963,7 +19963,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>1.05</v>
+        <v>0.75</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -20004,7 +20004,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>1.08</v>
+        <v>0.57</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -20045,7 +20045,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -20127,7 +20127,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>0.64</v>
+        <v>0.77</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -20168,7 +20168,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>0.61</v>
+        <v>0.78</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -20209,7 +20209,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>0.52</v>
+        <v>0.67</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -20291,7 +20291,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>0.75</v>
+        <v>0.43</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -20332,7 +20332,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -20373,7 +20373,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -20414,7 +20414,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>1.08</v>
+        <v>0.47</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.09</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -20496,7 +20496,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>0.98</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -20537,7 +20537,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>0.65</v>
+        <v>1.08</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -20578,7 +20578,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>0.96</v>
+        <v>0.67</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -20610,7 +20610,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -20619,7 +20619,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>0.99</v>
+        <v>1.06</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -20660,7 +20660,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>0.73</v>
+        <v>0.52</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -20701,7 +20701,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>0.82</v>
+        <v>0.61</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -20742,7 +20742,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>0.61</v>
+        <v>0.72</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -20774,7 +20774,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -20783,7 +20783,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>0.55</v>
+        <v>0.91</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -20824,7 +20824,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>1.07</v>
+        <v>0.93</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -20865,7 +20865,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>0.61</v>
+        <v>1.05</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -20906,7 +20906,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -20988,7 +20988,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>0.49</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -21029,7 +21029,7 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>1.05</v>
+        <v>0.95</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -21070,7 +21070,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>1.12</v>
+        <v>0.68</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -21111,7 +21111,7 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>0.73</v>
+        <v>0.47</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -21152,7 +21152,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>0.62</v>
+        <v>0.98</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -21193,7 +21193,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -21225,7 +21225,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -21234,7 +21234,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>0.83</v>
+        <v>0.96</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -21275,7 +21275,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>1.04</v>
+        <v>0.66</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -21316,7 +21316,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>1.08</v>
+        <v>0.83</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -21357,7 +21357,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>0.48</v>
+        <v>1.14</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -21398,7 +21398,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>1</v>
+        <v>0.51</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>0.43</v>
+        <v>1.03</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -21521,7 +21521,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>0.42</v>
+        <v>0.8</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -21562,7 +21562,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>0.78</v>
+        <v>1.08</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -21603,7 +21603,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>0.75</v>
+        <v>0.46</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -21644,7 +21644,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -21685,7 +21685,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>0.7</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -21726,7 +21726,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>0.64</v>
+        <v>0.95</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -21767,7 +21767,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>1.03</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -21849,7 +21849,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>0.51</v>
+        <v>0.44</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -21890,7 +21890,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -21972,7 +21972,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>0.73</v>
+        <v>0.97</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -22013,7 +22013,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -22054,7 +22054,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>0.73</v>
+        <v>1.07</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -22095,7 +22095,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>1.04</v>
+        <v>0.98</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -22136,7 +22136,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>0.47</v>
+        <v>1.15</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -22177,7 +22177,7 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>0.54</v>
+        <v>0.76</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -22209,7 +22209,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -22218,7 +22218,7 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>0.92</v>
+        <v>0.77</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -22300,7 +22300,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -22341,7 +22341,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>0.96</v>
+        <v>1.12</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -22382,7 +22382,7 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>0.74</v>
+        <v>0.53</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -22423,7 +22423,7 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>1.11</v>
+        <v>0.84</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -22464,7 +22464,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>1.07</v>
+        <v>0.83</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -22505,7 +22505,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>0.92</v>
+        <v>1.06</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -22546,7 +22546,7 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>1.15</v>
+        <v>0.83</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -22628,7 +22628,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -22669,7 +22669,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>0.54</v>
+        <v>0.97</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -22710,7 +22710,7 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>0.79</v>
+        <v>0.48</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -22742,7 +22742,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -22751,7 +22751,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>0.84</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -22783,7 +22783,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -22792,7 +22792,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -22833,7 +22833,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.98</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -22865,7 +22865,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -22874,7 +22874,7 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>0.77</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -22915,7 +22915,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>0.84</v>
+        <v>0.71</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -22947,7 +22947,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>1.01</v>
+        <v>0.85</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>0.48</v>
+        <v>0.99</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -23038,7 +23038,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -23079,7 +23079,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>0.48</v>
+        <v>0.64</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>0.82</v>
+        <v>0.58</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -23152,7 +23152,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -23161,7 +23161,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>0.74</v>
+        <v>0.63</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -23202,7 +23202,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>0.53</v>
+        <v>1.15</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>0.55</v>
+        <v>1.07</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -23325,7 +23325,7 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>0.98</v>
+        <v>0.79</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>0.44</v>
+        <v>0.77</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -23407,7 +23407,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>1.11</v>
+        <v>0.65</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -23448,7 +23448,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>0.65</v>
+        <v>1.03</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -23489,7 +23489,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>0.52</v>
+        <v>0.64</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -23530,7 +23530,7 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -23571,7 +23571,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>0.54</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -23653,7 +23653,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>0.48</v>
+        <v>0.77</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -23694,7 +23694,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -23735,7 +23735,7 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>0.8</v>
+        <v>0.87</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -23776,7 +23776,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>0.67</v>
+        <v>0.98</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -23817,7 +23817,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -23849,7 +23849,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -23858,7 +23858,7 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>0.87</v>
+        <v>1.08</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -23899,7 +23899,7 @@
         </is>
       </c>
       <c r="G270" t="n">
-        <v>0.51</v>
+        <v>0.55</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -23940,7 +23940,7 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -23981,7 +23981,7 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>0.53</v>
+        <v>0.99</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -24013,7 +24013,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -24022,7 +24022,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -24063,7 +24063,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>0.95</v>
+        <v>1.11</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -24104,7 +24104,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>0.6</v>
+        <v>1.11</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>0.54</v>
+        <v>0.61</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.11</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -24227,7 +24227,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>0.46</v>
+        <v>0.86</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>1.09</v>
+        <v>0.59</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -24309,7 +24309,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>0.98</v>
+        <v>0.8</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -24391,7 +24391,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>1.08</v>
+        <v>0.85</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>0.54</v>
+        <v>0.73</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -24473,7 +24473,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -24514,7 +24514,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>0.95</v>
+        <v>0.71</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.87</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -24596,7 +24596,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>0.54</v>
+        <v>0.84</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -24637,7 +24637,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>0.9</v>
+        <v>0.49</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -24678,7 +24678,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>1.07</v>
+        <v>0.86</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -24710,7 +24710,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -24719,7 +24719,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -24760,7 +24760,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>0.89</v>
+        <v>0.96</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>0.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -24842,7 +24842,7 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>0.73</v>
+        <v>0.96</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -24883,7 +24883,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>0.67</v>
+        <v>0.92</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -24924,7 +24924,7 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>0.53</v>
+        <v>0.92</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -24965,7 +24965,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>0.98</v>
+        <v>1.13</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -25006,7 +25006,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>0.86</v>
+        <v>1.08</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -25047,7 +25047,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>0.6</v>
+        <v>1.03</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -25079,7 +25079,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -25088,7 +25088,7 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>0.7</v>
+        <v>1.13</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -25129,7 +25129,7 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>0.58</v>
+        <v>0.96</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
@@ -25170,7 +25170,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
